--- a/inst/extdata/colorado_criteria_crosswalk.xlsx
+++ b/inst/extdata/colorado_criteria_crosswalk.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772D23B5-C957-47CD-B329-A0B759926CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD77611A-A625-4F3B-80D2-923462D5119F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{380839A1-A469-4C26-93CF-5FD0D1BCA51C}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="20710" windowHeight="11020" xr2:uid="{380839A1-A469-4C26-93CF-5FD0D1BCA51C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3376" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3376" uniqueCount="198">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -371,12 +371,6 @@
     <t>geometric mean</t>
   </si>
   <si>
-    <t>Potential Primary Contact Use</t>
-  </si>
-  <si>
-    <t>Not Primary Contact Use Recreation</t>
-  </si>
-  <si>
     <t>Copper</t>
   </si>
   <si>
@@ -633,6 +627,9 @@
   </si>
   <si>
     <t>DISSOLVED OXYGEN</t>
+  </si>
+  <si>
+    <t>Recreation</t>
   </si>
 </sst>
 </file>
@@ -1045,6 +1042,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" s="4" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
@@ -1184,7 +1182,7 @@
         <v>43</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>44</v>
@@ -1255,7 +1253,7 @@
         <v>43</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>54</v>
@@ -1326,7 +1324,7 @@
         <v>43</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>55</v>
@@ -1811,7 +1809,7 @@
         <v>43</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>58</v>
@@ -1880,7 +1878,7 @@
         <v>43</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>59</v>
@@ -1949,7 +1947,7 @@
         <v>43</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>58</v>
@@ -2018,7 +2016,7 @@
         <v>43</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>59</v>
@@ -2087,7 +2085,7 @@
         <v>43</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>44</v>
@@ -2174,7 +2172,7 @@
         <v>43</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>54</v>
@@ -2261,7 +2259,7 @@
         <v>43</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>55</v>
@@ -2773,7 +2771,7 @@
         <v>43</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>44</v>
@@ -2854,7 +2852,7 @@
         <v>43</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>44</v>
@@ -6429,7 +6427,7 @@
         <v>43</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>106</v>
@@ -6496,10 +6494,10 @@
         <v>43</v>
       </c>
       <c r="C74" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D74" s="5" t="s">
         <v>197</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>111</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>107</v>
@@ -6563,10 +6561,10 @@
         <v>43</v>
       </c>
       <c r="C75" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D75" s="5" t="s">
         <v>197</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>107</v>
@@ -6630,7 +6628,7 @@
         <v>43</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>59</v>
@@ -6697,7 +6695,7 @@
         <v>43</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>54</v>
@@ -6768,13 +6766,13 @@
         <v>43</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>79</v>
@@ -6839,13 +6837,13 @@
         <v>43</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
@@ -6908,13 +6906,13 @@
         <v>43</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
@@ -6977,13 +6975,13 @@
         <v>43</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
@@ -7046,13 +7044,13 @@
         <v>43</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
@@ -7115,13 +7113,13 @@
         <v>43</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
@@ -7167,13 +7165,13 @@
       <c r="AC83" s="5"/>
       <c r="AD83" s="5"/>
       <c r="AE83" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AF83" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG83" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AH83" s="5"/>
       <c r="AI83" s="5"/>
@@ -7194,13 +7192,13 @@
         <v>43</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
@@ -7263,13 +7261,13 @@
         <v>43</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
@@ -7332,13 +7330,13 @@
         <v>43</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D86" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
@@ -7384,13 +7382,13 @@
       <c r="AC86" s="5"/>
       <c r="AD86" s="5"/>
       <c r="AE86" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AF86" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG86" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AH86" s="5"/>
       <c r="AI86" s="5"/>
@@ -7411,13 +7409,13 @@
         <v>43</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
@@ -7480,13 +7478,13 @@
         <v>43</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
@@ -7549,13 +7547,13 @@
         <v>43</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>106</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>79</v>
@@ -7585,13 +7583,13 @@
         <v>51</v>
       </c>
       <c r="S89" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="T89" s="5">
         <v>15</v>
       </c>
       <c r="U89" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V89" s="5"/>
       <c r="W89" s="5"/>
@@ -7618,13 +7616,13 @@
         <v>43</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>79</v>
@@ -7654,13 +7652,13 @@
         <v>51</v>
       </c>
       <c r="S90" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="T90" s="5">
         <v>15</v>
       </c>
       <c r="U90" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V90" s="5"/>
       <c r="W90" s="5"/>
@@ -7687,13 +7685,13 @@
         <v>43</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>79</v>
@@ -7723,13 +7721,13 @@
         <v>51</v>
       </c>
       <c r="S91" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="T91" s="5">
         <v>15</v>
       </c>
       <c r="U91" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V91" s="5"/>
       <c r="W91" s="5"/>
@@ -7756,13 +7754,13 @@
         <v>43</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>79</v>
@@ -7792,13 +7790,13 @@
         <v>51</v>
       </c>
       <c r="S92" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="T92" s="5">
         <v>15</v>
       </c>
       <c r="U92" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V92" s="5"/>
       <c r="W92" s="5"/>
@@ -7825,13 +7823,13 @@
         <v>43</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>79</v>
@@ -7861,19 +7859,19 @@
         <v>51</v>
       </c>
       <c r="S93" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="T93" s="5">
         <v>15</v>
       </c>
       <c r="U93" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V93" s="5"/>
       <c r="W93" s="5"/>
       <c r="X93" s="5"/>
       <c r="Y93" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="Z93" s="5"/>
       <c r="AA93" s="5"/>
@@ -7896,13 +7894,13 @@
         <v>43</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>79</v>
@@ -7932,13 +7930,13 @@
         <v>51</v>
       </c>
       <c r="S94" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="T94" s="5">
         <v>15</v>
       </c>
       <c r="U94" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V94" s="5"/>
       <c r="W94" s="5"/>
@@ -7965,13 +7963,13 @@
         <v>43</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F95" s="5" t="s">
         <v>79</v>
@@ -8001,13 +7999,13 @@
         <v>51</v>
       </c>
       <c r="S95" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="T95" s="5">
         <v>15</v>
       </c>
       <c r="U95" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V95" s="5"/>
       <c r="W95" s="5"/>
@@ -8034,13 +8032,13 @@
         <v>43</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F96" s="5" t="s">
         <v>79</v>
@@ -8070,13 +8068,13 @@
         <v>51</v>
       </c>
       <c r="S96" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="T96" s="5">
         <v>15</v>
       </c>
       <c r="U96" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V96" s="5"/>
       <c r="W96" s="5"/>
@@ -8103,13 +8101,13 @@
         <v>43</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>79</v>
@@ -8139,13 +8137,13 @@
         <v>51</v>
       </c>
       <c r="S97" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="T97" s="5">
         <v>15</v>
       </c>
       <c r="U97" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V97" s="5"/>
       <c r="W97" s="5"/>
@@ -8178,7 +8176,7 @@
         <v>106</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
@@ -8199,7 +8197,7 @@
         <v>9</v>
       </c>
       <c r="P98" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q98" s="5">
         <v>1</v>
@@ -8208,13 +8206,13 @@
         <v>51</v>
       </c>
       <c r="S98" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T98" s="5">
         <v>15</v>
       </c>
       <c r="U98" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V98" s="5"/>
       <c r="W98" s="5"/>
@@ -8244,10 +8242,10 @@
         <v>67</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
@@ -8268,7 +8266,7 @@
         <v>9</v>
       </c>
       <c r="P99" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q99" s="5">
         <v>1</v>
@@ -8277,13 +8275,13 @@
         <v>51</v>
       </c>
       <c r="S99" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T99" s="5">
         <v>15</v>
       </c>
       <c r="U99" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V99" s="5"/>
       <c r="W99" s="5"/>
@@ -8313,10 +8311,10 @@
         <v>67</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F100" s="5"/>
       <c r="G100" s="5"/>
@@ -8337,7 +8335,7 @@
         <v>9</v>
       </c>
       <c r="P100" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q100" s="5">
         <v>1</v>
@@ -8346,13 +8344,13 @@
         <v>51</v>
       </c>
       <c r="S100" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T100" s="5">
         <v>15</v>
       </c>
       <c r="U100" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V100" s="5"/>
       <c r="W100" s="5"/>
@@ -8385,7 +8383,7 @@
         <v>44</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F101" s="5"/>
       <c r="G101" s="5"/>
@@ -8406,7 +8404,7 @@
         <v>9</v>
       </c>
       <c r="P101" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q101" s="5">
         <v>1</v>
@@ -8415,13 +8413,13 @@
         <v>51</v>
       </c>
       <c r="S101" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T101" s="5">
         <v>15</v>
       </c>
       <c r="U101" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V101" s="5"/>
       <c r="W101" s="5"/>
@@ -8454,7 +8452,7 @@
         <v>54</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
@@ -8475,7 +8473,7 @@
         <v>9</v>
       </c>
       <c r="P102" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q102" s="5">
         <v>1</v>
@@ -8484,13 +8482,13 @@
         <v>51</v>
       </c>
       <c r="S102" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T102" s="5">
         <v>15</v>
       </c>
       <c r="U102" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V102" s="5"/>
       <c r="W102" s="5"/>
@@ -8523,7 +8521,7 @@
         <v>55</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
@@ -8544,7 +8542,7 @@
         <v>9</v>
       </c>
       <c r="P103" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q103" s="5">
         <v>1</v>
@@ -8553,13 +8551,13 @@
         <v>51</v>
       </c>
       <c r="S103" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T103" s="5">
         <v>15</v>
       </c>
       <c r="U103" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V103" s="5"/>
       <c r="W103" s="5"/>
@@ -8592,7 +8590,7 @@
         <v>59</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F104" s="5"/>
       <c r="G104" s="5"/>
@@ -8613,7 +8611,7 @@
         <v>9</v>
       </c>
       <c r="P104" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q104" s="5">
         <v>1</v>
@@ -8622,13 +8620,13 @@
         <v>51</v>
       </c>
       <c r="S104" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T104" s="5">
         <v>15</v>
       </c>
       <c r="U104" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V104" s="5"/>
       <c r="W104" s="5"/>
@@ -8655,7 +8653,7 @@
         <v>43</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>44</v>
@@ -8699,7 +8697,7 @@
         <v>50</v>
       </c>
       <c r="U105" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V105" s="5"/>
       <c r="W105" s="5"/>
@@ -8726,7 +8724,7 @@
         <v>43</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>54</v>
@@ -8770,7 +8768,7 @@
         <v>50</v>
       </c>
       <c r="U106" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V106" s="5"/>
       <c r="W106" s="5"/>
@@ -8797,7 +8795,7 @@
         <v>43</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>55</v>
@@ -8841,7 +8839,7 @@
         <v>50</v>
       </c>
       <c r="U107" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V107" s="5"/>
       <c r="W107" s="5"/>
@@ -8868,16 +8866,16 @@
         <v>43</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="5" t="s">
@@ -8912,7 +8910,7 @@
         <v>85</v>
       </c>
       <c r="U108" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V108" s="5"/>
       <c r="W108" s="5"/>
@@ -8939,16 +8937,16 @@
         <v>43</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G109" s="5"/>
       <c r="H109" s="5" t="s">
@@ -8983,7 +8981,7 @@
         <v>85</v>
       </c>
       <c r="U109" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V109" s="5"/>
       <c r="W109" s="5"/>
@@ -9010,16 +9008,16 @@
         <v>43</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="5" t="s">
@@ -9054,7 +9052,7 @@
         <v>85</v>
       </c>
       <c r="U110" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V110" s="5"/>
       <c r="W110" s="5"/>
@@ -9081,16 +9079,16 @@
         <v>43</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="5" t="s">
@@ -9125,7 +9123,7 @@
         <v>85</v>
       </c>
       <c r="U111" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V111" s="5"/>
       <c r="W111" s="5"/>
@@ -9152,13 +9150,13 @@
         <v>43</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F112" s="5"/>
       <c r="G112" s="5"/>
@@ -9194,7 +9192,7 @@
         <v>85</v>
       </c>
       <c r="U112" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V112" s="5"/>
       <c r="W112" s="5"/>
@@ -9221,13 +9219,13 @@
         <v>43</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F113" s="5"/>
       <c r="G113" s="5"/>
@@ -9263,7 +9261,7 @@
         <v>85</v>
       </c>
       <c r="U113" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V113" s="5"/>
       <c r="W113" s="5"/>
@@ -9290,13 +9288,13 @@
         <v>43</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>79</v>
@@ -9334,7 +9332,7 @@
         <v>85</v>
       </c>
       <c r="U114" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V114" s="5"/>
       <c r="W114" s="5"/>
@@ -9361,13 +9359,13 @@
         <v>43</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F115" s="5"/>
       <c r="G115" s="5"/>
@@ -9388,7 +9386,7 @@
         <v>7000000</v>
       </c>
       <c r="P115" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="Q115" s="5">
         <v>30</v>
@@ -9403,7 +9401,7 @@
         <v>85</v>
       </c>
       <c r="U115" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V115" s="5"/>
       <c r="W115" s="5"/>
@@ -9430,7 +9428,7 @@
         <v>43</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>44</v>
@@ -9472,7 +9470,7 @@
         <v>85</v>
       </c>
       <c r="U116" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V116" s="5"/>
       <c r="W116" s="5"/>
@@ -9484,13 +9482,13 @@
       <c r="AC116" s="5"/>
       <c r="AD116" s="5"/>
       <c r="AE116" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AF116" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG116" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="AF116" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="AG116" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="AH116" s="5"/>
       <c r="AI116" s="5"/>
@@ -9505,7 +9503,7 @@
         <v>43</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>44</v>
@@ -9547,7 +9545,7 @@
         <v>85</v>
       </c>
       <c r="U117" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V117" s="5"/>
       <c r="W117" s="5"/>
@@ -9559,13 +9557,13 @@
       <c r="AC117" s="5"/>
       <c r="AD117" s="5"/>
       <c r="AE117" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AF117" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG117" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AH117" s="5"/>
       <c r="AI117" s="5"/>
@@ -9580,7 +9578,7 @@
         <v>43</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D118" s="5" t="s">
         <v>54</v>
@@ -9622,7 +9620,7 @@
         <v>85</v>
       </c>
       <c r="U118" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V118" s="5"/>
       <c r="W118" s="5"/>
@@ -9634,13 +9632,13 @@
       <c r="AC118" s="5"/>
       <c r="AD118" s="5"/>
       <c r="AE118" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AF118" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG118" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AH118" s="5"/>
       <c r="AI118" s="5"/>
@@ -9655,7 +9653,7 @@
         <v>43</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>54</v>
@@ -9697,7 +9695,7 @@
         <v>85</v>
       </c>
       <c r="U119" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V119" s="5"/>
       <c r="W119" s="5"/>
@@ -9709,13 +9707,13 @@
       <c r="AC119" s="5"/>
       <c r="AD119" s="5"/>
       <c r="AE119" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AF119" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG119" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AH119" s="5"/>
       <c r="AI119" s="5"/>
@@ -9730,7 +9728,7 @@
         <v>43</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>55</v>
@@ -9772,7 +9770,7 @@
         <v>85</v>
       </c>
       <c r="U120" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V120" s="5"/>
       <c r="W120" s="5"/>
@@ -9784,13 +9782,13 @@
       <c r="AC120" s="5"/>
       <c r="AD120" s="5"/>
       <c r="AE120" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AF120" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG120" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="AF120" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="AG120" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="AH120" s="5"/>
       <c r="AI120" s="5"/>
@@ -9805,7 +9803,7 @@
         <v>43</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>55</v>
@@ -9847,7 +9845,7 @@
         <v>85</v>
       </c>
       <c r="U121" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V121" s="5"/>
       <c r="W121" s="5"/>
@@ -9859,13 +9857,13 @@
       <c r="AC121" s="5"/>
       <c r="AD121" s="5"/>
       <c r="AE121" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AF121" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG121" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AH121" s="5"/>
       <c r="AI121" s="5"/>
@@ -9922,7 +9920,7 @@
         <v>50</v>
       </c>
       <c r="U122" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V122" s="5"/>
       <c r="W122" s="5"/>
@@ -9934,13 +9932,13 @@
       <c r="AC122" s="5"/>
       <c r="AD122" s="5"/>
       <c r="AE122" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AF122" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AG122" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AH122" s="5"/>
       <c r="AI122" s="5"/>
@@ -9963,13 +9961,13 @@
         <v>43</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>79</v>
@@ -10007,7 +10005,7 @@
         <v>85</v>
       </c>
       <c r="U123" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V123" s="5"/>
       <c r="W123" s="5"/>
@@ -10034,13 +10032,13 @@
         <v>43</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>79</v>
@@ -10078,7 +10076,7 @@
         <v>85</v>
       </c>
       <c r="U124" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V124" s="5"/>
       <c r="W124" s="5"/>
@@ -10105,13 +10103,13 @@
         <v>43</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>79</v>
@@ -10149,7 +10147,7 @@
         <v>85</v>
       </c>
       <c r="U125" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V125" s="5"/>
       <c r="W125" s="5"/>
@@ -10176,13 +10174,13 @@
         <v>43</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F126" s="5" t="s">
         <v>79</v>
@@ -10220,7 +10218,7 @@
         <v>85</v>
       </c>
       <c r="U126" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V126" s="5"/>
       <c r="W126" s="5"/>
@@ -10247,13 +10245,13 @@
         <v>43</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>79</v>
@@ -10291,7 +10289,7 @@
         <v>85</v>
       </c>
       <c r="U127" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V127" s="5"/>
       <c r="W127" s="5"/>
@@ -10318,13 +10316,13 @@
         <v>43</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D128" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>79</v>
@@ -10362,7 +10360,7 @@
         <v>50</v>
       </c>
       <c r="U128" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V128" s="5"/>
       <c r="W128" s="5"/>
@@ -10389,13 +10387,13 @@
         <v>43</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>79</v>
@@ -10433,7 +10431,7 @@
         <v>50</v>
       </c>
       <c r="U129" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V129" s="5"/>
       <c r="W129" s="5"/>
@@ -10460,13 +10458,13 @@
         <v>43</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D130" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>79</v>
@@ -10504,7 +10502,7 @@
         <v>50</v>
       </c>
       <c r="U130" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V130" s="5"/>
       <c r="W130" s="5"/>
@@ -10531,13 +10529,13 @@
         <v>43</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>79</v>
@@ -10575,7 +10573,7 @@
         <v>50</v>
       </c>
       <c r="U131" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V131" s="5"/>
       <c r="W131" s="5"/>
@@ -10602,13 +10600,13 @@
         <v>43</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>79</v>
@@ -10646,7 +10644,7 @@
         <v>50</v>
       </c>
       <c r="U132" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V132" s="5"/>
       <c r="W132" s="5"/>
@@ -10673,13 +10671,13 @@
         <v>43</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>79</v>
@@ -10717,7 +10715,7 @@
         <v>50</v>
       </c>
       <c r="U133" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V133" s="5"/>
       <c r="W133" s="5"/>
@@ -10744,13 +10742,13 @@
         <v>43</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D134" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>79</v>
@@ -10788,7 +10786,7 @@
         <v>50</v>
       </c>
       <c r="U134" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V134" s="5"/>
       <c r="W134" s="5"/>
@@ -10857,7 +10855,7 @@
         <v>85</v>
       </c>
       <c r="U135" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V135" s="5"/>
       <c r="W135" s="5"/>
@@ -10869,13 +10867,13 @@
       <c r="AC135" s="5"/>
       <c r="AD135" s="5"/>
       <c r="AE135" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AF135" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG135" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AH135" s="5">
         <v>1.101672</v>
@@ -10944,7 +10942,7 @@
         <v>50</v>
       </c>
       <c r="U136" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V136" s="5"/>
       <c r="W136" s="5"/>
@@ -11015,7 +11013,7 @@
         <v>50</v>
       </c>
       <c r="U137" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V137" s="5"/>
       <c r="W137" s="5"/>
@@ -11042,7 +11040,7 @@
         <v>43</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>44</v>
@@ -11084,7 +11082,7 @@
         <v>85</v>
       </c>
       <c r="U138" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V138" s="5"/>
       <c r="W138" s="5"/>
@@ -11096,13 +11094,13 @@
       <c r="AC138" s="5"/>
       <c r="AD138" s="5"/>
       <c r="AE138" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AF138" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG138" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AH138" s="5"/>
       <c r="AI138" s="5"/>
@@ -11123,7 +11121,7 @@
         <v>43</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>58</v>
@@ -11167,7 +11165,7 @@
         <v>50</v>
       </c>
       <c r="U139" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V139" s="5"/>
       <c r="W139" s="5"/>
@@ -11194,7 +11192,7 @@
         <v>43</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>59</v>
@@ -11238,7 +11236,7 @@
         <v>50</v>
       </c>
       <c r="U140" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V140" s="5"/>
       <c r="W140" s="5"/>
@@ -11265,7 +11263,7 @@
         <v>43</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>44</v>
@@ -11309,7 +11307,7 @@
         <v>85</v>
       </c>
       <c r="U141" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V141" s="5"/>
       <c r="W141" s="5"/>
@@ -11336,7 +11334,7 @@
         <v>43</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>58</v>
@@ -11380,7 +11378,7 @@
         <v>50</v>
       </c>
       <c r="U142" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V142" s="5"/>
       <c r="W142" s="5"/>
@@ -11407,7 +11405,7 @@
         <v>43</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>59</v>
@@ -11451,7 +11449,7 @@
         <v>50</v>
       </c>
       <c r="U143" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V143" s="5"/>
       <c r="W143" s="5"/>
@@ -11478,13 +11476,13 @@
         <v>43</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>79</v>
@@ -11520,7 +11518,7 @@
         <v>85</v>
       </c>
       <c r="U144" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V144" s="5"/>
       <c r="W144" s="5"/>
@@ -11532,13 +11530,13 @@
       <c r="AC144" s="5"/>
       <c r="AD144" s="5"/>
       <c r="AE144" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AF144" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG144" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AH144" s="5"/>
       <c r="AI144" s="5"/>
@@ -11559,13 +11557,13 @@
         <v>43</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>79</v>
@@ -11601,7 +11599,7 @@
         <v>85</v>
       </c>
       <c r="U145" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V145" s="5"/>
       <c r="W145" s="5"/>
@@ -11613,13 +11611,13 @@
       <c r="AC145" s="5"/>
       <c r="AD145" s="5"/>
       <c r="AE145" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AF145" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG145" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AH145" s="5"/>
       <c r="AI145" s="5"/>
@@ -11640,13 +11638,13 @@
         <v>43</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>79</v>
@@ -11684,7 +11682,7 @@
         <v>50</v>
       </c>
       <c r="U146" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V146" s="5"/>
       <c r="W146" s="5"/>
@@ -11711,13 +11709,13 @@
         <v>43</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>79</v>
@@ -11755,7 +11753,7 @@
         <v>50</v>
       </c>
       <c r="U147" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V147" s="5"/>
       <c r="W147" s="5"/>
@@ -11782,13 +11780,13 @@
         <v>43</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F148" s="5" t="s">
         <v>73</v>
@@ -11826,7 +11824,7 @@
         <v>50</v>
       </c>
       <c r="U148" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V148" s="5"/>
       <c r="W148" s="5"/>
@@ -11853,13 +11851,13 @@
         <v>43</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>79</v>
@@ -11897,7 +11895,7 @@
         <v>85</v>
       </c>
       <c r="U149" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V149" s="5"/>
       <c r="W149" s="5"/>
@@ -11924,13 +11922,13 @@
         <v>43</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>79</v>
@@ -11966,7 +11964,7 @@
         <v>85</v>
       </c>
       <c r="U150" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V150" s="5"/>
       <c r="W150" s="5"/>
@@ -11978,13 +11976,13 @@
       <c r="AC150" s="5"/>
       <c r="AD150" s="5"/>
       <c r="AE150" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AF150" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG150" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AH150" s="5">
         <v>1.4620299999999999</v>
@@ -12009,13 +12007,13 @@
         <v>43</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>79</v>
@@ -12051,7 +12049,7 @@
         <v>85</v>
       </c>
       <c r="U151" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V151" s="5"/>
       <c r="W151" s="5"/>
@@ -12063,13 +12061,13 @@
       <c r="AC151" s="5"/>
       <c r="AD151" s="5"/>
       <c r="AE151" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AF151" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG151" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AH151" s="5">
         <v>1.4620299999999999</v>
@@ -12094,13 +12092,13 @@
         <v>43</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>79</v>
@@ -12138,7 +12136,7 @@
         <v>50</v>
       </c>
       <c r="U152" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V152" s="5"/>
       <c r="W152" s="5"/>
@@ -12165,13 +12163,13 @@
         <v>43</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D153" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>79</v>
@@ -12209,7 +12207,7 @@
         <v>50</v>
       </c>
       <c r="U153" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V153" s="5"/>
       <c r="W153" s="5"/>
@@ -12236,13 +12234,13 @@
         <v>43</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>79</v>
@@ -12278,7 +12276,7 @@
         <v>85</v>
       </c>
       <c r="U154" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V154" s="5"/>
       <c r="W154" s="5"/>
@@ -12290,13 +12288,13 @@
       <c r="AC154" s="5"/>
       <c r="AD154" s="5"/>
       <c r="AE154" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AF154" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG154" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AH154" s="5"/>
       <c r="AI154" s="5"/>
@@ -12317,13 +12315,13 @@
         <v>43</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>79</v>
@@ -12359,7 +12357,7 @@
         <v>85</v>
       </c>
       <c r="U155" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V155" s="5"/>
       <c r="W155" s="5"/>
@@ -12371,13 +12369,13 @@
       <c r="AC155" s="5"/>
       <c r="AD155" s="5"/>
       <c r="AE155" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AF155" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG155" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AH155" s="5"/>
       <c r="AI155" s="5"/>
@@ -12398,13 +12396,13 @@
         <v>43</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>79</v>
@@ -12442,7 +12440,7 @@
         <v>50</v>
       </c>
       <c r="U156" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V156" s="5"/>
       <c r="W156" s="5"/>
@@ -12469,13 +12467,13 @@
         <v>43</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>79</v>
@@ -12513,7 +12511,7 @@
         <v>50</v>
       </c>
       <c r="U157" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V157" s="5"/>
       <c r="W157" s="5"/>
@@ -12540,13 +12538,13 @@
         <v>43</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D158" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>73</v>
@@ -12584,7 +12582,7 @@
         <v>50</v>
       </c>
       <c r="U158" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V158" s="5"/>
       <c r="W158" s="5"/>
@@ -12611,13 +12609,13 @@
         <v>43</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>73</v>
@@ -12655,7 +12653,7 @@
         <v>50</v>
       </c>
       <c r="U159" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V159" s="5"/>
       <c r="W159" s="5"/>
@@ -12682,13 +12680,13 @@
         <v>43</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D160" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F160" s="5" t="s">
         <v>79</v>
@@ -12726,7 +12724,7 @@
         <v>50</v>
       </c>
       <c r="U160" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V160" s="5"/>
       <c r="W160" s="5"/>
@@ -12753,13 +12751,13 @@
         <v>43</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D161" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>79</v>
@@ -12797,7 +12795,7 @@
         <v>50</v>
       </c>
       <c r="U161" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V161" s="5"/>
       <c r="W161" s="5"/>
@@ -12824,13 +12822,13 @@
         <v>43</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F162" s="5" t="s">
         <v>79</v>
@@ -12866,7 +12864,7 @@
         <v>85</v>
       </c>
       <c r="U162" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V162" s="5"/>
       <c r="W162" s="5"/>
@@ -12878,13 +12876,13 @@
       <c r="AC162" s="5"/>
       <c r="AD162" s="5"/>
       <c r="AE162" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AF162" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG162" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AH162" s="5"/>
       <c r="AI162" s="5"/>
@@ -12905,13 +12903,13 @@
         <v>43</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>79</v>
@@ -12947,7 +12945,7 @@
         <v>85</v>
       </c>
       <c r="U163" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V163" s="5"/>
       <c r="W163" s="5"/>
@@ -12959,13 +12957,13 @@
       <c r="AC163" s="5"/>
       <c r="AD163" s="5"/>
       <c r="AE163" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AF163" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG163" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AH163" s="5"/>
       <c r="AI163" s="5"/>
@@ -12986,13 +12984,13 @@
         <v>43</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D164" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F164" s="5" t="s">
         <v>79</v>
@@ -13030,7 +13028,7 @@
         <v>50</v>
       </c>
       <c r="U164" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V164" s="5"/>
       <c r="W164" s="5"/>
@@ -13057,13 +13055,13 @@
         <v>43</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>79</v>
@@ -13101,7 +13099,7 @@
         <v>50</v>
       </c>
       <c r="U165" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V165" s="5"/>
       <c r="W165" s="5"/>
@@ -13128,13 +13126,13 @@
         <v>43</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D166" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>79</v>
@@ -13172,7 +13170,7 @@
         <v>85</v>
       </c>
       <c r="U166" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V166" s="5"/>
       <c r="W166" s="5"/>
@@ -13199,13 +13197,13 @@
         <v>43</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D167" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>79</v>
@@ -13243,7 +13241,7 @@
         <v>85</v>
       </c>
       <c r="U167" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V167" s="5"/>
       <c r="W167" s="5"/>
@@ -13270,13 +13268,13 @@
         <v>43</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F168" s="5" t="s">
         <v>79</v>
@@ -13314,7 +13312,7 @@
         <v>50</v>
       </c>
       <c r="U168" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V168" s="5"/>
       <c r="W168" s="5"/>
@@ -13341,13 +13339,13 @@
         <v>43</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D169" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F169" s="5" t="s">
         <v>79</v>
@@ -13385,7 +13383,7 @@
         <v>50</v>
       </c>
       <c r="U169" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V169" s="5"/>
       <c r="W169" s="5"/>
@@ -13412,13 +13410,13 @@
         <v>43</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D170" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F170" s="5" t="s">
         <v>79</v>
@@ -13454,7 +13452,7 @@
         <v>85</v>
       </c>
       <c r="U170" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V170" s="5"/>
       <c r="W170" s="5"/>
@@ -13466,13 +13464,13 @@
       <c r="AC170" s="5"/>
       <c r="AD170" s="5"/>
       <c r="AE170" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AF170" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG170" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AH170" s="5"/>
       <c r="AI170" s="5"/>
@@ -13493,13 +13491,13 @@
         <v>43</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>79</v>
@@ -13535,7 +13533,7 @@
         <v>85</v>
       </c>
       <c r="U171" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V171" s="5"/>
       <c r="W171" s="5"/>
@@ -13547,13 +13545,13 @@
       <c r="AC171" s="5"/>
       <c r="AD171" s="5"/>
       <c r="AE171" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AF171" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG171" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AH171" s="5"/>
       <c r="AI171" s="5"/>
@@ -13574,13 +13572,13 @@
         <v>43</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D172" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F172" s="5" t="s">
         <v>79</v>
@@ -13618,7 +13616,7 @@
         <v>50</v>
       </c>
       <c r="U172" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V172" s="5"/>
       <c r="W172" s="5"/>
@@ -13645,13 +13643,13 @@
         <v>43</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D173" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>79</v>
@@ -13689,7 +13687,7 @@
         <v>85</v>
       </c>
       <c r="U173" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V173" s="5"/>
       <c r="W173" s="5"/>
@@ -13716,13 +13714,13 @@
         <v>43</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D174" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F174" s="5" t="s">
         <v>79</v>
@@ -13760,7 +13758,7 @@
         <v>50</v>
       </c>
       <c r="U174" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V174" s="5"/>
       <c r="W174" s="5"/>
@@ -13787,13 +13785,13 @@
         <v>43</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D175" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>79</v>
@@ -13829,7 +13827,7 @@
         <v>85</v>
       </c>
       <c r="U175" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V175" s="5"/>
       <c r="W175" s="5"/>
@@ -13841,13 +13839,13 @@
       <c r="AC175" s="5"/>
       <c r="AD175" s="5"/>
       <c r="AE175" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AF175" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG175" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AH175" s="5"/>
       <c r="AI175" s="5"/>
@@ -13868,13 +13866,13 @@
         <v>43</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D176" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>79</v>
@@ -13910,7 +13908,7 @@
         <v>85</v>
       </c>
       <c r="U176" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V176" s="5"/>
       <c r="W176" s="5"/>
@@ -13922,13 +13920,13 @@
       <c r="AC176" s="5"/>
       <c r="AD176" s="5"/>
       <c r="AE176" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AF176" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG176" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AH176" s="5"/>
       <c r="AI176" s="5"/>
@@ -13949,13 +13947,13 @@
         <v>43</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D177" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F177" s="5" t="s">
         <v>79</v>
@@ -13993,7 +13991,7 @@
         <v>50</v>
       </c>
       <c r="U177" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V177" s="5"/>
       <c r="W177" s="5"/>
@@ -14020,13 +14018,13 @@
         <v>43</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D178" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F178" s="5" t="s">
         <v>79</v>
@@ -14062,7 +14060,7 @@
         <v>85</v>
       </c>
       <c r="U178" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V178" s="5"/>
       <c r="W178" s="5"/>
@@ -14074,13 +14072,13 @@
       <c r="AC178" s="5"/>
       <c r="AD178" s="5"/>
       <c r="AE178" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AF178" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG178" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AH178" s="5"/>
       <c r="AI178" s="5"/>
@@ -14101,13 +14099,13 @@
         <v>43</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D179" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F179" s="5" t="s">
         <v>79</v>
@@ -14143,7 +14141,7 @@
         <v>85</v>
       </c>
       <c r="U179" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V179" s="5"/>
       <c r="W179" s="5"/>
@@ -14155,13 +14153,13 @@
       <c r="AC179" s="5"/>
       <c r="AD179" s="5"/>
       <c r="AE179" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AF179" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG179" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AH179" s="5"/>
       <c r="AI179" s="5"/>
@@ -14182,13 +14180,13 @@
         <v>43</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D180" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F180" s="5" t="s">
         <v>79</v>
@@ -14226,7 +14224,7 @@
         <v>50</v>
       </c>
       <c r="U180" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V180" s="5"/>
       <c r="W180" s="5"/>
@@ -14253,13 +14251,13 @@
         <v>43</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D181" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F181" s="5" t="s">
         <v>79</v>
@@ -14297,7 +14295,7 @@
         <v>50</v>
       </c>
       <c r="U181" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V181" s="5"/>
       <c r="W181" s="5"/>
@@ -14324,7 +14322,7 @@
         <v>43</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D182" s="5" t="s">
         <v>82</v>
@@ -14464,7 +14462,7 @@
         <v>43</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D184" s="5" t="s">
         <v>82</v>
@@ -15719,13 +15717,13 @@
         <v>43</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D201" s="5" t="s">
         <v>82</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F201" s="5" t="s">
         <v>79</v>
@@ -15755,13 +15753,13 @@
         <v>51</v>
       </c>
       <c r="S201" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="T201" s="5">
         <v>15</v>
       </c>
       <c r="U201" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V201" s="5"/>
       <c r="W201" s="5"/>
@@ -15794,7 +15792,7 @@
         <v>82</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F202" s="5"/>
       <c r="G202" s="5"/>
@@ -15815,7 +15813,7 @@
         <v>9</v>
       </c>
       <c r="P202" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q202" s="5">
         <v>1</v>
@@ -15824,13 +15822,13 @@
         <v>51</v>
       </c>
       <c r="S202" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T202" s="5">
         <v>15</v>
       </c>
       <c r="U202" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V202" s="5"/>
       <c r="W202" s="5"/>
@@ -15857,7 +15855,7 @@
         <v>43</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D203" s="5" t="s">
         <v>82</v>
@@ -15901,7 +15899,7 @@
         <v>50</v>
       </c>
       <c r="U203" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V203" s="5"/>
       <c r="W203" s="5"/>
@@ -15928,16 +15926,16 @@
         <v>43</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D204" s="5" t="s">
         <v>82</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G204" s="5"/>
       <c r="H204" s="5" t="s">
@@ -15972,7 +15970,7 @@
         <v>85</v>
       </c>
       <c r="U204" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V204" s="5"/>
       <c r="W204" s="5"/>
@@ -15999,7 +15997,7 @@
         <v>43</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D205" s="5" t="s">
         <v>82</v>
@@ -16041,7 +16039,7 @@
         <v>85</v>
       </c>
       <c r="U205" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V205" s="5"/>
       <c r="W205" s="5"/>
@@ -16053,13 +16051,13 @@
       <c r="AC205" s="5"/>
       <c r="AD205" s="5"/>
       <c r="AE205" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AF205" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG205" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="AF205" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="AG205" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="AH205" s="5"/>
       <c r="AI205" s="5"/>
@@ -16074,7 +16072,7 @@
         <v>43</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D206" s="5" t="s">
         <v>82</v>
@@ -16116,7 +16114,7 @@
         <v>85</v>
       </c>
       <c r="U206" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V206" s="5"/>
       <c r="W206" s="5"/>
@@ -16128,13 +16126,13 @@
       <c r="AC206" s="5"/>
       <c r="AD206" s="5"/>
       <c r="AE206" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AF206" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG206" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AH206" s="5"/>
       <c r="AI206" s="5"/>
@@ -16149,7 +16147,7 @@
         <v>43</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D207" s="5" t="s">
         <v>82</v>
@@ -16220,13 +16218,13 @@
         <v>43</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D208" s="5" t="s">
         <v>82</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F208" s="5" t="s">
         <v>79</v>
@@ -16291,13 +16289,13 @@
         <v>43</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D209" s="5" t="s">
         <v>82</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F209" s="5"/>
       <c r="G209" s="5"/>
@@ -16360,13 +16358,13 @@
         <v>43</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D210" s="5" t="s">
         <v>82</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F210" s="5"/>
       <c r="G210" s="5"/>
@@ -16429,13 +16427,13 @@
         <v>43</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D211" s="5" t="s">
         <v>82</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F211" s="5"/>
       <c r="G211" s="5"/>
@@ -16498,13 +16496,13 @@
         <v>43</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D212" s="5" t="s">
         <v>82</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F212" s="5"/>
       <c r="G212" s="5"/>
@@ -16567,13 +16565,13 @@
         <v>43</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D213" s="5" t="s">
         <v>82</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F213" s="5" t="s">
         <v>79</v>
@@ -16611,7 +16609,7 @@
         <v>85</v>
       </c>
       <c r="U213" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V213" s="5"/>
       <c r="W213" s="5"/>
@@ -16638,13 +16636,13 @@
         <v>43</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D214" s="5" t="s">
         <v>82</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F214" s="5" t="s">
         <v>79</v>
@@ -16682,7 +16680,7 @@
         <v>50</v>
       </c>
       <c r="U214" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V214" s="5"/>
       <c r="W214" s="5"/>
@@ -16709,7 +16707,7 @@
         <v>43</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D215" s="5" t="s">
         <v>44</v>
@@ -16780,13 +16778,13 @@
         <v>43</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D216" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F216" s="5" t="s">
         <v>79</v>
@@ -16851,13 +16849,13 @@
         <v>43</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D217" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F217" s="5"/>
       <c r="G217" s="5"/>
@@ -16920,13 +16918,13 @@
         <v>43</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D218" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F218" s="5"/>
       <c r="G218" s="5"/>
@@ -16989,13 +16987,13 @@
         <v>43</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D219" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F219" s="5"/>
       <c r="G219" s="5"/>
@@ -17058,13 +17056,13 @@
         <v>43</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D220" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F220" s="5"/>
       <c r="G220" s="5"/>
@@ -17127,13 +17125,13 @@
         <v>43</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D221" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F221" s="5" t="s">
         <v>79</v>
@@ -17171,7 +17169,7 @@
         <v>85</v>
       </c>
       <c r="U221" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V221" s="5"/>
       <c r="W221" s="5"/>
@@ -17198,13 +17196,13 @@
         <v>43</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D222" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F222" s="5" t="s">
         <v>79</v>
@@ -17242,7 +17240,7 @@
         <v>50</v>
       </c>
       <c r="U222" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V222" s="5"/>
       <c r="W222" s="5"/>
@@ -17269,7 +17267,7 @@
         <v>43</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D223" s="5" t="s">
         <v>55</v>
@@ -17340,13 +17338,13 @@
         <v>43</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D224" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F224" s="5" t="s">
         <v>79</v>
@@ -17411,13 +17409,13 @@
         <v>43</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D225" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F225" s="5"/>
       <c r="G225" s="5"/>
@@ -17480,13 +17478,13 @@
         <v>43</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D226" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F226" s="5"/>
       <c r="G226" s="5"/>
@@ -17549,13 +17547,13 @@
         <v>43</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D227" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F227" s="5"/>
       <c r="G227" s="5"/>
@@ -17618,13 +17616,13 @@
         <v>43</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D228" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F228" s="5"/>
       <c r="G228" s="5"/>
@@ -17687,13 +17685,13 @@
         <v>43</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D229" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F229" s="5" t="s">
         <v>79</v>
@@ -17731,7 +17729,7 @@
         <v>85</v>
       </c>
       <c r="U229" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V229" s="5"/>
       <c r="W229" s="5"/>
@@ -17758,13 +17756,13 @@
         <v>43</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D230" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F230" s="5" t="s">
         <v>79</v>
@@ -17802,7 +17800,7 @@
         <v>50</v>
       </c>
       <c r="U230" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V230" s="5"/>
       <c r="W230" s="5"/>
@@ -17829,13 +17827,13 @@
         <v>43</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D231" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F231" s="5"/>
       <c r="G231" s="5"/>
@@ -17898,13 +17896,13 @@
         <v>43</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D232" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F232" s="5"/>
       <c r="G232" s="5"/>
@@ -17967,13 +17965,13 @@
         <v>43</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D233" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F233" s="5"/>
       <c r="G233" s="5"/>
@@ -18036,13 +18034,13 @@
         <v>43</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D234" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F234" s="5"/>
       <c r="G234" s="5"/>
@@ -18105,13 +18103,13 @@
         <v>43</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D235" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F235" s="5" t="s">
         <v>79</v>
@@ -18149,7 +18147,7 @@
         <v>85</v>
       </c>
       <c r="U235" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V235" s="5"/>
       <c r="W235" s="5"/>
@@ -18257,7 +18255,7 @@
         <v>43</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D237" s="5" t="s">
         <v>54</v>
@@ -18338,7 +18336,7 @@
         <v>43</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D238" s="5" t="s">
         <v>54</v>
@@ -18409,13 +18407,13 @@
         <v>43</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D239" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F239" s="5"/>
       <c r="G239" s="5"/>
@@ -18461,13 +18459,13 @@
       <c r="AC239" s="5"/>
       <c r="AD239" s="5"/>
       <c r="AE239" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AF239" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG239" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AH239" s="5"/>
       <c r="AI239" s="5"/>
@@ -18488,13 +18486,13 @@
         <v>43</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D240" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F240" s="5"/>
       <c r="G240" s="5"/>
@@ -18540,13 +18538,13 @@
       <c r="AC240" s="5"/>
       <c r="AD240" s="5"/>
       <c r="AE240" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AF240" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG240" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AH240" s="5"/>
       <c r="AI240" s="5"/>
@@ -18609,7 +18607,7 @@
         <v>50</v>
       </c>
       <c r="U241" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V241" s="5"/>
       <c r="W241" s="5"/>
@@ -18621,13 +18619,13 @@
       <c r="AC241" s="5"/>
       <c r="AD241" s="5"/>
       <c r="AE241" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AF241" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AG241" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AH241" s="5"/>
       <c r="AI241" s="5"/>
@@ -18650,13 +18648,13 @@
         <v>43</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D242" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E242" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F242" s="5" t="s">
         <v>79</v>
@@ -18694,7 +18692,7 @@
         <v>85</v>
       </c>
       <c r="U242" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V242" s="5"/>
       <c r="W242" s="5"/>
@@ -18721,13 +18719,13 @@
         <v>43</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D243" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F243" s="5" t="s">
         <v>79</v>
@@ -18765,7 +18763,7 @@
         <v>85</v>
       </c>
       <c r="U243" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V243" s="5"/>
       <c r="W243" s="5"/>
@@ -18834,7 +18832,7 @@
         <v>85</v>
       </c>
       <c r="U244" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V244" s="5"/>
       <c r="W244" s="5"/>
@@ -18846,13 +18844,13 @@
       <c r="AC244" s="5"/>
       <c r="AD244" s="5"/>
       <c r="AE244" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AF244" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG244" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AH244" s="5">
         <v>1.101672</v>
@@ -18877,7 +18875,7 @@
         <v>43</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D245" s="5" t="s">
         <v>54</v>
@@ -18919,7 +18917,7 @@
         <v>85</v>
       </c>
       <c r="U245" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V245" s="5"/>
       <c r="W245" s="5"/>
@@ -18931,13 +18929,13 @@
       <c r="AC245" s="5"/>
       <c r="AD245" s="5"/>
       <c r="AE245" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AF245" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG245" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AH245" s="5"/>
       <c r="AI245" s="5"/>
@@ -18958,7 +18956,7 @@
         <v>43</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D246" s="5" t="s">
         <v>54</v>
@@ -19002,7 +19000,7 @@
         <v>85</v>
       </c>
       <c r="U246" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V246" s="5"/>
       <c r="W246" s="5"/>
@@ -19029,13 +19027,13 @@
         <v>43</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D247" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E247" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F247" s="5" t="s">
         <v>79</v>
@@ -19071,7 +19069,7 @@
         <v>85</v>
       </c>
       <c r="U247" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V247" s="5"/>
       <c r="W247" s="5"/>
@@ -19083,13 +19081,13 @@
       <c r="AC247" s="5"/>
       <c r="AD247" s="5"/>
       <c r="AE247" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AF247" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG247" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AH247" s="5"/>
       <c r="AI247" s="5"/>
@@ -19110,13 +19108,13 @@
         <v>43</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D248" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F248" s="5" t="s">
         <v>79</v>
@@ -19152,7 +19150,7 @@
         <v>85</v>
       </c>
       <c r="U248" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V248" s="5"/>
       <c r="W248" s="5"/>
@@ -19164,13 +19162,13 @@
       <c r="AC248" s="5"/>
       <c r="AD248" s="5"/>
       <c r="AE248" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AF248" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG248" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AH248" s="5"/>
       <c r="AI248" s="5"/>
@@ -19191,13 +19189,13 @@
         <v>43</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D249" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F249" s="5" t="s">
         <v>73</v>
@@ -19235,7 +19233,7 @@
         <v>50</v>
       </c>
       <c r="U249" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V249" s="5"/>
       <c r="W249" s="5"/>
@@ -19262,13 +19260,13 @@
         <v>43</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D250" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F250" s="5" t="s">
         <v>79</v>
@@ -19304,7 +19302,7 @@
         <v>85</v>
       </c>
       <c r="U250" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V250" s="5"/>
       <c r="W250" s="5"/>
@@ -19316,13 +19314,13 @@
       <c r="AC250" s="5"/>
       <c r="AD250" s="5"/>
       <c r="AE250" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AF250" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG250" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AH250" s="5">
         <v>1.4620299999999999</v>
@@ -19347,13 +19345,13 @@
         <v>43</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D251" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F251" s="5" t="s">
         <v>79</v>
@@ -19389,7 +19387,7 @@
         <v>85</v>
       </c>
       <c r="U251" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V251" s="5"/>
       <c r="W251" s="5"/>
@@ -19401,13 +19399,13 @@
       <c r="AC251" s="5"/>
       <c r="AD251" s="5"/>
       <c r="AE251" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AF251" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG251" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AH251" s="5">
         <v>1.4620299999999999</v>
@@ -19432,13 +19430,13 @@
         <v>43</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D252" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E252" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F252" s="5" t="s">
         <v>79</v>
@@ -19474,7 +19472,7 @@
         <v>85</v>
       </c>
       <c r="U252" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V252" s="5"/>
       <c r="W252" s="5"/>
@@ -19486,13 +19484,13 @@
       <c r="AC252" s="5"/>
       <c r="AD252" s="5"/>
       <c r="AE252" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AF252" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG252" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AH252" s="5"/>
       <c r="AI252" s="5"/>
@@ -19513,13 +19511,13 @@
         <v>43</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D253" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F253" s="5" t="s">
         <v>79</v>
@@ -19555,7 +19553,7 @@
         <v>85</v>
       </c>
       <c r="U253" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V253" s="5"/>
       <c r="W253" s="5"/>
@@ -19567,13 +19565,13 @@
       <c r="AC253" s="5"/>
       <c r="AD253" s="5"/>
       <c r="AE253" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AF253" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG253" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AH253" s="5"/>
       <c r="AI253" s="5"/>
@@ -19594,13 +19592,13 @@
         <v>43</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D254" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E254" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F254" s="5" t="s">
         <v>73</v>
@@ -19638,7 +19636,7 @@
         <v>50</v>
       </c>
       <c r="U254" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V254" s="5"/>
       <c r="W254" s="5"/>
@@ -19665,13 +19663,13 @@
         <v>43</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D255" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F255" s="5" t="s">
         <v>79</v>
@@ -19707,7 +19705,7 @@
         <v>85</v>
       </c>
       <c r="U255" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V255" s="5"/>
       <c r="W255" s="5"/>
@@ -19719,13 +19717,13 @@
       <c r="AC255" s="5"/>
       <c r="AD255" s="5"/>
       <c r="AE255" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AF255" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG255" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AH255" s="5"/>
       <c r="AI255" s="5"/>
@@ -19746,13 +19744,13 @@
         <v>43</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D256" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F256" s="5" t="s">
         <v>79</v>
@@ -19788,7 +19786,7 @@
         <v>85</v>
       </c>
       <c r="U256" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V256" s="5"/>
       <c r="W256" s="5"/>
@@ -19800,13 +19798,13 @@
       <c r="AC256" s="5"/>
       <c r="AD256" s="5"/>
       <c r="AE256" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AF256" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG256" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AH256" s="5"/>
       <c r="AI256" s="5"/>
@@ -19827,13 +19825,13 @@
         <v>43</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D257" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F257" s="5" t="s">
         <v>79</v>
@@ -19871,7 +19869,7 @@
         <v>85</v>
       </c>
       <c r="U257" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V257" s="5"/>
       <c r="W257" s="5"/>
@@ -19898,13 +19896,13 @@
         <v>43</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D258" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E258" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F258" s="5" t="s">
         <v>79</v>
@@ -19942,7 +19940,7 @@
         <v>85</v>
       </c>
       <c r="U258" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V258" s="5"/>
       <c r="W258" s="5"/>
@@ -19969,13 +19967,13 @@
         <v>43</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D259" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E259" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F259" s="5" t="s">
         <v>79</v>
@@ -20011,7 +20009,7 @@
         <v>85</v>
       </c>
       <c r="U259" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V259" s="5"/>
       <c r="W259" s="5"/>
@@ -20023,13 +20021,13 @@
       <c r="AC259" s="5"/>
       <c r="AD259" s="5"/>
       <c r="AE259" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AF259" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG259" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AH259" s="5"/>
       <c r="AI259" s="5"/>
@@ -20050,13 +20048,13 @@
         <v>43</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D260" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E260" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F260" s="5" t="s">
         <v>79</v>
@@ -20092,7 +20090,7 @@
         <v>85</v>
       </c>
       <c r="U260" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V260" s="5"/>
       <c r="W260" s="5"/>
@@ -20104,13 +20102,13 @@
       <c r="AC260" s="5"/>
       <c r="AD260" s="5"/>
       <c r="AE260" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AF260" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG260" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AH260" s="5"/>
       <c r="AI260" s="5"/>
@@ -20131,13 +20129,13 @@
         <v>43</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D261" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E261" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F261" s="5" t="s">
         <v>79</v>
@@ -20175,7 +20173,7 @@
         <v>85</v>
       </c>
       <c r="U261" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V261" s="5"/>
       <c r="W261" s="5"/>
@@ -20202,13 +20200,13 @@
         <v>43</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D262" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E262" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F262" s="5" t="s">
         <v>79</v>
@@ -20244,7 +20242,7 @@
         <v>85</v>
       </c>
       <c r="U262" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V262" s="5"/>
       <c r="W262" s="5"/>
@@ -20256,13 +20254,13 @@
       <c r="AC262" s="5"/>
       <c r="AD262" s="5"/>
       <c r="AE262" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AF262" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG262" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AH262" s="5"/>
       <c r="AI262" s="5"/>
@@ -20283,13 +20281,13 @@
         <v>43</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D263" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E263" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F263" s="5" t="s">
         <v>79</v>
@@ -20325,7 +20323,7 @@
         <v>85</v>
       </c>
       <c r="U263" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V263" s="5"/>
       <c r="W263" s="5"/>
@@ -20337,13 +20335,13 @@
       <c r="AC263" s="5"/>
       <c r="AD263" s="5"/>
       <c r="AE263" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AF263" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG263" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AH263" s="5"/>
       <c r="AI263" s="5"/>
@@ -20364,13 +20362,13 @@
         <v>43</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D264" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E264" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F264" s="5" t="s">
         <v>79</v>
@@ -20406,7 +20404,7 @@
         <v>85</v>
       </c>
       <c r="U264" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V264" s="5"/>
       <c r="W264" s="5"/>
@@ -20418,13 +20416,13 @@
       <c r="AC264" s="5"/>
       <c r="AD264" s="5"/>
       <c r="AE264" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AF264" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG264" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AH264" s="5"/>
       <c r="AI264" s="5"/>
@@ -20445,13 +20443,13 @@
         <v>43</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D265" s="5" t="s">
         <v>54</v>
       </c>
       <c r="E265" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F265" s="5" t="s">
         <v>79</v>
@@ -20487,7 +20485,7 @@
         <v>85</v>
       </c>
       <c r="U265" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="V265" s="5"/>
       <c r="W265" s="5"/>
@@ -20499,13 +20497,13 @@
       <c r="AC265" s="5"/>
       <c r="AD265" s="5"/>
       <c r="AE265" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AF265" s="5" t="s">
         <v>76</v>
       </c>
       <c r="AG265" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AH265" s="5"/>
       <c r="AI265" s="5"/>

--- a/inst/extdata/colorado_criteria_crosswalk.xlsx
+++ b/inst/extdata/colorado_criteria_crosswalk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/sheila_saia_tetratech_com/Documents/Documents/github/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{CD77611A-A625-4F3B-80D2-923462D5119F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{133DE8DF-8112-48B4-8C1B-81FDB88B3B08}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{CD77611A-A625-4F3B-80D2-923462D5119F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FDA45C8-46DF-45DA-9BDF-43F283F3B38C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{380839A1-A469-4C26-93CF-5FD0D1BCA51C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3365" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3492" uniqueCount="217">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -305,9 +305,6 @@
     <t>NumberNotMeeting</t>
   </si>
   <si>
-    <t>June-Sept</t>
-  </si>
-  <si>
     <t>Tier I Rivers</t>
   </si>
   <si>
@@ -407,9 +404,6 @@
     <t>Percentile</t>
   </si>
   <si>
-    <t>Spawning season</t>
-  </si>
-  <si>
     <t>PH</t>
   </si>
   <si>
@@ -651,6 +645,48 @@
   </si>
   <si>
     <t>min(87, e^(1.3695*In(hardness)-0.1158))</t>
+  </si>
+  <si>
+    <t>Jun 1</t>
+  </si>
+  <si>
+    <t>Oct 1</t>
+  </si>
+  <si>
+    <t>Nov 1</t>
+  </si>
+  <si>
+    <t>Jan 1</t>
+  </si>
+  <si>
+    <t>Sep 31</t>
+  </si>
+  <si>
+    <t>May 31</t>
+  </si>
+  <si>
+    <t>Oct 31</t>
+  </si>
+  <si>
+    <t>Mar 31</t>
+  </si>
+  <si>
+    <t>Dec 31</t>
+  </si>
+  <si>
+    <t>June-Sep</t>
+  </si>
+  <si>
+    <t>Mar 1</t>
+  </si>
+  <si>
+    <t>Dec 1</t>
+  </si>
+  <si>
+    <t>Nov 30</t>
+  </si>
+  <si>
+    <t>Feb 28</t>
   </si>
 </sst>
 </file>
@@ -705,7 +741,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -720,6 +756,12 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1201,7 +1243,7 @@
         <v>42</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>43</v>
@@ -1271,7 +1313,7 @@
         <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>53</v>
@@ -1341,7 +1383,7 @@
         <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>54</v>
@@ -1819,7 +1861,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>57</v>
@@ -1887,7 +1929,7 @@
         <v>42</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>58</v>
@@ -1955,7 +1997,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>57</v>
@@ -2023,7 +2065,7 @@
         <v>42</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>58</v>
@@ -2091,7 +2133,7 @@
         <v>42</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>43</v>
@@ -2175,7 +2217,7 @@
         <v>42</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>53</v>
@@ -2259,7 +2301,7 @@
         <v>42</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>54</v>
@@ -2753,7 +2795,7 @@
         <v>42</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>43</v>
@@ -2831,7 +2873,7 @@
         <v>42</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>43</v>
@@ -2920,7 +2962,7 @@
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>48</v>
@@ -2951,10 +2993,14 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z25" s="4"/>
-      <c r="AA25" s="4"/>
+        <v>192</v>
+      </c>
+      <c r="Z25" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA25" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="AB25" s="3"/>
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
@@ -2992,7 +3038,7 @@
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>48</v>
@@ -3023,10 +3069,14 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z26" s="4"/>
-      <c r="AA26" s="4"/>
+        <v>90</v>
+      </c>
+      <c r="Z26" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="AA26" s="4" t="s">
+        <v>208</v>
+      </c>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
@@ -3064,7 +3114,7 @@
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>48</v>
@@ -3095,10 +3145,14 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z27" s="4"/>
-      <c r="AA27" s="4"/>
+        <v>91</v>
+      </c>
+      <c r="Z27" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA27" s="4" t="s">
+        <v>209</v>
+      </c>
       <c r="AB27" s="3"/>
       <c r="AC27" s="3"/>
       <c r="AD27" s="3"/>
@@ -3136,7 +3190,7 @@
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>48</v>
@@ -3167,10 +3221,14 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z28" s="4"/>
-      <c r="AA28" s="4"/>
+        <v>93</v>
+      </c>
+      <c r="Z28" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="AA28" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
       <c r="AD28" s="3"/>
@@ -3208,7 +3266,7 @@
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>48</v>
@@ -3239,10 +3297,14 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z29" s="4"/>
-      <c r="AA29" s="4"/>
+        <v>94</v>
+      </c>
+      <c r="Z29" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA29" s="4" t="s">
+        <v>211</v>
+      </c>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
@@ -3280,7 +3342,7 @@
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>48</v>
@@ -3311,10 +3373,14 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z30" s="4"/>
-      <c r="AA30" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="Z30" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA30" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="AB30" s="3"/>
       <c r="AC30" s="3"/>
       <c r="AD30" s="3"/>
@@ -3352,7 +3418,7 @@
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>48</v>
@@ -3383,10 +3449,14 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z31" s="4"/>
-      <c r="AA31" s="4"/>
+        <v>94</v>
+      </c>
+      <c r="Z31" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA31" s="4" t="s">
+        <v>211</v>
+      </c>
       <c r="AB31" s="3"/>
       <c r="AC31" s="3"/>
       <c r="AD31" s="3"/>
@@ -3424,7 +3494,7 @@
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>48</v>
@@ -3455,10 +3525,14 @@
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z32" s="4"/>
-      <c r="AA32" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="Z32" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA32" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="AB32" s="3"/>
       <c r="AC32" s="3"/>
       <c r="AD32" s="3"/>
@@ -3496,7 +3570,7 @@
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>48</v>
@@ -3527,10 +3601,14 @@
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z33" s="4"/>
-      <c r="AA33" s="4"/>
+        <v>98</v>
+      </c>
+      <c r="Z33" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="AA33" s="4" t="s">
+        <v>215</v>
+      </c>
       <c r="AB33" s="3"/>
       <c r="AC33" s="3"/>
       <c r="AD33" s="3"/>
@@ -3568,7 +3646,7 @@
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M34" s="3" t="s">
         <v>48</v>
@@ -3599,10 +3677,14 @@
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z34" s="4"/>
-      <c r="AA34" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="Z34" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA34" s="4" t="s">
+        <v>216</v>
+      </c>
       <c r="AB34" s="3"/>
       <c r="AC34" s="3"/>
       <c r="AD34" s="3"/>
@@ -3640,7 +3722,7 @@
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>48</v>
@@ -3671,10 +3753,14 @@
       <c r="W35" s="3"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z35" s="4"/>
-      <c r="AA35" s="4"/>
+        <v>98</v>
+      </c>
+      <c r="Z35" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="AA35" s="4" t="s">
+        <v>215</v>
+      </c>
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
       <c r="AD35" s="3"/>
@@ -3712,7 +3798,7 @@
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M36" s="3" t="s">
         <v>48</v>
@@ -3743,10 +3829,14 @@
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z36" s="4"/>
-      <c r="AA36" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="Z36" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA36" s="4" t="s">
+        <v>216</v>
+      </c>
       <c r="AB36" s="3"/>
       <c r="AC36" s="3"/>
       <c r="AD36" s="3"/>
@@ -3784,7 +3874,7 @@
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M37" s="3" t="s">
         <v>48</v>
@@ -3815,10 +3905,14 @@
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z37" s="4"/>
-      <c r="AA37" s="4"/>
+        <v>98</v>
+      </c>
+      <c r="Z37" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="AA37" s="4" t="s">
+        <v>215</v>
+      </c>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
       <c r="AD37" s="3"/>
@@ -3856,7 +3950,7 @@
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M38" s="3" t="s">
         <v>48</v>
@@ -3887,10 +3981,14 @@
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z38" s="4"/>
-      <c r="AA38" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="Z38" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA38" s="4" t="s">
+        <v>216</v>
+      </c>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
       <c r="AD38" s="3"/>
@@ -3928,7 +4026,7 @@
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>48</v>
@@ -3959,10 +4057,14 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z39" s="4"/>
-      <c r="AA39" s="4"/>
+        <v>94</v>
+      </c>
+      <c r="Z39" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA39" s="4" t="s">
+        <v>211</v>
+      </c>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
@@ -4000,7 +4102,7 @@
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>48</v>
@@ -4031,10 +4133,14 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z40" s="4"/>
-      <c r="AA40" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="Z40" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA40" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
@@ -4072,7 +4178,7 @@
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>48</v>
@@ -4103,10 +4209,14 @@
       <c r="W41" s="3"/>
       <c r="X41" s="3"/>
       <c r="Y41" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z41" s="4"/>
-      <c r="AA41" s="4"/>
+        <v>192</v>
+      </c>
+      <c r="Z41" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA41" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="AB41" s="3"/>
       <c r="AC41" s="3"/>
       <c r="AD41" s="3"/>
@@ -4144,7 +4254,7 @@
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>48</v>
@@ -4175,10 +4285,14 @@
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
       <c r="Y42" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z42" s="4"/>
-      <c r="AA42" s="4"/>
+        <v>90</v>
+      </c>
+      <c r="Z42" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="AA42" s="4" t="s">
+        <v>208</v>
+      </c>
       <c r="AB42" s="3"/>
       <c r="AC42" s="3"/>
       <c r="AD42" s="3"/>
@@ -4216,7 +4330,7 @@
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>48</v>
@@ -4247,10 +4361,14 @@
       <c r="W43" s="3"/>
       <c r="X43" s="3"/>
       <c r="Y43" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z43" s="4"/>
-      <c r="AA43" s="4"/>
+        <v>91</v>
+      </c>
+      <c r="Z43" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA43" s="4" t="s">
+        <v>209</v>
+      </c>
       <c r="AB43" s="3"/>
       <c r="AC43" s="3"/>
       <c r="AD43" s="3"/>
@@ -4288,7 +4406,7 @@
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>48</v>
@@ -4319,10 +4437,14 @@
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
       <c r="Y44" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z44" s="4"/>
-      <c r="AA44" s="4"/>
+        <v>93</v>
+      </c>
+      <c r="Z44" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="AA44" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="AB44" s="3"/>
       <c r="AC44" s="3"/>
       <c r="AD44" s="3"/>
@@ -4360,7 +4482,7 @@
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>48</v>
@@ -4391,10 +4513,14 @@
       <c r="W45" s="3"/>
       <c r="X45" s="3"/>
       <c r="Y45" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z45" s="4"/>
-      <c r="AA45" s="4"/>
+        <v>94</v>
+      </c>
+      <c r="Z45" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA45" s="4" t="s">
+        <v>211</v>
+      </c>
       <c r="AB45" s="3"/>
       <c r="AC45" s="3"/>
       <c r="AD45" s="3"/>
@@ -4432,7 +4558,7 @@
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>48</v>
@@ -4463,10 +4589,14 @@
       <c r="W46" s="3"/>
       <c r="X46" s="3"/>
       <c r="Y46" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z46" s="4"/>
-      <c r="AA46" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="Z46" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA46" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="AB46" s="3"/>
       <c r="AC46" s="3"/>
       <c r="AD46" s="3"/>
@@ -4504,7 +4634,7 @@
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>48</v>
@@ -4535,10 +4665,14 @@
       <c r="W47" s="3"/>
       <c r="X47" s="3"/>
       <c r="Y47" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z47" s="4"/>
-      <c r="AA47" s="4"/>
+        <v>94</v>
+      </c>
+      <c r="Z47" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA47" s="4" t="s">
+        <v>211</v>
+      </c>
       <c r="AB47" s="3"/>
       <c r="AC47" s="3"/>
       <c r="AD47" s="3"/>
@@ -4576,7 +4710,7 @@
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>48</v>
@@ -4607,10 +4741,14 @@
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
       <c r="Y48" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z48" s="4"/>
-      <c r="AA48" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="Z48" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA48" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="AB48" s="3"/>
       <c r="AC48" s="3"/>
       <c r="AD48" s="3"/>
@@ -4648,7 +4786,7 @@
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>48</v>
@@ -4667,7 +4805,7 @@
         <v>50</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T49" s="3">
         <v>1</v>
@@ -4679,10 +4817,14 @@
       <c r="W49" s="3"/>
       <c r="X49" s="3"/>
       <c r="Y49" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z49" s="4"/>
-      <c r="AA49" s="4"/>
+        <v>192</v>
+      </c>
+      <c r="Z49" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA49" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="AB49" s="3"/>
       <c r="AC49" s="3"/>
       <c r="AD49" s="3"/>
@@ -4720,7 +4862,7 @@
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M50" s="3" t="s">
         <v>48</v>
@@ -4739,7 +4881,7 @@
         <v>50</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T50" s="3">
         <v>1</v>
@@ -4751,10 +4893,14 @@
       <c r="W50" s="3"/>
       <c r="X50" s="3"/>
       <c r="Y50" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z50" s="4"/>
-      <c r="AA50" s="4"/>
+        <v>90</v>
+      </c>
+      <c r="Z50" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="AA50" s="4" t="s">
+        <v>208</v>
+      </c>
       <c r="AB50" s="3"/>
       <c r="AC50" s="3"/>
       <c r="AD50" s="3"/>
@@ -4792,7 +4938,7 @@
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M51" s="3" t="s">
         <v>48</v>
@@ -4811,7 +4957,7 @@
         <v>50</v>
       </c>
       <c r="S51" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T51" s="3">
         <v>1</v>
@@ -4823,10 +4969,14 @@
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
       <c r="Y51" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z51" s="4"/>
-      <c r="AA51" s="4"/>
+        <v>91</v>
+      </c>
+      <c r="Z51" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA51" s="4" t="s">
+        <v>209</v>
+      </c>
       <c r="AB51" s="3"/>
       <c r="AC51" s="3"/>
       <c r="AD51" s="3"/>
@@ -4864,7 +5014,7 @@
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>48</v>
@@ -4883,7 +5033,7 @@
         <v>50</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T52" s="3">
         <v>1</v>
@@ -4895,10 +5045,14 @@
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
       <c r="Y52" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z52" s="4"/>
-      <c r="AA52" s="4"/>
+        <v>93</v>
+      </c>
+      <c r="Z52" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="AA52" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="AB52" s="3"/>
       <c r="AC52" s="3"/>
       <c r="AD52" s="3"/>
@@ -4936,7 +5090,7 @@
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M53" s="3" t="s">
         <v>48</v>
@@ -4955,7 +5109,7 @@
         <v>50</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T53" s="3">
         <v>1</v>
@@ -4967,10 +5121,14 @@
       <c r="W53" s="3"/>
       <c r="X53" s="3"/>
       <c r="Y53" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z53" s="4"/>
-      <c r="AA53" s="4"/>
+        <v>94</v>
+      </c>
+      <c r="Z53" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA53" s="4" t="s">
+        <v>211</v>
+      </c>
       <c r="AB53" s="3"/>
       <c r="AC53" s="3"/>
       <c r="AD53" s="3"/>
@@ -5008,7 +5166,7 @@
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M54" s="3" t="s">
         <v>48</v>
@@ -5027,7 +5185,7 @@
         <v>50</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T54" s="3">
         <v>1</v>
@@ -5039,10 +5197,14 @@
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
       <c r="Y54" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z54" s="4"/>
-      <c r="AA54" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="Z54" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA54" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="AB54" s="3"/>
       <c r="AC54" s="3"/>
       <c r="AD54" s="3"/>
@@ -5080,7 +5242,7 @@
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M55" s="3" t="s">
         <v>48</v>
@@ -5099,7 +5261,7 @@
         <v>50</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T55" s="3">
         <v>1</v>
@@ -5111,10 +5273,14 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z55" s="4"/>
-      <c r="AA55" s="4"/>
+        <v>94</v>
+      </c>
+      <c r="Z55" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA55" s="4" t="s">
+        <v>211</v>
+      </c>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
@@ -5152,7 +5318,7 @@
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M56" s="3" t="s">
         <v>48</v>
@@ -5171,7 +5337,7 @@
         <v>50</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T56" s="3">
         <v>1</v>
@@ -5183,10 +5349,14 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z56" s="4"/>
-      <c r="AA56" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="Z56" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA56" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
@@ -5224,7 +5394,7 @@
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>48</v>
@@ -5243,7 +5413,7 @@
         <v>50</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T57" s="3">
         <v>1</v>
@@ -5255,10 +5425,14 @@
       <c r="W57" s="3"/>
       <c r="X57" s="3"/>
       <c r="Y57" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z57" s="4"/>
-      <c r="AA57" s="4"/>
+        <v>98</v>
+      </c>
+      <c r="Z57" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="AA57" s="4" t="s">
+        <v>215</v>
+      </c>
       <c r="AB57" s="3"/>
       <c r="AC57" s="3"/>
       <c r="AD57" s="3"/>
@@ -5296,7 +5470,7 @@
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>48</v>
@@ -5315,7 +5489,7 @@
         <v>50</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T58" s="3">
         <v>1</v>
@@ -5327,10 +5501,14 @@
       <c r="W58" s="3"/>
       <c r="X58" s="3"/>
       <c r="Y58" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z58" s="4"/>
-      <c r="AA58" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="Z58" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA58" s="4" t="s">
+        <v>216</v>
+      </c>
       <c r="AB58" s="3"/>
       <c r="AC58" s="3"/>
       <c r="AD58" s="3"/>
@@ -5368,7 +5546,7 @@
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>48</v>
@@ -5387,7 +5565,7 @@
         <v>50</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T59" s="3">
         <v>1</v>
@@ -5399,10 +5577,14 @@
       <c r="W59" s="3"/>
       <c r="X59" s="3"/>
       <c r="Y59" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z59" s="4"/>
-      <c r="AA59" s="4"/>
+        <v>98</v>
+      </c>
+      <c r="Z59" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="AA59" s="4" t="s">
+        <v>215</v>
+      </c>
       <c r="AB59" s="3"/>
       <c r="AC59" s="3"/>
       <c r="AD59" s="3"/>
@@ -5440,7 +5622,7 @@
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>48</v>
@@ -5459,7 +5641,7 @@
         <v>50</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T60" s="3">
         <v>1</v>
@@ -5471,10 +5653,14 @@
       <c r="W60" s="3"/>
       <c r="X60" s="3"/>
       <c r="Y60" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z60" s="4"/>
-      <c r="AA60" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="Z60" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA60" s="4" t="s">
+        <v>216</v>
+      </c>
       <c r="AB60" s="3"/>
       <c r="AC60" s="3"/>
       <c r="AD60" s="3"/>
@@ -5512,7 +5698,7 @@
       </c>
       <c r="K61" s="3"/>
       <c r="L61" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M61" s="3" t="s">
         <v>48</v>
@@ -5531,7 +5717,7 @@
         <v>50</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T61" s="3">
         <v>1</v>
@@ -5543,10 +5729,14 @@
       <c r="W61" s="3"/>
       <c r="X61" s="3"/>
       <c r="Y61" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z61" s="4"/>
-      <c r="AA61" s="4"/>
+        <v>98</v>
+      </c>
+      <c r="Z61" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="AA61" s="4" t="s">
+        <v>215</v>
+      </c>
       <c r="AB61" s="3"/>
       <c r="AC61" s="3"/>
       <c r="AD61" s="3"/>
@@ -5584,7 +5774,7 @@
       </c>
       <c r="K62" s="3"/>
       <c r="L62" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>48</v>
@@ -5603,7 +5793,7 @@
         <v>50</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T62" s="3">
         <v>1</v>
@@ -5615,10 +5805,14 @@
       <c r="W62" s="3"/>
       <c r="X62" s="3"/>
       <c r="Y62" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z62" s="4"/>
-      <c r="AA62" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="Z62" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA62" s="4" t="s">
+        <v>216</v>
+      </c>
       <c r="AB62" s="3"/>
       <c r="AC62" s="3"/>
       <c r="AD62" s="3"/>
@@ -5656,7 +5850,7 @@
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M63" s="3" t="s">
         <v>48</v>
@@ -5675,7 +5869,7 @@
         <v>50</v>
       </c>
       <c r="S63" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T63" s="3">
         <v>1</v>
@@ -5687,10 +5881,14 @@
       <c r="W63" s="3"/>
       <c r="X63" s="3"/>
       <c r="Y63" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z63" s="4"/>
-      <c r="AA63" s="4"/>
+        <v>94</v>
+      </c>
+      <c r="Z63" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA63" s="4" t="s">
+        <v>211</v>
+      </c>
       <c r="AB63" s="3"/>
       <c r="AC63" s="3"/>
       <c r="AD63" s="3"/>
@@ -5728,7 +5926,7 @@
       </c>
       <c r="K64" s="3"/>
       <c r="L64" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M64" s="3" t="s">
         <v>48</v>
@@ -5747,7 +5945,7 @@
         <v>50</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T64" s="3">
         <v>1</v>
@@ -5759,10 +5957,14 @@
       <c r="W64" s="3"/>
       <c r="X64" s="3"/>
       <c r="Y64" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z64" s="4"/>
-      <c r="AA64" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="Z64" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA64" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="AB64" s="3"/>
       <c r="AC64" s="3"/>
       <c r="AD64" s="3"/>
@@ -5800,7 +6002,7 @@
       </c>
       <c r="K65" s="3"/>
       <c r="L65" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M65" s="3" t="s">
         <v>48</v>
@@ -5819,7 +6021,7 @@
         <v>50</v>
       </c>
       <c r="S65" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T65" s="3">
         <v>1</v>
@@ -5831,10 +6033,14 @@
       <c r="W65" s="3"/>
       <c r="X65" s="3"/>
       <c r="Y65" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z65" s="4"/>
-      <c r="AA65" s="4"/>
+        <v>192</v>
+      </c>
+      <c r="Z65" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA65" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="AB65" s="3"/>
       <c r="AC65" s="3"/>
       <c r="AD65" s="3"/>
@@ -5872,7 +6078,7 @@
       </c>
       <c r="K66" s="3"/>
       <c r="L66" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M66" s="3" t="s">
         <v>48</v>
@@ -5891,7 +6097,7 @@
         <v>50</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T66" s="3">
         <v>1</v>
@@ -5903,10 +6109,14 @@
       <c r="W66" s="3"/>
       <c r="X66" s="3"/>
       <c r="Y66" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z66" s="4"/>
-      <c r="AA66" s="4"/>
+        <v>90</v>
+      </c>
+      <c r="Z66" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="AA66" s="4" t="s">
+        <v>208</v>
+      </c>
       <c r="AB66" s="3"/>
       <c r="AC66" s="3"/>
       <c r="AD66" s="3"/>
@@ -5944,7 +6154,7 @@
       </c>
       <c r="K67" s="3"/>
       <c r="L67" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M67" s="3" t="s">
         <v>48</v>
@@ -5963,7 +6173,7 @@
         <v>50</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T67" s="3">
         <v>1</v>
@@ -5975,10 +6185,14 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z67" s="4"/>
-      <c r="AA67" s="4"/>
+        <v>91</v>
+      </c>
+      <c r="Z67" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA67" s="4" t="s">
+        <v>209</v>
+      </c>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
@@ -6016,7 +6230,7 @@
       </c>
       <c r="K68" s="3"/>
       <c r="L68" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M68" s="3" t="s">
         <v>48</v>
@@ -6035,7 +6249,7 @@
         <v>50</v>
       </c>
       <c r="S68" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T68" s="3">
         <v>1</v>
@@ -6047,10 +6261,14 @@
       <c r="W68" s="3"/>
       <c r="X68" s="3"/>
       <c r="Y68" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z68" s="4"/>
-      <c r="AA68" s="4"/>
+        <v>93</v>
+      </c>
+      <c r="Z68" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="AA68" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="AB68" s="3"/>
       <c r="AC68" s="3"/>
       <c r="AD68" s="3"/>
@@ -6088,7 +6306,7 @@
       </c>
       <c r="K69" s="3"/>
       <c r="L69" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M69" s="3" t="s">
         <v>48</v>
@@ -6107,7 +6325,7 @@
         <v>50</v>
       </c>
       <c r="S69" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T69" s="3">
         <v>1</v>
@@ -6119,10 +6337,14 @@
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
       <c r="Y69" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z69" s="4"/>
-      <c r="AA69" s="4"/>
+        <v>94</v>
+      </c>
+      <c r="Z69" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA69" s="4" t="s">
+        <v>211</v>
+      </c>
       <c r="AB69" s="3"/>
       <c r="AC69" s="3"/>
       <c r="AD69" s="3"/>
@@ -6160,7 +6382,7 @@
       </c>
       <c r="K70" s="3"/>
       <c r="L70" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M70" s="3" t="s">
         <v>48</v>
@@ -6179,7 +6401,7 @@
         <v>50</v>
       </c>
       <c r="S70" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T70" s="3">
         <v>1</v>
@@ -6191,10 +6413,14 @@
       <c r="W70" s="3"/>
       <c r="X70" s="3"/>
       <c r="Y70" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z70" s="4"/>
-      <c r="AA70" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="Z70" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA70" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="AB70" s="3"/>
       <c r="AC70" s="3"/>
       <c r="AD70" s="3"/>
@@ -6232,7 +6458,7 @@
       </c>
       <c r="K71" s="3"/>
       <c r="L71" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M71" s="3" t="s">
         <v>48</v>
@@ -6251,7 +6477,7 @@
         <v>50</v>
       </c>
       <c r="S71" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T71" s="3">
         <v>1</v>
@@ -6263,10 +6489,14 @@
       <c r="W71" s="3"/>
       <c r="X71" s="3"/>
       <c r="Y71" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z71" s="4"/>
-      <c r="AA71" s="4"/>
+        <v>94</v>
+      </c>
+      <c r="Z71" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA71" s="4" t="s">
+        <v>211</v>
+      </c>
       <c r="AB71" s="3"/>
       <c r="AC71" s="3"/>
       <c r="AD71" s="3"/>
@@ -6304,7 +6534,7 @@
       </c>
       <c r="K72" s="3"/>
       <c r="L72" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>48</v>
@@ -6323,7 +6553,7 @@
         <v>50</v>
       </c>
       <c r="S72" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T72" s="3">
         <v>1</v>
@@ -6335,10 +6565,14 @@
       <c r="W72" s="3"/>
       <c r="X72" s="3"/>
       <c r="Y72" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z72" s="4"/>
-      <c r="AA72" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="Z72" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA72" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="AB72" s="3"/>
       <c r="AC72" s="3"/>
       <c r="AD72" s="3"/>
@@ -6357,13 +6591,13 @@
         <v>42</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D73" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
@@ -6382,16 +6616,16 @@
         <v>126</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q73" s="3">
         <v>2</v>
       </c>
       <c r="R73" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="S73" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="S73" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="T73" s="3">
         <v>1</v>
@@ -6423,13 +6657,13 @@
         <v>42</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="E74" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
@@ -6448,16 +6682,16 @@
         <v>205</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q74" s="3">
         <v>2</v>
       </c>
       <c r="R74" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="S74" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="S74" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="T74" s="3">
         <v>1</v>
@@ -6489,13 +6723,13 @@
         <v>42</v>
       </c>
       <c r="C75" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="E75" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
@@ -6514,16 +6748,16 @@
         <v>630</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q75" s="3">
         <v>2</v>
       </c>
       <c r="R75" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="S75" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="S75" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="T75" s="3">
         <v>1</v>
@@ -6555,13 +6789,13 @@
         <v>42</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
@@ -6580,16 +6814,16 @@
         <v>630</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q76" s="3">
         <v>2</v>
       </c>
       <c r="R76" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="S76" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="T76" s="3">
         <v>1</v>
@@ -6621,7 +6855,7 @@
         <v>42</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>53</v>
@@ -6691,13 +6925,13 @@
         <v>42</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>76</v>
@@ -6761,13 +6995,13 @@
         <v>42</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
@@ -6829,13 +7063,13 @@
         <v>42</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
@@ -6897,13 +7131,13 @@
         <v>42</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
@@ -6965,13 +7199,13 @@
         <v>42</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
@@ -7033,13 +7267,13 @@
         <v>42</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
@@ -7052,7 +7286,7 @@
       </c>
       <c r="K83" s="3"/>
       <c r="L83" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>64</v>
@@ -7090,7 +7324,7 @@
         <v>73</v>
       </c>
       <c r="AF83" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AG83" s="3"/>
       <c r="AH83" s="3"/>
@@ -7111,13 +7345,13 @@
         <v>42</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
@@ -7178,13 +7412,13 @@
         <v>42</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
@@ -7246,13 +7480,13 @@
         <v>42</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
@@ -7265,7 +7499,7 @@
       </c>
       <c r="K86" s="3"/>
       <c r="L86" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M86" s="3" t="s">
         <v>64</v>
@@ -7303,7 +7537,7 @@
         <v>73</v>
       </c>
       <c r="AF86" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG86" s="3"/>
       <c r="AH86" s="3"/>
@@ -7324,13 +7558,13 @@
         <v>42</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
@@ -7392,13 +7626,13 @@
         <v>42</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
@@ -7460,13 +7694,13 @@
         <v>42</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>76</v>
@@ -7496,13 +7730,13 @@
         <v>50</v>
       </c>
       <c r="S89" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="T89" s="3">
         <v>15</v>
       </c>
       <c r="U89" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V89" s="3"/>
       <c r="W89" s="3"/>
@@ -7528,13 +7762,13 @@
         <v>42</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>76</v>
@@ -7564,13 +7798,13 @@
         <v>50</v>
       </c>
       <c r="S90" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="T90" s="3">
         <v>15</v>
       </c>
       <c r="U90" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
@@ -7596,13 +7830,13 @@
         <v>42</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>76</v>
@@ -7632,13 +7866,13 @@
         <v>50</v>
       </c>
       <c r="S91" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="T91" s="3">
         <v>15</v>
       </c>
       <c r="U91" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V91" s="3"/>
       <c r="W91" s="3"/>
@@ -7664,13 +7898,13 @@
         <v>42</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>76</v>
@@ -7700,13 +7934,13 @@
         <v>50</v>
       </c>
       <c r="S92" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="T92" s="3">
         <v>15</v>
       </c>
       <c r="U92" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V92" s="3"/>
       <c r="W92" s="3"/>
@@ -7732,13 +7966,13 @@
         <v>42</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>76</v>
@@ -7768,20 +8002,18 @@
         <v>50</v>
       </c>
       <c r="S93" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="T93" s="3">
         <v>15</v>
       </c>
       <c r="U93" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V93" s="3"/>
       <c r="W93" s="3"/>
       <c r="X93" s="3"/>
-      <c r="Y93" s="3" t="s">
-        <v>123</v>
-      </c>
+      <c r="Y93" s="3"/>
       <c r="Z93" s="4"/>
       <c r="AA93" s="4"/>
       <c r="AB93" s="3"/>
@@ -7802,13 +8034,13 @@
         <v>42</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>76</v>
@@ -7838,13 +8070,13 @@
         <v>50</v>
       </c>
       <c r="S94" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="T94" s="3">
         <v>15</v>
       </c>
       <c r="U94" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V94" s="3"/>
       <c r="W94" s="3"/>
@@ -7870,13 +8102,13 @@
         <v>42</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>76</v>
@@ -7906,13 +8138,13 @@
         <v>50</v>
       </c>
       <c r="S95" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="T95" s="3">
         <v>15</v>
       </c>
       <c r="U95" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
@@ -7938,13 +8170,13 @@
         <v>42</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>76</v>
@@ -7974,13 +8206,13 @@
         <v>50</v>
       </c>
       <c r="S96" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="T96" s="3">
         <v>15</v>
       </c>
       <c r="U96" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V96" s="3"/>
       <c r="W96" s="3"/>
@@ -8006,13 +8238,13 @@
         <v>42</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>76</v>
@@ -8042,13 +8274,13 @@
         <v>50</v>
       </c>
       <c r="S97" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="T97" s="3">
         <v>15</v>
       </c>
       <c r="U97" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V97" s="3"/>
       <c r="W97" s="3"/>
@@ -8077,10 +8309,10 @@
         <v>65</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
@@ -8101,7 +8333,7 @@
         <v>9</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Q98" s="3">
         <v>1</v>
@@ -8110,13 +8342,13 @@
         <v>50</v>
       </c>
       <c r="S98" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="T98" s="3">
         <v>15</v>
       </c>
       <c r="U98" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V98" s="3"/>
       <c r="W98" s="3"/>
@@ -8145,10 +8377,10 @@
         <v>65</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
@@ -8169,7 +8401,7 @@
         <v>9</v>
       </c>
       <c r="P99" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Q99" s="3">
         <v>1</v>
@@ -8178,13 +8410,13 @@
         <v>50</v>
       </c>
       <c r="S99" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="T99" s="3">
         <v>15</v>
       </c>
       <c r="U99" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V99" s="3"/>
       <c r="W99" s="3"/>
@@ -8213,10 +8445,10 @@
         <v>65</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
@@ -8237,7 +8469,7 @@
         <v>9</v>
       </c>
       <c r="P100" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Q100" s="3">
         <v>1</v>
@@ -8246,13 +8478,13 @@
         <v>50</v>
       </c>
       <c r="S100" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="T100" s="3">
         <v>15</v>
       </c>
       <c r="U100" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V100" s="3"/>
       <c r="W100" s="3"/>
@@ -8284,7 +8516,7 @@
         <v>43</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
@@ -8305,7 +8537,7 @@
         <v>9</v>
       </c>
       <c r="P101" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Q101" s="3">
         <v>1</v>
@@ -8314,13 +8546,13 @@
         <v>50</v>
       </c>
       <c r="S101" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="T101" s="3">
         <v>15</v>
       </c>
       <c r="U101" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V101" s="3"/>
       <c r="W101" s="3"/>
@@ -8352,7 +8584,7 @@
         <v>53</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
@@ -8373,7 +8605,7 @@
         <v>9</v>
       </c>
       <c r="P102" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Q102" s="3">
         <v>1</v>
@@ -8382,13 +8614,13 @@
         <v>50</v>
       </c>
       <c r="S102" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="T102" s="3">
         <v>15</v>
       </c>
       <c r="U102" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V102" s="3"/>
       <c r="W102" s="3"/>
@@ -8420,7 +8652,7 @@
         <v>54</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
@@ -8441,7 +8673,7 @@
         <v>9</v>
       </c>
       <c r="P103" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Q103" s="3">
         <v>1</v>
@@ -8450,13 +8682,13 @@
         <v>50</v>
       </c>
       <c r="S103" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="T103" s="3">
         <v>15</v>
       </c>
       <c r="U103" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V103" s="3"/>
       <c r="W103" s="3"/>
@@ -8488,7 +8720,7 @@
         <v>58</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
@@ -8509,7 +8741,7 @@
         <v>9</v>
       </c>
       <c r="P104" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Q104" s="3">
         <v>1</v>
@@ -8518,13 +8750,13 @@
         <v>50</v>
       </c>
       <c r="S104" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="T104" s="3">
         <v>15</v>
       </c>
       <c r="U104" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V104" s="3"/>
       <c r="W104" s="3"/>
@@ -8550,7 +8782,7 @@
         <v>42</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>43</v>
@@ -8594,7 +8826,7 @@
         <v>50</v>
       </c>
       <c r="U105" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V105" s="3"/>
       <c r="W105" s="3"/>
@@ -8620,7 +8852,7 @@
         <v>42</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>53</v>
@@ -8664,7 +8896,7 @@
         <v>50</v>
       </c>
       <c r="U106" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V106" s="3"/>
       <c r="W106" s="3"/>
@@ -8690,7 +8922,7 @@
         <v>42</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>54</v>
@@ -8734,7 +8966,7 @@
         <v>50</v>
       </c>
       <c r="U107" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V107" s="3"/>
       <c r="W107" s="3"/>
@@ -8760,16 +8992,16 @@
         <v>42</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G108" s="3"/>
       <c r="H108" s="3" t="s">
@@ -8804,7 +9036,7 @@
         <v>85</v>
       </c>
       <c r="U108" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V108" s="3"/>
       <c r="W108" s="3"/>
@@ -8830,16 +9062,16 @@
         <v>42</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G109" s="3"/>
       <c r="H109" s="3" t="s">
@@ -8874,7 +9106,7 @@
         <v>85</v>
       </c>
       <c r="U109" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V109" s="3"/>
       <c r="W109" s="3"/>
@@ -8900,16 +9132,16 @@
         <v>42</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G110" s="3"/>
       <c r="H110" s="3" t="s">
@@ -8944,7 +9176,7 @@
         <v>85</v>
       </c>
       <c r="U110" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V110" s="3"/>
       <c r="W110" s="3"/>
@@ -8970,16 +9202,16 @@
         <v>42</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G111" s="3"/>
       <c r="H111" s="3" t="s">
@@ -9014,7 +9246,7 @@
         <v>85</v>
       </c>
       <c r="U111" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V111" s="3"/>
       <c r="W111" s="3"/>
@@ -9040,13 +9272,13 @@
         <v>42</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="3"/>
@@ -9082,7 +9314,7 @@
         <v>85</v>
       </c>
       <c r="U112" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V112" s="3"/>
       <c r="W112" s="3"/>
@@ -9108,13 +9340,13 @@
         <v>42</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F113" s="3"/>
       <c r="G113" s="3"/>
@@ -9150,7 +9382,7 @@
         <v>85</v>
       </c>
       <c r="U113" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V113" s="3"/>
       <c r="W113" s="3"/>
@@ -9176,13 +9408,13 @@
         <v>42</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>76</v>
@@ -9220,7 +9452,7 @@
         <v>85</v>
       </c>
       <c r="U114" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V114" s="3"/>
       <c r="W114" s="3"/>
@@ -9246,13 +9478,13 @@
         <v>42</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F115" s="3"/>
       <c r="G115" s="3"/>
@@ -9273,7 +9505,7 @@
         <v>7000000</v>
       </c>
       <c r="P115" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="Q115" s="3">
         <v>30</v>
@@ -9288,7 +9520,7 @@
         <v>85</v>
       </c>
       <c r="U115" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V115" s="3"/>
       <c r="W115" s="3"/>
@@ -9314,7 +9546,7 @@
         <v>42</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>43</v>
@@ -9335,7 +9567,7 @@
       </c>
       <c r="K116" s="3"/>
       <c r="L116" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="M116" s="3" t="s">
         <v>64</v>
@@ -9358,7 +9590,7 @@
         <v>85</v>
       </c>
       <c r="U116" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V116" s="3"/>
       <c r="W116" s="3"/>
@@ -9370,10 +9602,10 @@
       <c r="AC116" s="3"/>
       <c r="AD116" s="3"/>
       <c r="AE116" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AF116" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AG116" s="3"/>
       <c r="AH116" s="3"/>
@@ -9388,7 +9620,7 @@
         <v>42</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>43</v>
@@ -9409,7 +9641,7 @@
       </c>
       <c r="K117" s="3"/>
       <c r="L117" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M117" s="3" t="s">
         <v>64</v>
@@ -9432,7 +9664,7 @@
         <v>85</v>
       </c>
       <c r="U117" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V117" s="3"/>
       <c r="W117" s="3"/>
@@ -9444,10 +9676,10 @@
       <c r="AC117" s="3"/>
       <c r="AD117" s="3"/>
       <c r="AE117" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF117" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="AF117" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="AG117" s="3"/>
       <c r="AH117" s="3"/>
@@ -9462,7 +9694,7 @@
         <v>42</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>53</v>
@@ -9504,27 +9736,27 @@
         <v>85</v>
       </c>
       <c r="U118" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V118" s="3"/>
       <c r="W118" s="3"/>
       <c r="Y118" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Z118" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AA118" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AB118" s="3"/>
       <c r="AC118" s="3"/>
       <c r="AD118" s="3"/>
       <c r="AE118" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AF118" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AG118" s="3"/>
       <c r="AH118" s="3"/>
@@ -9539,7 +9771,7 @@
         <v>42</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D119" s="3" t="s">
         <v>53</v>
@@ -9581,27 +9813,27 @@
         <v>85</v>
       </c>
       <c r="U119" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V119" s="3"/>
       <c r="W119" s="3"/>
       <c r="Y119" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="Z119" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AA119" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AB119" s="3"/>
       <c r="AC119" s="3"/>
       <c r="AD119" s="3"/>
       <c r="AE119" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF119" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="AF119" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="AG119" s="3"/>
       <c r="AH119" s="3"/>
@@ -9616,7 +9848,7 @@
         <v>42</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>54</v>
@@ -9637,7 +9869,7 @@
       </c>
       <c r="K120" s="3"/>
       <c r="L120" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="M120" s="3" t="s">
         <v>64</v>
@@ -9660,7 +9892,7 @@
         <v>85</v>
       </c>
       <c r="U120" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V120" s="3"/>
       <c r="W120" s="3"/>
@@ -9672,10 +9904,10 @@
       <c r="AC120" s="3"/>
       <c r="AD120" s="3"/>
       <c r="AE120" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AF120" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AG120" s="3"/>
       <c r="AH120" s="3"/>
@@ -9690,7 +9922,7 @@
         <v>42</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>54</v>
@@ -9711,7 +9943,7 @@
       </c>
       <c r="K121" s="3"/>
       <c r="L121" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M121" s="3" t="s">
         <v>64</v>
@@ -9734,7 +9966,7 @@
         <v>85</v>
       </c>
       <c r="U121" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V121" s="3"/>
       <c r="W121" s="3"/>
@@ -9746,10 +9978,10 @@
       <c r="AC121" s="3"/>
       <c r="AD121" s="3"/>
       <c r="AE121" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF121" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="AF121" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="AG121" s="3"/>
       <c r="AH121" s="3"/>
@@ -9785,7 +10017,7 @@
       </c>
       <c r="K122" s="3"/>
       <c r="L122" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M122" s="3" t="s">
         <v>64</v>
@@ -9808,7 +10040,7 @@
         <v>50</v>
       </c>
       <c r="U122" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V122" s="3"/>
       <c r="W122" s="3"/>
@@ -9820,10 +10052,10 @@
       <c r="AC122" s="3"/>
       <c r="AD122" s="3"/>
       <c r="AE122" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AF122" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AG122" s="3"/>
       <c r="AH122" s="3"/>
@@ -9865,7 +10097,7 @@
       </c>
       <c r="K123" s="3"/>
       <c r="L123" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M123" s="3" t="s">
         <v>64</v>
@@ -9888,7 +10120,7 @@
         <v>50</v>
       </c>
       <c r="U123" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V123" s="3"/>
       <c r="W123" s="3"/>
@@ -9900,10 +10132,10 @@
       <c r="AC123" s="3"/>
       <c r="AD123" s="3"/>
       <c r="AE123" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AF123" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG123" s="3"/>
       <c r="AH123" s="3"/>
@@ -9926,13 +10158,13 @@
         <v>42</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>76</v>
@@ -9970,7 +10202,7 @@
         <v>85</v>
       </c>
       <c r="U124" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V124" s="3"/>
       <c r="W124" s="3"/>
@@ -9996,13 +10228,13 @@
         <v>42</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>76</v>
@@ -10040,7 +10272,7 @@
         <v>85</v>
       </c>
       <c r="U125" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V125" s="3"/>
       <c r="W125" s="3"/>
@@ -10066,13 +10298,13 @@
         <v>42</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>76</v>
@@ -10110,7 +10342,7 @@
         <v>85</v>
       </c>
       <c r="U126" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V126" s="3"/>
       <c r="W126" s="3"/>
@@ -10136,13 +10368,13 @@
         <v>42</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>76</v>
@@ -10180,7 +10412,7 @@
         <v>85</v>
       </c>
       <c r="U127" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V127" s="3"/>
       <c r="W127" s="3"/>
@@ -10206,13 +10438,13 @@
         <v>42</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>76</v>
@@ -10250,7 +10482,7 @@
         <v>85</v>
       </c>
       <c r="U128" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V128" s="3"/>
       <c r="W128" s="3"/>
@@ -10276,13 +10508,13 @@
         <v>42</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>76</v>
@@ -10320,7 +10552,7 @@
         <v>50</v>
       </c>
       <c r="U129" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V129" s="3"/>
       <c r="W129" s="3"/>
@@ -10346,13 +10578,13 @@
         <v>42</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>76</v>
@@ -10390,7 +10622,7 @@
         <v>50</v>
       </c>
       <c r="U130" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V130" s="3"/>
       <c r="W130" s="3"/>
@@ -10416,13 +10648,13 @@
         <v>42</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>76</v>
@@ -10460,7 +10692,7 @@
         <v>50</v>
       </c>
       <c r="U131" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V131" s="3"/>
       <c r="W131" s="3"/>
@@ -10486,13 +10718,13 @@
         <v>42</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>76</v>
@@ -10530,7 +10762,7 @@
         <v>50</v>
       </c>
       <c r="U132" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V132" s="3"/>
       <c r="W132" s="3"/>
@@ -10556,13 +10788,13 @@
         <v>42</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>76</v>
@@ -10600,7 +10832,7 @@
         <v>50</v>
       </c>
       <c r="U133" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V133" s="3"/>
       <c r="W133" s="3"/>
@@ -10626,13 +10858,13 @@
         <v>42</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>76</v>
@@ -10670,7 +10902,7 @@
         <v>50</v>
       </c>
       <c r="U134" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V134" s="3"/>
       <c r="W134" s="3"/>
@@ -10696,13 +10928,13 @@
         <v>42</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>76</v>
@@ -10740,7 +10972,7 @@
         <v>50</v>
       </c>
       <c r="U135" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V135" s="3"/>
       <c r="W135" s="3"/>
@@ -10808,7 +11040,7 @@
         <v>85</v>
       </c>
       <c r="U136" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V136" s="3"/>
       <c r="W136" s="3"/>
@@ -10823,7 +11055,7 @@
         <v>73</v>
       </c>
       <c r="AF136" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AG136" s="3">
         <v>1.101672</v>
@@ -10892,7 +11124,7 @@
         <v>50</v>
       </c>
       <c r="U137" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V137" s="3"/>
       <c r="W137" s="3"/>
@@ -10962,7 +11194,7 @@
         <v>50</v>
       </c>
       <c r="U138" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V138" s="3"/>
       <c r="W138" s="3"/>
@@ -10988,7 +11220,7 @@
         <v>42</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>43</v>
@@ -11030,7 +11262,7 @@
         <v>85</v>
       </c>
       <c r="U139" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V139" s="3"/>
       <c r="W139" s="3"/>
@@ -11045,7 +11277,7 @@
         <v>73</v>
       </c>
       <c r="AF139" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AG139" s="3"/>
       <c r="AH139" s="3"/>
@@ -11066,7 +11298,7 @@
         <v>42</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D140" s="3" t="s">
         <v>57</v>
@@ -11110,7 +11342,7 @@
         <v>50</v>
       </c>
       <c r="U140" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V140" s="3"/>
       <c r="W140" s="3"/>
@@ -11136,7 +11368,7 @@
         <v>42</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D141" s="3" t="s">
         <v>58</v>
@@ -11180,7 +11412,7 @@
         <v>50</v>
       </c>
       <c r="U141" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V141" s="3"/>
       <c r="W141" s="3"/>
@@ -11206,7 +11438,7 @@
         <v>42</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>43</v>
@@ -11250,7 +11482,7 @@
         <v>85</v>
       </c>
       <c r="U142" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V142" s="3"/>
       <c r="W142" s="3"/>
@@ -11276,7 +11508,7 @@
         <v>42</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D143" s="3" t="s">
         <v>57</v>
@@ -11320,7 +11552,7 @@
         <v>50</v>
       </c>
       <c r="U143" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V143" s="3"/>
       <c r="W143" s="3"/>
@@ -11346,7 +11578,7 @@
         <v>42</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>58</v>
@@ -11390,7 +11622,7 @@
         <v>50</v>
       </c>
       <c r="U144" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V144" s="3"/>
       <c r="W144" s="3"/>
@@ -11416,13 +11648,13 @@
         <v>42</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>76</v>
@@ -11458,7 +11690,7 @@
         <v>85</v>
       </c>
       <c r="U145" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V145" s="3"/>
       <c r="W145" s="3"/>
@@ -11473,7 +11705,7 @@
         <v>73</v>
       </c>
       <c r="AF145" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AG145" s="3"/>
       <c r="AH145" s="3"/>
@@ -11494,13 +11726,13 @@
         <v>42</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>76</v>
@@ -11536,7 +11768,7 @@
         <v>85</v>
       </c>
       <c r="U146" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V146" s="3"/>
       <c r="W146" s="3"/>
@@ -11551,7 +11783,7 @@
         <v>73</v>
       </c>
       <c r="AF146" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AG146" s="3"/>
       <c r="AH146" s="3"/>
@@ -11572,13 +11804,13 @@
         <v>42</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D147" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>76</v>
@@ -11616,7 +11848,7 @@
         <v>50</v>
       </c>
       <c r="U147" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V147" s="3"/>
       <c r="W147" s="3"/>
@@ -11642,13 +11874,13 @@
         <v>42</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>76</v>
@@ -11686,7 +11918,7 @@
         <v>50</v>
       </c>
       <c r="U148" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V148" s="3"/>
       <c r="W148" s="3"/>
@@ -11712,13 +11944,13 @@
         <v>42</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D149" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>70</v>
@@ -11756,7 +11988,7 @@
         <v>50</v>
       </c>
       <c r="U149" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V149" s="3"/>
       <c r="W149" s="3"/>
@@ -11782,13 +12014,13 @@
         <v>42</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D150" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>76</v>
@@ -11826,7 +12058,7 @@
         <v>85</v>
       </c>
       <c r="U150" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V150" s="3"/>
       <c r="W150" s="3"/>
@@ -11852,13 +12084,13 @@
         <v>42</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D151" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>76</v>
@@ -11894,7 +12126,7 @@
         <v>85</v>
       </c>
       <c r="U151" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V151" s="3"/>
       <c r="W151" s="3"/>
@@ -11909,7 +12141,7 @@
         <v>73</v>
       </c>
       <c r="AF151" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AG151" s="3">
         <v>1.4620299999999999</v>
@@ -11934,13 +12166,13 @@
         <v>42</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>76</v>
@@ -11976,7 +12208,7 @@
         <v>85</v>
       </c>
       <c r="U152" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V152" s="3"/>
       <c r="W152" s="3"/>
@@ -11991,7 +12223,7 @@
         <v>73</v>
       </c>
       <c r="AF152" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG152" s="3">
         <v>1.4620299999999999</v>
@@ -12016,13 +12248,13 @@
         <v>42</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D153" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>76</v>
@@ -12060,7 +12292,7 @@
         <v>50</v>
       </c>
       <c r="U153" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V153" s="3"/>
       <c r="W153" s="3"/>
@@ -12086,13 +12318,13 @@
         <v>42</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D154" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>76</v>
@@ -12130,7 +12362,7 @@
         <v>50</v>
       </c>
       <c r="U154" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V154" s="3"/>
       <c r="W154" s="3"/>
@@ -12156,13 +12388,13 @@
         <v>42</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D155" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>76</v>
@@ -12198,7 +12430,7 @@
         <v>85</v>
       </c>
       <c r="U155" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V155" s="3"/>
       <c r="W155" s="3"/>
@@ -12213,7 +12445,7 @@
         <v>73</v>
       </c>
       <c r="AF155" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AG155" s="3"/>
       <c r="AH155" s="3"/>
@@ -12234,13 +12466,13 @@
         <v>42</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>76</v>
@@ -12276,7 +12508,7 @@
         <v>85</v>
       </c>
       <c r="U156" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V156" s="3"/>
       <c r="W156" s="3"/>
@@ -12291,7 +12523,7 @@
         <v>73</v>
       </c>
       <c r="AF156" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG156" s="3"/>
       <c r="AH156" s="3"/>
@@ -12312,13 +12544,13 @@
         <v>42</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>76</v>
@@ -12356,7 +12588,7 @@
         <v>50</v>
       </c>
       <c r="U157" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V157" s="3"/>
       <c r="W157" s="3"/>
@@ -12382,13 +12614,13 @@
         <v>42</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D158" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>76</v>
@@ -12426,7 +12658,7 @@
         <v>50</v>
       </c>
       <c r="U158" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V158" s="3"/>
       <c r="W158" s="3"/>
@@ -12452,13 +12684,13 @@
         <v>42</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>70</v>
@@ -12496,7 +12728,7 @@
         <v>50</v>
       </c>
       <c r="U159" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V159" s="3"/>
       <c r="W159" s="3"/>
@@ -12522,13 +12754,13 @@
         <v>42</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>70</v>
@@ -12566,7 +12798,7 @@
         <v>50</v>
       </c>
       <c r="U160" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V160" s="3"/>
       <c r="W160" s="3"/>
@@ -12592,13 +12824,13 @@
         <v>42</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>76</v>
@@ -12636,7 +12868,7 @@
         <v>50</v>
       </c>
       <c r="U161" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V161" s="3"/>
       <c r="W161" s="3"/>
@@ -12662,13 +12894,13 @@
         <v>42</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>76</v>
@@ -12706,7 +12938,7 @@
         <v>50</v>
       </c>
       <c r="U162" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V162" s="3"/>
       <c r="W162" s="3"/>
@@ -12732,13 +12964,13 @@
         <v>42</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D163" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>76</v>
@@ -12774,7 +13006,7 @@
         <v>85</v>
       </c>
       <c r="U163" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V163" s="3"/>
       <c r="W163" s="3"/>
@@ -12789,7 +13021,7 @@
         <v>73</v>
       </c>
       <c r="AF163" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AG163" s="3"/>
       <c r="AH163" s="3"/>
@@ -12810,13 +13042,13 @@
         <v>42</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D164" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>76</v>
@@ -12852,7 +13084,7 @@
         <v>85</v>
       </c>
       <c r="U164" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V164" s="3"/>
       <c r="W164" s="3"/>
@@ -12867,7 +13099,7 @@
         <v>73</v>
       </c>
       <c r="AF164" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AG164" s="3"/>
       <c r="AH164" s="3"/>
@@ -12888,13 +13120,13 @@
         <v>42</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>76</v>
@@ -12932,7 +13164,7 @@
         <v>50</v>
       </c>
       <c r="U165" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V165" s="3"/>
       <c r="W165" s="3"/>
@@ -12958,13 +13190,13 @@
         <v>42</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D166" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>76</v>
@@ -13002,7 +13234,7 @@
         <v>50</v>
       </c>
       <c r="U166" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V166" s="3"/>
       <c r="W166" s="3"/>
@@ -13028,13 +13260,13 @@
         <v>42</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>76</v>
@@ -13072,7 +13304,7 @@
         <v>85</v>
       </c>
       <c r="U167" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V167" s="3"/>
       <c r="W167" s="3"/>
@@ -13098,13 +13330,13 @@
         <v>42</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D168" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>76</v>
@@ -13142,7 +13374,7 @@
         <v>85</v>
       </c>
       <c r="U168" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V168" s="3"/>
       <c r="W168" s="3"/>
@@ -13168,13 +13400,13 @@
         <v>42</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D169" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>76</v>
@@ -13212,7 +13444,7 @@
         <v>50</v>
       </c>
       <c r="U169" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V169" s="3"/>
       <c r="W169" s="3"/>
@@ -13238,13 +13470,13 @@
         <v>42</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>76</v>
@@ -13282,7 +13514,7 @@
         <v>50</v>
       </c>
       <c r="U170" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V170" s="3"/>
       <c r="W170" s="3"/>
@@ -13308,13 +13540,13 @@
         <v>42</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D171" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>76</v>
@@ -13350,7 +13582,7 @@
         <v>85</v>
       </c>
       <c r="U171" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V171" s="3"/>
       <c r="W171" s="3"/>
@@ -13365,7 +13597,7 @@
         <v>73</v>
       </c>
       <c r="AF171" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG171" s="3"/>
       <c r="AH171" s="3"/>
@@ -13386,13 +13618,13 @@
         <v>42</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D172" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>76</v>
@@ -13428,7 +13660,7 @@
         <v>85</v>
       </c>
       <c r="U172" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V172" s="3"/>
       <c r="W172" s="3"/>
@@ -13443,7 +13675,7 @@
         <v>73</v>
       </c>
       <c r="AF172" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AG172" s="3"/>
       <c r="AH172" s="3"/>
@@ -13464,13 +13696,13 @@
         <v>42</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>76</v>
@@ -13508,7 +13740,7 @@
         <v>50</v>
       </c>
       <c r="U173" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V173" s="3"/>
       <c r="W173" s="3"/>
@@ -13534,13 +13766,13 @@
         <v>42</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>76</v>
@@ -13578,7 +13810,7 @@
         <v>85</v>
       </c>
       <c r="U174" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V174" s="3"/>
       <c r="W174" s="3"/>
@@ -13604,13 +13836,13 @@
         <v>42</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>76</v>
@@ -13648,7 +13880,7 @@
         <v>50</v>
       </c>
       <c r="U175" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V175" s="3"/>
       <c r="W175" s="3"/>
@@ -13674,13 +13906,13 @@
         <v>42</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>76</v>
@@ -13716,7 +13948,7 @@
         <v>85</v>
       </c>
       <c r="U176" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V176" s="3"/>
       <c r="W176" s="3"/>
@@ -13731,7 +13963,7 @@
         <v>73</v>
       </c>
       <c r="AF176" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG176" s="3"/>
       <c r="AH176" s="3"/>
@@ -13752,13 +13984,13 @@
         <v>42</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>76</v>
@@ -13794,7 +14026,7 @@
         <v>85</v>
       </c>
       <c r="U177" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V177" s="3"/>
       <c r="W177" s="3"/>
@@ -13809,7 +14041,7 @@
         <v>73</v>
       </c>
       <c r="AF177" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AG177" s="3"/>
       <c r="AH177" s="3"/>
@@ -13830,13 +14062,13 @@
         <v>42</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D178" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>76</v>
@@ -13874,7 +14106,7 @@
         <v>50</v>
       </c>
       <c r="U178" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V178" s="3"/>
       <c r="W178" s="3"/>
@@ -13900,13 +14132,13 @@
         <v>42</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>76</v>
@@ -13942,7 +14174,7 @@
         <v>85</v>
       </c>
       <c r="U179" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V179" s="3"/>
       <c r="W179" s="3"/>
@@ -13957,7 +14189,7 @@
         <v>73</v>
       </c>
       <c r="AF179" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG179" s="3"/>
       <c r="AH179" s="3"/>
@@ -13978,13 +14210,13 @@
         <v>42</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D180" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>76</v>
@@ -14020,7 +14252,7 @@
         <v>85</v>
       </c>
       <c r="U180" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V180" s="3"/>
       <c r="W180" s="3"/>
@@ -14035,7 +14267,7 @@
         <v>73</v>
       </c>
       <c r="AF180" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG180" s="3"/>
       <c r="AH180" s="3"/>
@@ -14056,13 +14288,13 @@
         <v>42</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D181" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>76</v>
@@ -14100,7 +14332,7 @@
         <v>50</v>
       </c>
       <c r="U181" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V181" s="3"/>
       <c r="W181" s="3"/>
@@ -14126,13 +14358,13 @@
         <v>42</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D182" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>76</v>
@@ -14170,7 +14402,7 @@
         <v>50</v>
       </c>
       <c r="U182" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V182" s="3"/>
       <c r="W182" s="3"/>
@@ -14196,7 +14428,7 @@
         <v>42</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D183" s="3" t="s">
         <v>79</v>
@@ -14334,7 +14566,7 @@
         <v>42</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D185" s="3" t="s">
         <v>79</v>
@@ -14437,7 +14669,7 @@
       </c>
       <c r="K186" s="3"/>
       <c r="L186" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M186" s="3" t="s">
         <v>48</v>
@@ -14456,7 +14688,7 @@
         <v>50</v>
       </c>
       <c r="S186" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T186" s="3">
         <v>1</v>
@@ -14467,11 +14699,15 @@
       <c r="V186" s="3"/>
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
-      <c r="Y186" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z186" s="4"/>
-      <c r="AA186" s="4"/>
+      <c r="Y186" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z186" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA186" s="6" t="s">
+        <v>207</v>
+      </c>
       <c r="AB186" s="3"/>
       <c r="AC186" s="3"/>
       <c r="AD186" s="3"/>
@@ -14509,7 +14745,7 @@
       </c>
       <c r="K187" s="3"/>
       <c r="L187" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M187" s="3" t="s">
         <v>48</v>
@@ -14528,7 +14764,7 @@
         <v>50</v>
       </c>
       <c r="S187" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T187" s="3">
         <v>1</v>
@@ -14539,11 +14775,15 @@
       <c r="V187" s="3"/>
       <c r="W187" s="3"/>
       <c r="X187" s="3"/>
-      <c r="Y187" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z187" s="4"/>
-      <c r="AA187" s="4"/>
+      <c r="Y187" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z187" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="AA187" s="6" t="s">
+        <v>208</v>
+      </c>
       <c r="AB187" s="3"/>
       <c r="AC187" s="3"/>
       <c r="AD187" s="3"/>
@@ -14581,7 +14821,7 @@
       </c>
       <c r="K188" s="3"/>
       <c r="L188" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M188" s="3" t="s">
         <v>48</v>
@@ -14600,7 +14840,7 @@
         <v>50</v>
       </c>
       <c r="S188" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T188" s="3">
         <v>1</v>
@@ -14611,11 +14851,15 @@
       <c r="V188" s="3"/>
       <c r="W188" s="3"/>
       <c r="X188" s="3"/>
-      <c r="Y188" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z188" s="4"/>
-      <c r="AA188" s="4"/>
+      <c r="Y188" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z188" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA188" s="6" t="s">
+        <v>209</v>
+      </c>
       <c r="AB188" s="3"/>
       <c r="AC188" s="3"/>
       <c r="AD188" s="3"/>
@@ -14653,7 +14897,7 @@
       </c>
       <c r="K189" s="3"/>
       <c r="L189" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M189" s="3" t="s">
         <v>48</v>
@@ -14672,7 +14916,7 @@
         <v>50</v>
       </c>
       <c r="S189" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T189" s="3">
         <v>1</v>
@@ -14683,11 +14927,15 @@
       <c r="V189" s="3"/>
       <c r="W189" s="3"/>
       <c r="X189" s="3"/>
-      <c r="Y189" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z189" s="4"/>
-      <c r="AA189" s="4"/>
+      <c r="Y189" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z189" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="AA189" s="6" t="s">
+        <v>210</v>
+      </c>
       <c r="AB189" s="3"/>
       <c r="AC189" s="3"/>
       <c r="AD189" s="3"/>
@@ -14725,7 +14973,7 @@
       </c>
       <c r="K190" s="3"/>
       <c r="L190" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M190" s="3" t="s">
         <v>48</v>
@@ -14744,7 +14992,7 @@
         <v>50</v>
       </c>
       <c r="S190" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T190" s="3">
         <v>1</v>
@@ -14755,11 +15003,15 @@
       <c r="V190" s="3"/>
       <c r="W190" s="3"/>
       <c r="X190" s="3"/>
-      <c r="Y190" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z190" s="4"/>
-      <c r="AA190" s="4"/>
+      <c r="Y190" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z190" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA190" s="6" t="s">
+        <v>211</v>
+      </c>
       <c r="AB190" s="3"/>
       <c r="AC190" s="3"/>
       <c r="AD190" s="3"/>
@@ -14797,7 +15049,7 @@
       </c>
       <c r="K191" s="3"/>
       <c r="L191" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M191" s="3" t="s">
         <v>48</v>
@@ -14816,7 +15068,7 @@
         <v>50</v>
       </c>
       <c r="S191" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T191" s="3">
         <v>1</v>
@@ -14827,11 +15079,15 @@
       <c r="V191" s="3"/>
       <c r="W191" s="3"/>
       <c r="X191" s="3"/>
-      <c r="Y191" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z191" s="4"/>
-      <c r="AA191" s="4"/>
+      <c r="Y191" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z191" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA191" s="6" t="s">
+        <v>210</v>
+      </c>
       <c r="AB191" s="3"/>
       <c r="AC191" s="3"/>
       <c r="AD191" s="3"/>
@@ -14869,7 +15125,7 @@
       </c>
       <c r="K192" s="3"/>
       <c r="L192" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M192" s="3" t="s">
         <v>48</v>
@@ -14888,7 +15144,7 @@
         <v>50</v>
       </c>
       <c r="S192" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T192" s="3">
         <v>1</v>
@@ -14899,11 +15155,15 @@
       <c r="V192" s="3"/>
       <c r="W192" s="3"/>
       <c r="X192" s="3"/>
-      <c r="Y192" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z192" s="4"/>
-      <c r="AA192" s="4"/>
+      <c r="Y192" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z192" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA192" s="6" t="s">
+        <v>211</v>
+      </c>
       <c r="AB192" s="3"/>
       <c r="AC192" s="3"/>
       <c r="AD192" s="3"/>
@@ -14941,7 +15201,7 @@
       </c>
       <c r="K193" s="3"/>
       <c r="L193" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M193" s="3" t="s">
         <v>48</v>
@@ -14960,7 +15220,7 @@
         <v>50</v>
       </c>
       <c r="S193" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T193" s="3">
         <v>1</v>
@@ -14971,11 +15231,15 @@
       <c r="V193" s="3"/>
       <c r="W193" s="3"/>
       <c r="X193" s="3"/>
-      <c r="Y193" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z193" s="4"/>
-      <c r="AA193" s="4"/>
+      <c r="Y193" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z193" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA193" s="6" t="s">
+        <v>210</v>
+      </c>
       <c r="AB193" s="3"/>
       <c r="AC193" s="3"/>
       <c r="AD193" s="3"/>
@@ -15013,7 +15277,7 @@
       </c>
       <c r="K194" s="3"/>
       <c r="L194" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M194" s="3" t="s">
         <v>48</v>
@@ -15032,7 +15296,7 @@
         <v>50</v>
       </c>
       <c r="S194" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T194" s="3">
         <v>1</v>
@@ -15043,11 +15307,15 @@
       <c r="V194" s="3"/>
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
-      <c r="Y194" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z194" s="4"/>
-      <c r="AA194" s="4"/>
+      <c r="Y194" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z194" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA194" s="6" t="s">
+        <v>207</v>
+      </c>
       <c r="AB194" s="3"/>
       <c r="AC194" s="3"/>
       <c r="AD194" s="3"/>
@@ -15085,7 +15353,7 @@
       </c>
       <c r="K195" s="3"/>
       <c r="L195" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M195" s="3" t="s">
         <v>48</v>
@@ -15104,7 +15372,7 @@
         <v>50</v>
       </c>
       <c r="S195" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T195" s="3">
         <v>1</v>
@@ -15115,11 +15383,15 @@
       <c r="V195" s="3"/>
       <c r="W195" s="3"/>
       <c r="X195" s="3"/>
-      <c r="Y195" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z195" s="4"/>
-      <c r="AA195" s="4"/>
+      <c r="Y195" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z195" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="AA195" s="6" t="s">
+        <v>208</v>
+      </c>
       <c r="AB195" s="3"/>
       <c r="AC195" s="3"/>
       <c r="AD195" s="3"/>
@@ -15157,7 +15429,7 @@
       </c>
       <c r="K196" s="3"/>
       <c r="L196" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M196" s="3" t="s">
         <v>48</v>
@@ -15176,7 +15448,7 @@
         <v>50</v>
       </c>
       <c r="S196" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T196" s="3">
         <v>1</v>
@@ -15187,11 +15459,15 @@
       <c r="V196" s="3"/>
       <c r="W196" s="3"/>
       <c r="X196" s="3"/>
-      <c r="Y196" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z196" s="4"/>
-      <c r="AA196" s="4"/>
+      <c r="Y196" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z196" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA196" s="6" t="s">
+        <v>209</v>
+      </c>
       <c r="AB196" s="3"/>
       <c r="AC196" s="3"/>
       <c r="AD196" s="3"/>
@@ -15229,7 +15505,7 @@
       </c>
       <c r="K197" s="3"/>
       <c r="L197" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M197" s="3" t="s">
         <v>48</v>
@@ -15248,7 +15524,7 @@
         <v>50</v>
       </c>
       <c r="S197" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T197" s="3">
         <v>1</v>
@@ -15259,11 +15535,15 @@
       <c r="V197" s="3"/>
       <c r="W197" s="3"/>
       <c r="X197" s="3"/>
-      <c r="Y197" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z197" s="4"/>
-      <c r="AA197" s="4"/>
+      <c r="Y197" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z197" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="AA197" s="6" t="s">
+        <v>210</v>
+      </c>
       <c r="AB197" s="3"/>
       <c r="AC197" s="3"/>
       <c r="AD197" s="3"/>
@@ -15301,7 +15581,7 @@
       </c>
       <c r="K198" s="3"/>
       <c r="L198" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M198" s="3" t="s">
         <v>48</v>
@@ -15320,7 +15600,7 @@
         <v>50</v>
       </c>
       <c r="S198" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T198" s="3">
         <v>1</v>
@@ -15331,11 +15611,15 @@
       <c r="V198" s="3"/>
       <c r="W198" s="3"/>
       <c r="X198" s="3"/>
-      <c r="Y198" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z198" s="4"/>
-      <c r="AA198" s="4"/>
+      <c r="Y198" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z198" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA198" s="6" t="s">
+        <v>211</v>
+      </c>
       <c r="AB198" s="3"/>
       <c r="AC198" s="3"/>
       <c r="AD198" s="3"/>
@@ -15373,7 +15657,7 @@
       </c>
       <c r="K199" s="3"/>
       <c r="L199" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M199" s="3" t="s">
         <v>48</v>
@@ -15392,7 +15676,7 @@
         <v>50</v>
       </c>
       <c r="S199" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T199" s="3">
         <v>1</v>
@@ -15403,11 +15687,15 @@
       <c r="V199" s="3"/>
       <c r="W199" s="3"/>
       <c r="X199" s="3"/>
-      <c r="Y199" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z199" s="4"/>
-      <c r="AA199" s="4"/>
+      <c r="Y199" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z199" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA199" s="6" t="s">
+        <v>210</v>
+      </c>
       <c r="AB199" s="3"/>
       <c r="AC199" s="3"/>
       <c r="AD199" s="3"/>
@@ -15445,7 +15733,7 @@
       </c>
       <c r="K200" s="3"/>
       <c r="L200" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M200" s="3" t="s">
         <v>48</v>
@@ -15464,7 +15752,7 @@
         <v>50</v>
       </c>
       <c r="S200" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T200" s="3">
         <v>1</v>
@@ -15475,11 +15763,15 @@
       <c r="V200" s="3"/>
       <c r="W200" s="3"/>
       <c r="X200" s="3"/>
-      <c r="Y200" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z200" s="4"/>
-      <c r="AA200" s="4"/>
+      <c r="Y200" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z200" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA200" s="6" t="s">
+        <v>211</v>
+      </c>
       <c r="AB200" s="3"/>
       <c r="AC200" s="3"/>
       <c r="AD200" s="3"/>
@@ -15517,7 +15809,7 @@
       </c>
       <c r="K201" s="3"/>
       <c r="L201" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M201" s="3" t="s">
         <v>48</v>
@@ -15536,7 +15828,7 @@
         <v>50</v>
       </c>
       <c r="S201" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T201" s="3">
         <v>1</v>
@@ -15547,11 +15839,15 @@
       <c r="V201" s="3"/>
       <c r="W201" s="3"/>
       <c r="X201" s="3"/>
-      <c r="Y201" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z201" s="4"/>
-      <c r="AA201" s="4"/>
+      <c r="Y201" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z201" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA201" s="6" t="s">
+        <v>210</v>
+      </c>
       <c r="AB201" s="3"/>
       <c r="AC201" s="3"/>
       <c r="AD201" s="3"/>
@@ -15570,13 +15866,13 @@
         <v>42</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D202" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>76</v>
@@ -15606,20 +15902,20 @@
         <v>50</v>
       </c>
       <c r="S202" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="T202" s="3">
         <v>15</v>
       </c>
       <c r="U202" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V202" s="3"/>
       <c r="W202" s="3"/>
       <c r="X202" s="3"/>
-      <c r="Y202" s="3"/>
-      <c r="Z202" s="4"/>
-      <c r="AA202" s="4"/>
+      <c r="Y202" s="7"/>
+      <c r="Z202" s="6"/>
+      <c r="AA202" s="6"/>
       <c r="AB202" s="3"/>
       <c r="AC202" s="3"/>
       <c r="AD202" s="3"/>
@@ -15644,7 +15940,7 @@
         <v>79</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="3"/>
@@ -15665,7 +15961,7 @@
         <v>9</v>
       </c>
       <c r="P203" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Q203" s="3">
         <v>1</v>
@@ -15674,21 +15970,21 @@
         <v>50</v>
       </c>
       <c r="S203" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="T203" s="3">
         <v>15</v>
       </c>
       <c r="U203" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V203" s="3"/>
       <c r="W203" s="3"/>
       <c r="X203" s="3"/>
-      <c r="Y203" s="3"/>
-      <c r="Z203" s="4"/>
-      <c r="AA203" s="4"/>
-      <c r="AB203" s="3"/>
+      <c r="Y203" s="7"/>
+      <c r="Z203" s="6"/>
+      <c r="AA203" s="6"/>
+      <c r="AB203" s="7"/>
       <c r="AC203" s="3"/>
       <c r="AD203" s="3"/>
       <c r="AE203" s="3"/>
@@ -15706,7 +16002,7 @@
         <v>42</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D204" s="3" t="s">
         <v>79</v>
@@ -15750,15 +16046,15 @@
         <v>50</v>
       </c>
       <c r="U204" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V204" s="3"/>
       <c r="W204" s="3"/>
       <c r="X204" s="3"/>
-      <c r="Y204" s="3"/>
-      <c r="Z204" s="4"/>
-      <c r="AA204" s="4"/>
-      <c r="AB204" s="3"/>
+      <c r="Y204" s="7"/>
+      <c r="Z204" s="6"/>
+      <c r="AA204" s="6"/>
+      <c r="AB204" s="7"/>
       <c r="AC204" s="3"/>
       <c r="AD204" s="3"/>
       <c r="AE204" s="3"/>
@@ -15776,16 +16072,16 @@
         <v>42</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D205" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G205" s="3"/>
       <c r="H205" s="3" t="s">
@@ -15820,15 +16116,15 @@
         <v>85</v>
       </c>
       <c r="U205" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V205" s="3"/>
       <c r="W205" s="3"/>
       <c r="X205" s="3"/>
       <c r="Y205" s="3"/>
-      <c r="Z205" s="4"/>
-      <c r="AA205" s="4"/>
-      <c r="AB205" s="3"/>
+      <c r="Z205" s="6"/>
+      <c r="AA205" s="6"/>
+      <c r="AB205" s="7"/>
       <c r="AC205" s="3"/>
       <c r="AD205" s="3"/>
       <c r="AE205" s="3"/>
@@ -15846,7 +16142,7 @@
         <v>42</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>79</v>
@@ -15867,7 +16163,7 @@
       </c>
       <c r="K206" s="3"/>
       <c r="L206" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="M206" s="3" t="s">
         <v>64</v>
@@ -15890,22 +16186,22 @@
         <v>85</v>
       </c>
       <c r="U206" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V206" s="3"/>
       <c r="W206" s="3"/>
       <c r="X206" s="3"/>
       <c r="Y206" s="3"/>
-      <c r="Z206" s="4"/>
-      <c r="AA206" s="4"/>
-      <c r="AB206" s="3"/>
+      <c r="Z206" s="6"/>
+      <c r="AA206" s="6"/>
+      <c r="AB206" s="7"/>
       <c r="AC206" s="3"/>
       <c r="AD206" s="3"/>
       <c r="AE206" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AF206" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AG206" s="3"/>
       <c r="AH206" s="3"/>
@@ -15920,7 +16216,7 @@
         <v>42</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D207" s="3" t="s">
         <v>79</v>
@@ -15941,7 +16237,7 @@
       </c>
       <c r="K207" s="3"/>
       <c r="L207" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M207" s="3" t="s">
         <v>64</v>
@@ -15964,22 +16260,22 @@
         <v>85</v>
       </c>
       <c r="U207" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V207" s="3"/>
       <c r="W207" s="3"/>
       <c r="X207" s="3"/>
       <c r="Y207" s="3"/>
-      <c r="Z207" s="4"/>
-      <c r="AA207" s="4"/>
-      <c r="AB207" s="3"/>
+      <c r="Z207" s="6"/>
+      <c r="AA207" s="6"/>
+      <c r="AB207" s="7"/>
       <c r="AC207" s="3"/>
       <c r="AD207" s="3"/>
       <c r="AE207" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF207" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="AF207" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="AG207" s="3"/>
       <c r="AH207" s="3"/>
@@ -15994,7 +16290,7 @@
         <v>42</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D208" s="3" t="s">
         <v>79</v>
@@ -16044,9 +16340,9 @@
       <c r="W208" s="3"/>
       <c r="X208" s="3"/>
       <c r="Y208" s="3"/>
-      <c r="Z208" s="4"/>
-      <c r="AA208" s="4"/>
-      <c r="AB208" s="3"/>
+      <c r="Z208" s="6"/>
+      <c r="AA208" s="6"/>
+      <c r="AB208" s="7"/>
       <c r="AC208" s="3"/>
       <c r="AD208" s="3"/>
       <c r="AE208" s="3"/>
@@ -16064,13 +16360,13 @@
         <v>42</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D209" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>76</v>
@@ -16114,9 +16410,9 @@
       <c r="W209" s="3"/>
       <c r="X209" s="3"/>
       <c r="Y209" s="3"/>
-      <c r="Z209" s="4"/>
-      <c r="AA209" s="4"/>
-      <c r="AB209" s="3"/>
+      <c r="Z209" s="6"/>
+      <c r="AA209" s="6"/>
+      <c r="AB209" s="7"/>
       <c r="AC209" s="3"/>
       <c r="AD209" s="3"/>
       <c r="AE209" s="3"/>
@@ -16134,13 +16430,13 @@
         <v>42</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D210" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="3"/>
@@ -16182,9 +16478,9 @@
       <c r="W210" s="3"/>
       <c r="X210" s="3"/>
       <c r="Y210" s="3"/>
-      <c r="Z210" s="4"/>
-      <c r="AA210" s="4"/>
-      <c r="AB210" s="3"/>
+      <c r="Z210" s="6"/>
+      <c r="AA210" s="6"/>
+      <c r="AB210" s="7"/>
       <c r="AC210" s="3"/>
       <c r="AD210" s="3"/>
       <c r="AE210" s="3"/>
@@ -16202,13 +16498,13 @@
         <v>42</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D211" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F211" s="3"/>
       <c r="G211" s="3"/>
@@ -16250,9 +16546,9 @@
       <c r="W211" s="3"/>
       <c r="X211" s="3"/>
       <c r="Y211" s="3"/>
-      <c r="Z211" s="4"/>
-      <c r="AA211" s="4"/>
-      <c r="AB211" s="3"/>
+      <c r="Z211" s="6"/>
+      <c r="AA211" s="6"/>
+      <c r="AB211" s="7"/>
       <c r="AC211" s="3"/>
       <c r="AD211" s="3"/>
       <c r="AE211" s="3"/>
@@ -16270,13 +16566,13 @@
         <v>42</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D212" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F212" s="3"/>
       <c r="G212" s="3"/>
@@ -16318,9 +16614,9 @@
       <c r="W212" s="3"/>
       <c r="X212" s="3"/>
       <c r="Y212" s="3"/>
-      <c r="Z212" s="4"/>
-      <c r="AA212" s="4"/>
-      <c r="AB212" s="3"/>
+      <c r="Z212" s="6"/>
+      <c r="AA212" s="6"/>
+      <c r="AB212" s="7"/>
       <c r="AC212" s="3"/>
       <c r="AD212" s="3"/>
       <c r="AE212" s="3"/>
@@ -16338,13 +16634,13 @@
         <v>42</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D213" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F213" s="3"/>
       <c r="G213" s="3"/>
@@ -16386,9 +16682,9 @@
       <c r="W213" s="3"/>
       <c r="X213" s="3"/>
       <c r="Y213" s="3"/>
-      <c r="Z213" s="4"/>
-      <c r="AA213" s="4"/>
-      <c r="AB213" s="3"/>
+      <c r="Z213" s="6"/>
+      <c r="AA213" s="6"/>
+      <c r="AB213" s="7"/>
       <c r="AC213" s="3"/>
       <c r="AD213" s="3"/>
       <c r="AE213" s="3"/>
@@ -16406,13 +16702,13 @@
         <v>42</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D214" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>76</v>
@@ -16450,15 +16746,15 @@
         <v>85</v>
       </c>
       <c r="U214" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V214" s="3"/>
       <c r="W214" s="3"/>
       <c r="X214" s="3"/>
       <c r="Y214" s="3"/>
-      <c r="Z214" s="4"/>
-      <c r="AA214" s="4"/>
-      <c r="AB214" s="3"/>
+      <c r="Z214" s="6"/>
+      <c r="AA214" s="6"/>
+      <c r="AB214" s="7"/>
       <c r="AC214" s="3"/>
       <c r="AD214" s="3"/>
       <c r="AE214" s="3"/>
@@ -16476,13 +16772,13 @@
         <v>42</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D215" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>76</v>
@@ -16520,15 +16816,15 @@
         <v>50</v>
       </c>
       <c r="U215" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V215" s="3"/>
       <c r="W215" s="3"/>
       <c r="X215" s="3"/>
       <c r="Y215" s="3"/>
-      <c r="Z215" s="4"/>
-      <c r="AA215" s="4"/>
-      <c r="AB215" s="3"/>
+      <c r="Z215" s="6"/>
+      <c r="AA215" s="6"/>
+      <c r="AB215" s="7"/>
       <c r="AC215" s="3"/>
       <c r="AD215" s="3"/>
       <c r="AE215" s="3"/>
@@ -16546,7 +16842,7 @@
         <v>42</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D216" s="3" t="s">
         <v>43</v>
@@ -16596,9 +16892,9 @@
       <c r="W216" s="3"/>
       <c r="X216" s="3"/>
       <c r="Y216" s="3"/>
-      <c r="Z216" s="4"/>
-      <c r="AA216" s="4"/>
-      <c r="AB216" s="3"/>
+      <c r="Z216" s="6"/>
+      <c r="AA216" s="6"/>
+      <c r="AB216" s="7"/>
       <c r="AC216" s="3"/>
       <c r="AD216" s="3"/>
       <c r="AE216" s="3"/>
@@ -16616,13 +16912,13 @@
         <v>42</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>76</v>
@@ -16666,9 +16962,9 @@
       <c r="W217" s="3"/>
       <c r="X217" s="3"/>
       <c r="Y217" s="3"/>
-      <c r="Z217" s="4"/>
-      <c r="AA217" s="4"/>
-      <c r="AB217" s="3"/>
+      <c r="Z217" s="6"/>
+      <c r="AA217" s="6"/>
+      <c r="AB217" s="7"/>
       <c r="AC217" s="3"/>
       <c r="AD217" s="3"/>
       <c r="AE217" s="3"/>
@@ -16686,13 +16982,13 @@
         <v>42</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="3"/>
@@ -16734,9 +17030,9 @@
       <c r="W218" s="3"/>
       <c r="X218" s="3"/>
       <c r="Y218" s="3"/>
-      <c r="Z218" s="4"/>
-      <c r="AA218" s="4"/>
-      <c r="AB218" s="3"/>
+      <c r="Z218" s="6"/>
+      <c r="AA218" s="6"/>
+      <c r="AB218" s="7"/>
       <c r="AC218" s="3"/>
       <c r="AD218" s="3"/>
       <c r="AE218" s="3"/>
@@ -16754,13 +17050,13 @@
         <v>42</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D219" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="3"/>
@@ -16802,9 +17098,9 @@
       <c r="W219" s="3"/>
       <c r="X219" s="3"/>
       <c r="Y219" s="3"/>
-      <c r="Z219" s="4"/>
-      <c r="AA219" s="4"/>
-      <c r="AB219" s="3"/>
+      <c r="Z219" s="6"/>
+      <c r="AA219" s="6"/>
+      <c r="AB219" s="7"/>
       <c r="AC219" s="3"/>
       <c r="AD219" s="3"/>
       <c r="AE219" s="3"/>
@@ -16822,13 +17118,13 @@
         <v>42</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D220" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="3"/>
@@ -16870,9 +17166,9 @@
       <c r="W220" s="3"/>
       <c r="X220" s="3"/>
       <c r="Y220" s="3"/>
-      <c r="Z220" s="4"/>
-      <c r="AA220" s="4"/>
-      <c r="AB220" s="3"/>
+      <c r="Z220" s="6"/>
+      <c r="AA220" s="6"/>
+      <c r="AB220" s="7"/>
       <c r="AC220" s="3"/>
       <c r="AD220" s="3"/>
       <c r="AE220" s="3"/>
@@ -16890,13 +17186,13 @@
         <v>42</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D221" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="3"/>
@@ -16938,9 +17234,9 @@
       <c r="W221" s="3"/>
       <c r="X221" s="3"/>
       <c r="Y221" s="3"/>
-      <c r="Z221" s="4"/>
-      <c r="AA221" s="4"/>
-      <c r="AB221" s="3"/>
+      <c r="Z221" s="6"/>
+      <c r="AA221" s="6"/>
+      <c r="AB221" s="7"/>
       <c r="AC221" s="3"/>
       <c r="AD221" s="3"/>
       <c r="AE221" s="3"/>
@@ -16958,13 +17254,13 @@
         <v>42</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D222" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>76</v>
@@ -17002,15 +17298,15 @@
         <v>85</v>
       </c>
       <c r="U222" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V222" s="3"/>
       <c r="W222" s="3"/>
       <c r="X222" s="3"/>
       <c r="Y222" s="3"/>
-      <c r="Z222" s="4"/>
-      <c r="AA222" s="4"/>
-      <c r="AB222" s="3"/>
+      <c r="Z222" s="6"/>
+      <c r="AA222" s="6"/>
+      <c r="AB222" s="7"/>
       <c r="AC222" s="3"/>
       <c r="AD222" s="3"/>
       <c r="AE222" s="3"/>
@@ -17028,13 +17324,13 @@
         <v>42</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D223" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>76</v>
@@ -17072,15 +17368,15 @@
         <v>50</v>
       </c>
       <c r="U223" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V223" s="3"/>
       <c r="W223" s="3"/>
       <c r="X223" s="3"/>
       <c r="Y223" s="3"/>
-      <c r="Z223" s="4"/>
-      <c r="AA223" s="4"/>
-      <c r="AB223" s="3"/>
+      <c r="Z223" s="6"/>
+      <c r="AA223" s="6"/>
+      <c r="AB223" s="7"/>
       <c r="AC223" s="3"/>
       <c r="AD223" s="3"/>
       <c r="AE223" s="3"/>
@@ -17098,7 +17394,7 @@
         <v>42</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D224" s="3" t="s">
         <v>54</v>
@@ -17148,9 +17444,9 @@
       <c r="W224" s="3"/>
       <c r="X224" s="3"/>
       <c r="Y224" s="3"/>
-      <c r="Z224" s="4"/>
-      <c r="AA224" s="4"/>
-      <c r="AB224" s="3"/>
+      <c r="Z224" s="6"/>
+      <c r="AA224" s="6"/>
+      <c r="AB224" s="7"/>
       <c r="AC224" s="3"/>
       <c r="AD224" s="3"/>
       <c r="AE224" s="3"/>
@@ -17168,13 +17464,13 @@
         <v>42</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D225" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>76</v>
@@ -17218,9 +17514,9 @@
       <c r="W225" s="3"/>
       <c r="X225" s="3"/>
       <c r="Y225" s="3"/>
-      <c r="Z225" s="4"/>
-      <c r="AA225" s="4"/>
-      <c r="AB225" s="3"/>
+      <c r="Z225" s="6"/>
+      <c r="AA225" s="6"/>
+      <c r="AB225" s="7"/>
       <c r="AC225" s="3"/>
       <c r="AD225" s="3"/>
       <c r="AE225" s="3"/>
@@ -17238,13 +17534,13 @@
         <v>42</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D226" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F226" s="3"/>
       <c r="G226" s="3"/>
@@ -17286,9 +17582,9 @@
       <c r="W226" s="3"/>
       <c r="X226" s="3"/>
       <c r="Y226" s="3"/>
-      <c r="Z226" s="4"/>
-      <c r="AA226" s="4"/>
-      <c r="AB226" s="3"/>
+      <c r="Z226" s="6"/>
+      <c r="AA226" s="6"/>
+      <c r="AB226" s="7"/>
       <c r="AC226" s="3"/>
       <c r="AD226" s="3"/>
       <c r="AE226" s="3"/>
@@ -17306,13 +17602,13 @@
         <v>42</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="3"/>
@@ -17354,9 +17650,9 @@
       <c r="W227" s="3"/>
       <c r="X227" s="3"/>
       <c r="Y227" s="3"/>
-      <c r="Z227" s="4"/>
-      <c r="AA227" s="4"/>
-      <c r="AB227" s="3"/>
+      <c r="Z227" s="6"/>
+      <c r="AA227" s="6"/>
+      <c r="AB227" s="7"/>
       <c r="AC227" s="3"/>
       <c r="AD227" s="3"/>
       <c r="AE227" s="3"/>
@@ -17374,13 +17670,13 @@
         <v>42</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D228" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="3"/>
@@ -17442,13 +17738,13 @@
         <v>42</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F229" s="3"/>
       <c r="G229" s="3"/>
@@ -17510,13 +17806,13 @@
         <v>42</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D230" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>76</v>
@@ -17554,7 +17850,7 @@
         <v>85</v>
       </c>
       <c r="U230" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V230" s="3"/>
       <c r="W230" s="3"/>
@@ -17580,13 +17876,13 @@
         <v>42</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>76</v>
@@ -17624,7 +17920,7 @@
         <v>50</v>
       </c>
       <c r="U231" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V231" s="3"/>
       <c r="W231" s="3"/>
@@ -17650,13 +17946,13 @@
         <v>42</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D232" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="3"/>
@@ -17718,13 +18014,13 @@
         <v>42</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="3"/>
@@ -17786,13 +18082,13 @@
         <v>42</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D234" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="3"/>
@@ -17854,13 +18150,13 @@
         <v>42</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D235" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F235" s="3"/>
       <c r="G235" s="3"/>
@@ -17922,13 +18218,13 @@
         <v>42</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D236" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>76</v>
@@ -17966,7 +18262,7 @@
         <v>85</v>
       </c>
       <c r="U236" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V236" s="3"/>
       <c r="W236" s="3"/>
@@ -18070,7 +18366,7 @@
         <v>42</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D238" s="3" t="s">
         <v>53</v>
@@ -18148,7 +18444,7 @@
         <v>42</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D239" s="3" t="s">
         <v>53</v>
@@ -18218,13 +18514,13 @@
         <v>42</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D240" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="3"/>
@@ -18237,7 +18533,7 @@
       </c>
       <c r="K240" s="3"/>
       <c r="L240" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M240" s="3" t="s">
         <v>64</v>
@@ -18275,7 +18571,7 @@
         <v>73</v>
       </c>
       <c r="AF240" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AG240" s="3"/>
       <c r="AH240" s="3"/>
@@ -18296,13 +18592,13 @@
         <v>42</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D241" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F241" s="3"/>
       <c r="G241" s="3"/>
@@ -18315,7 +18611,7 @@
       </c>
       <c r="K241" s="3"/>
       <c r="L241" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M241" s="3" t="s">
         <v>64</v>
@@ -18353,7 +18649,7 @@
         <v>73</v>
       </c>
       <c r="AF241" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG241" s="3"/>
       <c r="AH241" s="3"/>
@@ -18395,7 +18691,7 @@
       </c>
       <c r="K242" s="3"/>
       <c r="L242" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M242" s="3" t="s">
         <v>64</v>
@@ -18418,7 +18714,7 @@
         <v>50</v>
       </c>
       <c r="U242" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V242" s="3"/>
       <c r="W242" s="3"/>
@@ -18430,10 +18726,10 @@
       <c r="AC242" s="3"/>
       <c r="AD242" s="3"/>
       <c r="AE242" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AF242" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AG242" s="3"/>
       <c r="AH242" s="3"/>
@@ -18475,7 +18771,7 @@
       </c>
       <c r="K243" s="3"/>
       <c r="L243" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M243" s="3" t="s">
         <v>64</v>
@@ -18498,7 +18794,7 @@
         <v>50</v>
       </c>
       <c r="U243" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V243" s="3"/>
       <c r="W243" s="3"/>
@@ -18510,10 +18806,10 @@
       <c r="AC243" s="3"/>
       <c r="AD243" s="3"/>
       <c r="AE243" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AF243" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AG243" s="3"/>
       <c r="AH243" s="3"/>
@@ -18536,13 +18832,13 @@
         <v>42</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D244" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>76</v>
@@ -18580,7 +18876,7 @@
         <v>85</v>
       </c>
       <c r="U244" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V244" s="3"/>
       <c r="W244" s="3"/>
@@ -18606,13 +18902,13 @@
         <v>42</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D245" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>76</v>
@@ -18650,7 +18946,7 @@
         <v>85</v>
       </c>
       <c r="U245" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V245" s="3"/>
       <c r="W245" s="3"/>
@@ -18718,7 +19014,7 @@
         <v>85</v>
       </c>
       <c r="U246" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V246" s="3"/>
       <c r="W246" s="3"/>
@@ -18733,7 +19029,7 @@
         <v>73</v>
       </c>
       <c r="AF246" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AG246" s="3">
         <v>1.101672</v>
@@ -18758,7 +19054,7 @@
         <v>42</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D247" s="3" t="s">
         <v>53</v>
@@ -18800,7 +19096,7 @@
         <v>85</v>
       </c>
       <c r="U247" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V247" s="3"/>
       <c r="W247" s="3"/>
@@ -18815,7 +19111,7 @@
         <v>73</v>
       </c>
       <c r="AF247" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AG247" s="3"/>
       <c r="AH247" s="3"/>
@@ -18836,7 +19132,7 @@
         <v>42</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>53</v>
@@ -18880,7 +19176,7 @@
         <v>85</v>
       </c>
       <c r="U248" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V248" s="3"/>
       <c r="W248" s="3"/>
@@ -18906,13 +19202,13 @@
         <v>42</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D249" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>76</v>
@@ -18948,7 +19244,7 @@
         <v>85</v>
       </c>
       <c r="U249" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V249" s="3"/>
       <c r="W249" s="3"/>
@@ -18963,7 +19259,7 @@
         <v>73</v>
       </c>
       <c r="AF249" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AG249" s="3"/>
       <c r="AH249" s="3"/>
@@ -18984,13 +19280,13 @@
         <v>42</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D250" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>76</v>
@@ -19026,7 +19322,7 @@
         <v>85</v>
       </c>
       <c r="U250" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V250" s="3"/>
       <c r="W250" s="3"/>
@@ -19041,7 +19337,7 @@
         <v>73</v>
       </c>
       <c r="AF250" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AG250" s="3"/>
       <c r="AH250" s="3"/>
@@ -19062,13 +19358,13 @@
         <v>42</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D251" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>70</v>
@@ -19106,7 +19402,7 @@
         <v>50</v>
       </c>
       <c r="U251" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V251" s="3"/>
       <c r="W251" s="3"/>
@@ -19132,13 +19428,13 @@
         <v>42</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D252" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>76</v>
@@ -19174,7 +19470,7 @@
         <v>85</v>
       </c>
       <c r="U252" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V252" s="3"/>
       <c r="W252" s="3"/>
@@ -19189,7 +19485,7 @@
         <v>73</v>
       </c>
       <c r="AF252" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AG252" s="3">
         <v>1.4620299999999999</v>
@@ -19214,13 +19510,13 @@
         <v>42</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D253" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>76</v>
@@ -19256,7 +19552,7 @@
         <v>85</v>
       </c>
       <c r="U253" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V253" s="3"/>
       <c r="W253" s="3"/>
@@ -19271,7 +19567,7 @@
         <v>73</v>
       </c>
       <c r="AF253" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG253" s="3">
         <v>1.4620299999999999</v>
@@ -19296,13 +19592,13 @@
         <v>42</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D254" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>76</v>
@@ -19338,7 +19634,7 @@
         <v>85</v>
       </c>
       <c r="U254" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V254" s="3"/>
       <c r="W254" s="3"/>
@@ -19353,7 +19649,7 @@
         <v>73</v>
       </c>
       <c r="AF254" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AG254" s="3"/>
       <c r="AH254" s="3"/>
@@ -19374,13 +19670,13 @@
         <v>42</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D255" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>76</v>
@@ -19416,7 +19712,7 @@
         <v>85</v>
       </c>
       <c r="U255" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V255" s="3"/>
       <c r="W255" s="3"/>
@@ -19431,7 +19727,7 @@
         <v>73</v>
       </c>
       <c r="AF255" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG255" s="3"/>
       <c r="AH255" s="3"/>
@@ -19452,13 +19748,13 @@
         <v>42</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D256" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>70</v>
@@ -19496,7 +19792,7 @@
         <v>50</v>
       </c>
       <c r="U256" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V256" s="3"/>
       <c r="W256" s="3"/>
@@ -19522,13 +19818,13 @@
         <v>42</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D257" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>76</v>
@@ -19564,7 +19860,7 @@
         <v>85</v>
       </c>
       <c r="U257" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V257" s="3"/>
       <c r="W257" s="3"/>
@@ -19579,7 +19875,7 @@
         <v>73</v>
       </c>
       <c r="AF257" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AG257" s="3"/>
       <c r="AH257" s="3"/>
@@ -19600,13 +19896,13 @@
         <v>42</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D258" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>76</v>
@@ -19642,7 +19938,7 @@
         <v>85</v>
       </c>
       <c r="U258" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V258" s="3"/>
       <c r="W258" s="3"/>
@@ -19657,7 +19953,7 @@
         <v>73</v>
       </c>
       <c r="AF258" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AG258" s="3"/>
       <c r="AH258" s="3"/>
@@ -19678,13 +19974,13 @@
         <v>42</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D259" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>76</v>
@@ -19722,7 +20018,7 @@
         <v>85</v>
       </c>
       <c r="U259" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V259" s="3"/>
       <c r="W259" s="3"/>
@@ -19748,13 +20044,13 @@
         <v>42</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D260" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>76</v>
@@ -19792,7 +20088,7 @@
         <v>85</v>
       </c>
       <c r="U260" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V260" s="3"/>
       <c r="W260" s="3"/>
@@ -19818,13 +20114,13 @@
         <v>42</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D261" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>76</v>
@@ -19860,7 +20156,7 @@
         <v>85</v>
       </c>
       <c r="U261" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V261" s="3"/>
       <c r="W261" s="3"/>
@@ -19875,7 +20171,7 @@
         <v>73</v>
       </c>
       <c r="AF261" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG261" s="3"/>
       <c r="AH261" s="3"/>
@@ -19896,13 +20192,13 @@
         <v>42</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D262" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>76</v>
@@ -19938,7 +20234,7 @@
         <v>85</v>
       </c>
       <c r="U262" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V262" s="3"/>
       <c r="W262" s="3"/>
@@ -19953,7 +20249,7 @@
         <v>73</v>
       </c>
       <c r="AF262" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AG262" s="3"/>
       <c r="AH262" s="3"/>
@@ -19974,13 +20270,13 @@
         <v>42</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D263" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>76</v>
@@ -20018,7 +20314,7 @@
         <v>85</v>
       </c>
       <c r="U263" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V263" s="3"/>
       <c r="W263" s="3"/>
@@ -20044,13 +20340,13 @@
         <v>42</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D264" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>76</v>
@@ -20086,7 +20382,7 @@
         <v>85</v>
       </c>
       <c r="U264" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V264" s="3"/>
       <c r="W264" s="3"/>
@@ -20101,7 +20397,7 @@
         <v>73</v>
       </c>
       <c r="AF264" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG264" s="3"/>
       <c r="AH264" s="3"/>
@@ -20122,13 +20418,13 @@
         <v>42</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D265" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>76</v>
@@ -20164,7 +20460,7 @@
         <v>85</v>
       </c>
       <c r="U265" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V265" s="3"/>
       <c r="W265" s="3"/>
@@ -20179,7 +20475,7 @@
         <v>73</v>
       </c>
       <c r="AF265" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AG265" s="3"/>
       <c r="AH265" s="3"/>
@@ -20200,13 +20496,13 @@
         <v>42</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D266" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>76</v>
@@ -20242,7 +20538,7 @@
         <v>85</v>
       </c>
       <c r="U266" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V266" s="3"/>
       <c r="W266" s="3"/>
@@ -20257,7 +20553,7 @@
         <v>73</v>
       </c>
       <c r="AF266" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG266" s="3"/>
       <c r="AH266" s="3"/>
@@ -20278,13 +20574,13 @@
         <v>42</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D267" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>76</v>
@@ -20320,7 +20616,7 @@
         <v>85</v>
       </c>
       <c r="U267" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V267" s="3"/>
       <c r="W267" s="3"/>
@@ -20335,7 +20631,7 @@
         <v>73</v>
       </c>
       <c r="AF267" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG267" s="3"/>
       <c r="AH267" s="3"/>
@@ -20352,5 +20648,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="AA25 AA186:AA194 AA41:AA53" twoDigitTextYear="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/inst/extdata/colorado_criteria_crosswalk.xlsx
+++ b/inst/extdata/colorado_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/sheila_saia_tetratech_com/Documents/Documents/github/TADACommunityHub/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{CD77611A-A625-4F3B-80D2-923462D5119F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FDA45C8-46DF-45DA-9BDF-43F283F3B38C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4797DA0B-16B5-46BD-9B2A-C79FCACDBD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{380839A1-A469-4C26-93CF-5FD0D1BCA51C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{380839A1-A469-4C26-93CF-5FD0D1BCA51C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -350,9 +350,6 @@
     <t>ESCHERICHIA COLI</t>
   </si>
   <si>
-    <t>#/100mL</t>
-  </si>
-  <si>
     <t>n-month</t>
   </si>
   <si>
@@ -687,6 +684,9 @@
   </si>
   <si>
     <t>Feb 28</t>
+  </si>
+  <si>
+    <t>CFU/100ML</t>
   </si>
 </sst>
 </file>
@@ -1099,17 +1099,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F27C99-86A4-42C9-ADFF-84FEE74EA84D}">
   <dimension ref="A1:AP267"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="5"/>
-    <col min="3" max="3" width="24.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="24" width="9.140625" style="5"/>
-    <col min="25" max="25" width="10.5703125" style="5" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="2" width="9.1796875" style="5"/>
+    <col min="3" max="3" width="24.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="24" width="9.1796875" style="5"/>
+    <col min="25" max="25" width="10.54296875" style="5" customWidth="1"/>
+    <col min="26" max="16384" width="9.1796875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1237,13 +1237,13 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>43</v>
@@ -1307,13 +1307,13 @@
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
     </row>
-    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>53</v>
@@ -1377,13 +1377,13 @@
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
     </row>
-    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>54</v>
@@ -1447,7 +1447,7 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
     </row>
-    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>42</v>
@@ -1515,7 +1515,7 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
     </row>
-    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>42</v>
@@ -1583,7 +1583,7 @@
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
     </row>
-    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>42</v>
@@ -1651,7 +1651,7 @@
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
     </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>42</v>
@@ -1719,7 +1719,7 @@
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
     </row>
-    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>42</v>
@@ -1787,7 +1787,7 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
     </row>
-    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>42</v>
@@ -1855,13 +1855,13 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
     </row>
-    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>57</v>
@@ -1923,13 +1923,13 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>58</v>
@@ -1991,13 +1991,13 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
     </row>
-    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>57</v>
@@ -2059,13 +2059,13 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
     </row>
-    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>58</v>
@@ -2127,13 +2127,13 @@
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
     </row>
-    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>43</v>
@@ -2211,13 +2211,13 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>53</v>
@@ -2295,13 +2295,13 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>54</v>
@@ -2379,7 +2379,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>42</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AL18" s="3"/>
     </row>
-    <row r="19" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>42</v>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>42</v>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="AL20" s="3"/>
     </row>
-    <row r="21" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>42</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AL21" s="3"/>
     </row>
-    <row r="22" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>42</v>
@@ -2789,13 +2789,13 @@
       </c>
       <c r="AL22" s="3"/>
     </row>
-    <row r="23" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>43</v>
@@ -2867,13 +2867,13 @@
       </c>
       <c r="AL23" s="3"/>
     </row>
-    <row r="24" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>43</v>
@@ -2937,7 +2937,7 @@
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
     </row>
-    <row r="25" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>42</v>
@@ -2993,13 +2993,13 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Z25" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AA25" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AB25" s="3"/>
       <c r="AC25" s="3"/>
@@ -3013,7 +3013,7 @@
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
     </row>
-    <row r="26" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>42</v>
@@ -3072,10 +3072,10 @@
         <v>90</v>
       </c>
       <c r="Z26" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AA26" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
@@ -3089,7 +3089,7 @@
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
     </row>
-    <row r="27" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>42</v>
@@ -3148,10 +3148,10 @@
         <v>91</v>
       </c>
       <c r="Z27" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA27" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AB27" s="3"/>
       <c r="AC27" s="3"/>
@@ -3165,7 +3165,7 @@
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
     </row>
-    <row r="28" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>42</v>
@@ -3224,10 +3224,10 @@
         <v>93</v>
       </c>
       <c r="Z28" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AA28" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
@@ -3241,7 +3241,7 @@
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
     </row>
-    <row r="29" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>42</v>
@@ -3300,10 +3300,10 @@
         <v>94</v>
       </c>
       <c r="Z29" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA29" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
@@ -3317,7 +3317,7 @@
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
-    <row r="30" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>42</v>
@@ -3376,10 +3376,10 @@
         <v>96</v>
       </c>
       <c r="Z30" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AA30" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB30" s="3"/>
       <c r="AC30" s="3"/>
@@ -3393,7 +3393,7 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
     </row>
-    <row r="31" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>42</v>
@@ -3452,10 +3452,10 @@
         <v>94</v>
       </c>
       <c r="Z31" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA31" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB31" s="3"/>
       <c r="AC31" s="3"/>
@@ -3469,7 +3469,7 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
     </row>
-    <row r="32" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>42</v>
@@ -3528,10 +3528,10 @@
         <v>96</v>
       </c>
       <c r="Z32" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AA32" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB32" s="3"/>
       <c r="AC32" s="3"/>
@@ -3545,7 +3545,7 @@
       <c r="AK32" s="3"/>
       <c r="AL32" s="3"/>
     </row>
-    <row r="33" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>42</v>
@@ -3604,10 +3604,10 @@
         <v>98</v>
       </c>
       <c r="Z33" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AA33" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AB33" s="3"/>
       <c r="AC33" s="3"/>
@@ -3621,7 +3621,7 @@
       <c r="AK33" s="3"/>
       <c r="AL33" s="3"/>
     </row>
-    <row r="34" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>42</v>
@@ -3680,10 +3680,10 @@
         <v>99</v>
       </c>
       <c r="Z34" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AA34" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AB34" s="3"/>
       <c r="AC34" s="3"/>
@@ -3697,7 +3697,7 @@
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
     </row>
-    <row r="35" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>42</v>
@@ -3756,10 +3756,10 @@
         <v>98</v>
       </c>
       <c r="Z35" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AA35" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
@@ -3773,7 +3773,7 @@
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
     </row>
-    <row r="36" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>42</v>
@@ -3832,10 +3832,10 @@
         <v>99</v>
       </c>
       <c r="Z36" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AA36" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AB36" s="3"/>
       <c r="AC36" s="3"/>
@@ -3849,7 +3849,7 @@
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
     </row>
-    <row r="37" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>42</v>
@@ -3908,10 +3908,10 @@
         <v>98</v>
       </c>
       <c r="Z37" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AA37" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
@@ -3925,7 +3925,7 @@
       <c r="AK37" s="3"/>
       <c r="AL37" s="3"/>
     </row>
-    <row r="38" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
         <v>42</v>
@@ -3984,10 +3984,10 @@
         <v>99</v>
       </c>
       <c r="Z38" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AA38" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
@@ -4001,7 +4001,7 @@
       <c r="AK38" s="3"/>
       <c r="AL38" s="3"/>
     </row>
-    <row r="39" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>42</v>
@@ -4060,10 +4060,10 @@
         <v>94</v>
       </c>
       <c r="Z39" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA39" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
@@ -4077,7 +4077,7 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
         <v>42</v>
@@ -4136,10 +4136,10 @@
         <v>96</v>
       </c>
       <c r="Z40" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AA40" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
@@ -4153,7 +4153,7 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>42</v>
@@ -4209,13 +4209,13 @@
       <c r="W41" s="3"/>
       <c r="X41" s="3"/>
       <c r="Y41" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Z41" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AA41" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AB41" s="3"/>
       <c r="AC41" s="3"/>
@@ -4229,7 +4229,7 @@
       <c r="AK41" s="3"/>
       <c r="AL41" s="3"/>
     </row>
-    <row r="42" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>42</v>
@@ -4288,10 +4288,10 @@
         <v>90</v>
       </c>
       <c r="Z42" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AA42" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AB42" s="3"/>
       <c r="AC42" s="3"/>
@@ -4305,7 +4305,7 @@
       <c r="AK42" s="3"/>
       <c r="AL42" s="3"/>
     </row>
-    <row r="43" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>42</v>
@@ -4364,10 +4364,10 @@
         <v>91</v>
       </c>
       <c r="Z43" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA43" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AB43" s="3"/>
       <c r="AC43" s="3"/>
@@ -4381,7 +4381,7 @@
       <c r="AK43" s="3"/>
       <c r="AL43" s="3"/>
     </row>
-    <row r="44" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
         <v>42</v>
@@ -4440,10 +4440,10 @@
         <v>93</v>
       </c>
       <c r="Z44" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AA44" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB44" s="3"/>
       <c r="AC44" s="3"/>
@@ -4457,7 +4457,7 @@
       <c r="AK44" s="3"/>
       <c r="AL44" s="3"/>
     </row>
-    <row r="45" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>42</v>
@@ -4516,10 +4516,10 @@
         <v>94</v>
       </c>
       <c r="Z45" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA45" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB45" s="3"/>
       <c r="AC45" s="3"/>
@@ -4533,7 +4533,7 @@
       <c r="AK45" s="3"/>
       <c r="AL45" s="3"/>
     </row>
-    <row r="46" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
         <v>42</v>
@@ -4592,10 +4592,10 @@
         <v>96</v>
       </c>
       <c r="Z46" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AA46" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB46" s="3"/>
       <c r="AC46" s="3"/>
@@ -4609,7 +4609,7 @@
       <c r="AK46" s="3"/>
       <c r="AL46" s="3"/>
     </row>
-    <row r="47" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>42</v>
@@ -4668,10 +4668,10 @@
         <v>94</v>
       </c>
       <c r="Z47" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA47" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB47" s="3"/>
       <c r="AC47" s="3"/>
@@ -4685,7 +4685,7 @@
       <c r="AK47" s="3"/>
       <c r="AL47" s="3"/>
     </row>
-    <row r="48" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
         <v>42</v>
@@ -4744,10 +4744,10 @@
         <v>96</v>
       </c>
       <c r="Z48" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AA48" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB48" s="3"/>
       <c r="AC48" s="3"/>
@@ -4761,7 +4761,7 @@
       <c r="AK48" s="3"/>
       <c r="AL48" s="3"/>
     </row>
-    <row r="49" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
         <v>42</v>
@@ -4817,13 +4817,13 @@
       <c r="W49" s="3"/>
       <c r="X49" s="3"/>
       <c r="Y49" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Z49" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AA49" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AB49" s="3"/>
       <c r="AC49" s="3"/>
@@ -4837,7 +4837,7 @@
       <c r="AK49" s="3"/>
       <c r="AL49" s="3"/>
     </row>
-    <row r="50" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
         <v>42</v>
@@ -4896,10 +4896,10 @@
         <v>90</v>
       </c>
       <c r="Z50" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AA50" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AB50" s="3"/>
       <c r="AC50" s="3"/>
@@ -4913,7 +4913,7 @@
       <c r="AK50" s="3"/>
       <c r="AL50" s="3"/>
     </row>
-    <row r="51" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
         <v>42</v>
@@ -4972,10 +4972,10 @@
         <v>91</v>
       </c>
       <c r="Z51" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA51" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AB51" s="3"/>
       <c r="AC51" s="3"/>
@@ -4989,7 +4989,7 @@
       <c r="AK51" s="3"/>
       <c r="AL51" s="3"/>
     </row>
-    <row r="52" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
         <v>42</v>
@@ -5048,10 +5048,10 @@
         <v>93</v>
       </c>
       <c r="Z52" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AA52" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB52" s="3"/>
       <c r="AC52" s="3"/>
@@ -5065,7 +5065,7 @@
       <c r="AK52" s="3"/>
       <c r="AL52" s="3"/>
     </row>
-    <row r="53" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
         <v>42</v>
@@ -5124,10 +5124,10 @@
         <v>94</v>
       </c>
       <c r="Z53" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA53" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB53" s="3"/>
       <c r="AC53" s="3"/>
@@ -5141,7 +5141,7 @@
       <c r="AK53" s="3"/>
       <c r="AL53" s="3"/>
     </row>
-    <row r="54" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
         <v>42</v>
@@ -5200,10 +5200,10 @@
         <v>96</v>
       </c>
       <c r="Z54" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AA54" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB54" s="3"/>
       <c r="AC54" s="3"/>
@@ -5217,7 +5217,7 @@
       <c r="AK54" s="3"/>
       <c r="AL54" s="3"/>
     </row>
-    <row r="55" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
         <v>42</v>
@@ -5276,10 +5276,10 @@
         <v>94</v>
       </c>
       <c r="Z55" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA55" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
@@ -5293,7 +5293,7 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
         <v>42</v>
@@ -5352,10 +5352,10 @@
         <v>96</v>
       </c>
       <c r="Z56" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AA56" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
@@ -5369,7 +5369,7 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
         <v>42</v>
@@ -5428,10 +5428,10 @@
         <v>98</v>
       </c>
       <c r="Z57" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AA57" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AB57" s="3"/>
       <c r="AC57" s="3"/>
@@ -5445,7 +5445,7 @@
       <c r="AK57" s="3"/>
       <c r="AL57" s="3"/>
     </row>
-    <row r="58" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
         <v>42</v>
@@ -5504,10 +5504,10 @@
         <v>99</v>
       </c>
       <c r="Z58" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AA58" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AB58" s="3"/>
       <c r="AC58" s="3"/>
@@ -5521,7 +5521,7 @@
       <c r="AK58" s="3"/>
       <c r="AL58" s="3"/>
     </row>
-    <row r="59" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
         <v>42</v>
@@ -5580,10 +5580,10 @@
         <v>98</v>
       </c>
       <c r="Z59" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AA59" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AB59" s="3"/>
       <c r="AC59" s="3"/>
@@ -5597,7 +5597,7 @@
       <c r="AK59" s="3"/>
       <c r="AL59" s="3"/>
     </row>
-    <row r="60" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
         <v>42</v>
@@ -5656,10 +5656,10 @@
         <v>99</v>
       </c>
       <c r="Z60" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AA60" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AB60" s="3"/>
       <c r="AC60" s="3"/>
@@ -5673,7 +5673,7 @@
       <c r="AK60" s="3"/>
       <c r="AL60" s="3"/>
     </row>
-    <row r="61" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
         <v>42</v>
@@ -5732,10 +5732,10 @@
         <v>98</v>
       </c>
       <c r="Z61" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AA61" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AB61" s="3"/>
       <c r="AC61" s="3"/>
@@ -5749,7 +5749,7 @@
       <c r="AK61" s="3"/>
       <c r="AL61" s="3"/>
     </row>
-    <row r="62" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
         <v>42</v>
@@ -5808,10 +5808,10 @@
         <v>99</v>
       </c>
       <c r="Z62" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AA62" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AB62" s="3"/>
       <c r="AC62" s="3"/>
@@ -5825,7 +5825,7 @@
       <c r="AK62" s="3"/>
       <c r="AL62" s="3"/>
     </row>
-    <row r="63" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
         <v>42</v>
@@ -5884,10 +5884,10 @@
         <v>94</v>
       </c>
       <c r="Z63" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA63" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB63" s="3"/>
       <c r="AC63" s="3"/>
@@ -5901,7 +5901,7 @@
       <c r="AK63" s="3"/>
       <c r="AL63" s="3"/>
     </row>
-    <row r="64" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
         <v>42</v>
@@ -5960,10 +5960,10 @@
         <v>96</v>
       </c>
       <c r="Z64" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AA64" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB64" s="3"/>
       <c r="AC64" s="3"/>
@@ -5977,7 +5977,7 @@
       <c r="AK64" s="3"/>
       <c r="AL64" s="3"/>
     </row>
-    <row r="65" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
         <v>42</v>
@@ -6033,13 +6033,13 @@
       <c r="W65" s="3"/>
       <c r="X65" s="3"/>
       <c r="Y65" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Z65" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AA65" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AB65" s="3"/>
       <c r="AC65" s="3"/>
@@ -6053,7 +6053,7 @@
       <c r="AK65" s="3"/>
       <c r="AL65" s="3"/>
     </row>
-    <row r="66" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
         <v>42</v>
@@ -6112,10 +6112,10 @@
         <v>90</v>
       </c>
       <c r="Z66" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AA66" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AB66" s="3"/>
       <c r="AC66" s="3"/>
@@ -6129,7 +6129,7 @@
       <c r="AK66" s="3"/>
       <c r="AL66" s="3"/>
     </row>
-    <row r="67" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
         <v>42</v>
@@ -6188,10 +6188,10 @@
         <v>91</v>
       </c>
       <c r="Z67" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA67" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
@@ -6205,7 +6205,7 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
         <v>42</v>
@@ -6264,10 +6264,10 @@
         <v>93</v>
       </c>
       <c r="Z68" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AA68" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB68" s="3"/>
       <c r="AC68" s="3"/>
@@ -6281,7 +6281,7 @@
       <c r="AK68" s="3"/>
       <c r="AL68" s="3"/>
     </row>
-    <row r="69" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
         <v>42</v>
@@ -6340,10 +6340,10 @@
         <v>94</v>
       </c>
       <c r="Z69" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA69" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB69" s="3"/>
       <c r="AC69" s="3"/>
@@ -6357,7 +6357,7 @@
       <c r="AK69" s="3"/>
       <c r="AL69" s="3"/>
     </row>
-    <row r="70" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="3"/>
       <c r="B70" s="3" t="s">
         <v>42</v>
@@ -6416,10 +6416,10 @@
         <v>96</v>
       </c>
       <c r="Z70" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AA70" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB70" s="3"/>
       <c r="AC70" s="3"/>
@@ -6433,7 +6433,7 @@
       <c r="AK70" s="3"/>
       <c r="AL70" s="3"/>
     </row>
-    <row r="71" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
       <c r="B71" s="3" t="s">
         <v>42</v>
@@ -6492,10 +6492,10 @@
         <v>94</v>
       </c>
       <c r="Z71" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA71" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB71" s="3"/>
       <c r="AC71" s="3"/>
@@ -6509,7 +6509,7 @@
       <c r="AK71" s="3"/>
       <c r="AL71" s="3"/>
     </row>
-    <row r="72" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="3"/>
       <c r="B72" s="3" t="s">
         <v>42</v>
@@ -6568,10 +6568,10 @@
         <v>96</v>
       </c>
       <c r="Z72" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AA72" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB72" s="3"/>
       <c r="AC72" s="3"/>
@@ -6585,13 +6585,13 @@
       <c r="AK72" s="3"/>
       <c r="AL72" s="3"/>
     </row>
-    <row r="73" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="3"/>
       <c r="B73" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>102</v>
@@ -6616,16 +6616,16 @@
         <v>126</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>104</v>
+        <v>216</v>
       </c>
       <c r="Q73" s="3">
         <v>2</v>
       </c>
       <c r="R73" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="S73" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="S73" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="T73" s="3">
         <v>1</v>
@@ -6651,16 +6651,16 @@
       <c r="AK73" s="3"/>
       <c r="AL73" s="3"/>
     </row>
-    <row r="74" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
       <c r="B74" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>103</v>
@@ -6682,16 +6682,16 @@
         <v>205</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>104</v>
+        <v>216</v>
       </c>
       <c r="Q74" s="3">
         <v>2</v>
       </c>
       <c r="R74" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="S74" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="S74" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="T74" s="3">
         <v>1</v>
@@ -6717,16 +6717,16 @@
       <c r="AK74" s="3"/>
       <c r="AL74" s="3"/>
     </row>
-    <row r="75" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="3"/>
       <c r="B75" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>103</v>
@@ -6748,16 +6748,16 @@
         <v>630</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>104</v>
+        <v>216</v>
       </c>
       <c r="Q75" s="3">
         <v>2</v>
       </c>
       <c r="R75" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="S75" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="S75" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="T75" s="3">
         <v>1</v>
@@ -6783,13 +6783,13 @@
       <c r="AK75" s="3"/>
       <c r="AL75" s="3"/>
     </row>
-    <row r="76" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="3"/>
       <c r="B76" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>58</v>
@@ -6814,16 +6814,16 @@
         <v>630</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>104</v>
+        <v>216</v>
       </c>
       <c r="Q76" s="3">
         <v>2</v>
       </c>
       <c r="R76" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="S76" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="T76" s="3">
         <v>1</v>
@@ -6849,13 +6849,13 @@
       <c r="AK76" s="3"/>
       <c r="AL76" s="3"/>
     </row>
-    <row r="77" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
       <c r="B77" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>53</v>
@@ -6919,19 +6919,19 @@
       <c r="AK77" s="3"/>
       <c r="AL77" s="3"/>
     </row>
-    <row r="78" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="3"/>
       <c r="B78" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>76</v>
@@ -6989,19 +6989,19 @@
       <c r="AK78" s="3"/>
       <c r="AL78" s="3"/>
     </row>
-    <row r="79" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
       <c r="B79" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
@@ -7057,19 +7057,19 @@
       <c r="AK79" s="3"/>
       <c r="AL79" s="3"/>
     </row>
-    <row r="80" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" s="3"/>
       <c r="B80" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
@@ -7125,19 +7125,19 @@
       <c r="AK80" s="3"/>
       <c r="AL80" s="3"/>
     </row>
-    <row r="81" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="3"/>
       <c r="B81" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
@@ -7193,19 +7193,19 @@
       <c r="AK81" s="3"/>
       <c r="AL81" s="3"/>
     </row>
-    <row r="82" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" s="3"/>
       <c r="B82" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
@@ -7261,19 +7261,19 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
       <c r="B83" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="K83" s="3"/>
       <c r="L83" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>64</v>
@@ -7324,7 +7324,7 @@
         <v>73</v>
       </c>
       <c r="AF83" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG83" s="3"/>
       <c r="AH83" s="3"/>
@@ -7339,19 +7339,19 @@
       </c>
       <c r="AL83" s="3"/>
     </row>
-    <row r="84" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" s="3"/>
       <c r="B84" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
@@ -7406,19 +7406,19 @@
       <c r="AK84" s="3"/>
       <c r="AL84" s="3"/>
     </row>
-    <row r="85" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="3"/>
       <c r="B85" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
@@ -7474,19 +7474,19 @@
       <c r="AK85" s="3"/>
       <c r="AL85" s="3"/>
     </row>
-    <row r="86" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" s="3"/>
       <c r="B86" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="K86" s="3"/>
       <c r="L86" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M86" s="3" t="s">
         <v>64</v>
@@ -7537,7 +7537,7 @@
         <v>73</v>
       </c>
       <c r="AF86" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG86" s="3"/>
       <c r="AH86" s="3"/>
@@ -7552,19 +7552,19 @@
       </c>
       <c r="AL86" s="3"/>
     </row>
-    <row r="87" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
       <c r="B87" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
@@ -7620,19 +7620,19 @@
       <c r="AK87" s="3"/>
       <c r="AL87" s="3"/>
     </row>
-    <row r="88" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" s="3"/>
       <c r="B88" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
@@ -7688,19 +7688,19 @@
       <c r="AK88" s="3"/>
       <c r="AL88" s="3"/>
     </row>
-    <row r="89" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="3"/>
       <c r="B89" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>102</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>76</v>
@@ -7730,13 +7730,13 @@
         <v>50</v>
       </c>
       <c r="S89" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T89" s="3">
         <v>15</v>
       </c>
       <c r="U89" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V89" s="3"/>
       <c r="W89" s="3"/>
@@ -7756,19 +7756,19 @@
       <c r="AK89" s="3"/>
       <c r="AL89" s="3"/>
     </row>
-    <row r="90" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" s="3"/>
       <c r="B90" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C90" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D90" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="E90" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>76</v>
@@ -7798,13 +7798,13 @@
         <v>50</v>
       </c>
       <c r="S90" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T90" s="3">
         <v>15</v>
       </c>
       <c r="U90" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
@@ -7824,19 +7824,19 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" s="3"/>
       <c r="B91" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C91" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="E91" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>76</v>
@@ -7866,13 +7866,13 @@
         <v>50</v>
       </c>
       <c r="S91" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T91" s="3">
         <v>15</v>
       </c>
       <c r="U91" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V91" s="3"/>
       <c r="W91" s="3"/>
@@ -7892,19 +7892,19 @@
       <c r="AK91" s="3"/>
       <c r="AL91" s="3"/>
     </row>
-    <row r="92" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="3"/>
       <c r="B92" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>76</v>
@@ -7934,13 +7934,13 @@
         <v>50</v>
       </c>
       <c r="S92" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T92" s="3">
         <v>15</v>
       </c>
       <c r="U92" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V92" s="3"/>
       <c r="W92" s="3"/>
@@ -7960,19 +7960,19 @@
       <c r="AK92" s="3"/>
       <c r="AL92" s="3"/>
     </row>
-    <row r="93" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="3"/>
       <c r="B93" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>76</v>
@@ -8002,13 +8002,13 @@
         <v>50</v>
       </c>
       <c r="S93" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T93" s="3">
         <v>15</v>
       </c>
       <c r="U93" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V93" s="3"/>
       <c r="W93" s="3"/>
@@ -8028,19 +8028,19 @@
       <c r="AK93" s="3"/>
       <c r="AL93" s="3"/>
     </row>
-    <row r="94" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" s="3"/>
       <c r="B94" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>76</v>
@@ -8070,13 +8070,13 @@
         <v>50</v>
       </c>
       <c r="S94" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T94" s="3">
         <v>15</v>
       </c>
       <c r="U94" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V94" s="3"/>
       <c r="W94" s="3"/>
@@ -8096,19 +8096,19 @@
       <c r="AK94" s="3"/>
       <c r="AL94" s="3"/>
     </row>
-    <row r="95" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="3"/>
       <c r="B95" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>76</v>
@@ -8138,13 +8138,13 @@
         <v>50</v>
       </c>
       <c r="S95" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T95" s="3">
         <v>15</v>
       </c>
       <c r="U95" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
@@ -8164,19 +8164,19 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" s="3"/>
       <c r="B96" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>76</v>
@@ -8206,13 +8206,13 @@
         <v>50</v>
       </c>
       <c r="S96" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T96" s="3">
         <v>15</v>
       </c>
       <c r="U96" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V96" s="3"/>
       <c r="W96" s="3"/>
@@ -8232,19 +8232,19 @@
       <c r="AK96" s="3"/>
       <c r="AL96" s="3"/>
     </row>
-    <row r="97" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="3"/>
       <c r="B97" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>76</v>
@@ -8274,13 +8274,13 @@
         <v>50</v>
       </c>
       <c r="S97" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T97" s="3">
         <v>15</v>
       </c>
       <c r="U97" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V97" s="3"/>
       <c r="W97" s="3"/>
@@ -8300,7 +8300,7 @@
       <c r="AK97" s="3"/>
       <c r="AL97" s="3"/>
     </row>
-    <row r="98" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" s="3"/>
       <c r="B98" s="3" t="s">
         <v>42</v>
@@ -8312,7 +8312,7 @@
         <v>102</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
@@ -8333,22 +8333,22 @@
         <v>9</v>
       </c>
       <c r="P98" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>1</v>
+      </c>
+      <c r="R98" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S98" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="Q98" s="3">
-        <v>1</v>
-      </c>
-      <c r="R98" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S98" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="T98" s="3">
         <v>15</v>
       </c>
       <c r="U98" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V98" s="3"/>
       <c r="W98" s="3"/>
@@ -8368,7 +8368,7 @@
       <c r="AK98" s="3"/>
       <c r="AL98" s="3"/>
     </row>
-    <row r="99" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
       <c r="B99" s="3" t="s">
         <v>42</v>
@@ -8377,10 +8377,10 @@
         <v>65</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
@@ -8401,22 +8401,22 @@
         <v>9</v>
       </c>
       <c r="P99" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>1</v>
+      </c>
+      <c r="R99" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S99" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="Q99" s="3">
-        <v>1</v>
-      </c>
-      <c r="R99" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S99" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="T99" s="3">
         <v>15</v>
       </c>
       <c r="U99" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V99" s="3"/>
       <c r="W99" s="3"/>
@@ -8436,7 +8436,7 @@
       <c r="AK99" s="3"/>
       <c r="AL99" s="3"/>
     </row>
-    <row r="100" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" s="3"/>
       <c r="B100" s="3" t="s">
         <v>42</v>
@@ -8445,10 +8445,10 @@
         <v>65</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
@@ -8469,22 +8469,22 @@
         <v>9</v>
       </c>
       <c r="P100" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>1</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S100" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>1</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="T100" s="3">
         <v>15</v>
       </c>
       <c r="U100" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V100" s="3"/>
       <c r="W100" s="3"/>
@@ -8504,7 +8504,7 @@
       <c r="AK100" s="3"/>
       <c r="AL100" s="3"/>
     </row>
-    <row r="101" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" s="3"/>
       <c r="B101" s="3" t="s">
         <v>42</v>
@@ -8516,7 +8516,7 @@
         <v>43</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
@@ -8537,22 +8537,22 @@
         <v>9</v>
       </c>
       <c r="P101" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>1</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S101" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>1</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="T101" s="3">
         <v>15</v>
       </c>
       <c r="U101" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V101" s="3"/>
       <c r="W101" s="3"/>
@@ -8572,7 +8572,7 @@
       <c r="AK101" s="3"/>
       <c r="AL101" s="3"/>
     </row>
-    <row r="102" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" s="3"/>
       <c r="B102" s="3" t="s">
         <v>42</v>
@@ -8584,7 +8584,7 @@
         <v>53</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
@@ -8605,22 +8605,22 @@
         <v>9</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>1</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>1</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="T102" s="3">
         <v>15</v>
       </c>
       <c r="U102" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V102" s="3"/>
       <c r="W102" s="3"/>
@@ -8640,7 +8640,7 @@
       <c r="AK102" s="3"/>
       <c r="AL102" s="3"/>
     </row>
-    <row r="103" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" s="3"/>
       <c r="B103" s="3" t="s">
         <v>42</v>
@@ -8652,7 +8652,7 @@
         <v>54</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
@@ -8673,22 +8673,22 @@
         <v>9</v>
       </c>
       <c r="P103" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q103" s="3">
+        <v>1</v>
+      </c>
+      <c r="R103" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S103" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="Q103" s="3">
-        <v>1</v>
-      </c>
-      <c r="R103" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S103" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="T103" s="3">
         <v>15</v>
       </c>
       <c r="U103" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V103" s="3"/>
       <c r="W103" s="3"/>
@@ -8708,7 +8708,7 @@
       <c r="AK103" s="3"/>
       <c r="AL103" s="3"/>
     </row>
-    <row r="104" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104" s="3"/>
       <c r="B104" s="3" t="s">
         <v>42</v>
@@ -8720,7 +8720,7 @@
         <v>58</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
@@ -8741,22 +8741,22 @@
         <v>9</v>
       </c>
       <c r="P104" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q104" s="3">
+        <v>1</v>
+      </c>
+      <c r="R104" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S104" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="Q104" s="3">
-        <v>1</v>
-      </c>
-      <c r="R104" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S104" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="T104" s="3">
         <v>15</v>
       </c>
       <c r="U104" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V104" s="3"/>
       <c r="W104" s="3"/>
@@ -8776,13 +8776,13 @@
       <c r="AK104" s="3"/>
       <c r="AL104" s="3"/>
     </row>
-    <row r="105" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" s="3"/>
       <c r="B105" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>43</v>
@@ -8826,7 +8826,7 @@
         <v>50</v>
       </c>
       <c r="U105" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V105" s="3"/>
       <c r="W105" s="3"/>
@@ -8846,13 +8846,13 @@
       <c r="AK105" s="3"/>
       <c r="AL105" s="3"/>
     </row>
-    <row r="106" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106" s="3"/>
       <c r="B106" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>53</v>
@@ -8896,7 +8896,7 @@
         <v>50</v>
       </c>
       <c r="U106" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V106" s="3"/>
       <c r="W106" s="3"/>
@@ -8916,13 +8916,13 @@
       <c r="AK106" s="3"/>
       <c r="AL106" s="3"/>
     </row>
-    <row r="107" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" s="3"/>
       <c r="B107" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>54</v>
@@ -8966,7 +8966,7 @@
         <v>50</v>
       </c>
       <c r="U107" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V107" s="3"/>
       <c r="W107" s="3"/>
@@ -8986,22 +8986,22 @@
       <c r="AK107" s="3"/>
       <c r="AL107" s="3"/>
     </row>
-    <row r="108" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A108" s="3"/>
       <c r="B108" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E108" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F108" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="G108" s="3"/>
       <c r="H108" s="3" t="s">
@@ -9036,7 +9036,7 @@
         <v>85</v>
       </c>
       <c r="U108" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V108" s="3"/>
       <c r="W108" s="3"/>
@@ -9056,22 +9056,22 @@
       <c r="AK108" s="3"/>
       <c r="AL108" s="3"/>
     </row>
-    <row r="109" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109" s="3"/>
       <c r="B109" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E109" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F109" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="F109" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="G109" s="3"/>
       <c r="H109" s="3" t="s">
@@ -9106,7 +9106,7 @@
         <v>85</v>
       </c>
       <c r="U109" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V109" s="3"/>
       <c r="W109" s="3"/>
@@ -9126,22 +9126,22 @@
       <c r="AK109" s="3"/>
       <c r="AL109" s="3"/>
     </row>
-    <row r="110" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110" s="3"/>
       <c r="B110" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E110" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F110" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="G110" s="3"/>
       <c r="H110" s="3" t="s">
@@ -9176,7 +9176,7 @@
         <v>85</v>
       </c>
       <c r="U110" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V110" s="3"/>
       <c r="W110" s="3"/>
@@ -9196,22 +9196,22 @@
       <c r="AK110" s="3"/>
       <c r="AL110" s="3"/>
     </row>
-    <row r="111" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" s="3"/>
       <c r="B111" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E111" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F111" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="G111" s="3"/>
       <c r="H111" s="3" t="s">
@@ -9246,7 +9246,7 @@
         <v>85</v>
       </c>
       <c r="U111" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V111" s="3"/>
       <c r="W111" s="3"/>
@@ -9266,19 +9266,19 @@
       <c r="AK111" s="3"/>
       <c r="AL111" s="3"/>
     </row>
-    <row r="112" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112" s="3"/>
       <c r="B112" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="3"/>
@@ -9314,7 +9314,7 @@
         <v>85</v>
       </c>
       <c r="U112" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V112" s="3"/>
       <c r="W112" s="3"/>
@@ -9334,19 +9334,19 @@
       <c r="AK112" s="3"/>
       <c r="AL112" s="3"/>
     </row>
-    <row r="113" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" s="3"/>
       <c r="B113" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F113" s="3"/>
       <c r="G113" s="3"/>
@@ -9382,7 +9382,7 @@
         <v>85</v>
       </c>
       <c r="U113" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V113" s="3"/>
       <c r="W113" s="3"/>
@@ -9402,19 +9402,19 @@
       <c r="AK113" s="3"/>
       <c r="AL113" s="3"/>
     </row>
-    <row r="114" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114" s="3"/>
       <c r="B114" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>76</v>
@@ -9452,7 +9452,7 @@
         <v>85</v>
       </c>
       <c r="U114" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V114" s="3"/>
       <c r="W114" s="3"/>
@@ -9472,19 +9472,19 @@
       <c r="AK114" s="3"/>
       <c r="AL114" s="3"/>
     </row>
-    <row r="115" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" s="3"/>
       <c r="B115" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F115" s="3"/>
       <c r="G115" s="3"/>
@@ -9505,7 +9505,7 @@
         <v>7000000</v>
       </c>
       <c r="P115" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q115" s="3">
         <v>30</v>
@@ -9520,7 +9520,7 @@
         <v>85</v>
       </c>
       <c r="U115" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V115" s="3"/>
       <c r="W115" s="3"/>
@@ -9540,13 +9540,13 @@
       <c r="AK115" s="3"/>
       <c r="AL115" s="3"/>
     </row>
-    <row r="116" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" s="3"/>
       <c r="B116" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>43</v>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="K116" s="3"/>
       <c r="L116" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M116" s="3" t="s">
         <v>64</v>
@@ -9590,7 +9590,7 @@
         <v>85</v>
       </c>
       <c r="U116" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V116" s="3"/>
       <c r="W116" s="3"/>
@@ -9602,10 +9602,10 @@
       <c r="AC116" s="3"/>
       <c r="AD116" s="3"/>
       <c r="AE116" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="AF116" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="AF116" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="AG116" s="3"/>
       <c r="AH116" s="3"/>
@@ -9614,13 +9614,13 @@
       <c r="AK116" s="3"/>
       <c r="AL116" s="3"/>
     </row>
-    <row r="117" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" s="3"/>
       <c r="B117" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>43</v>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="K117" s="3"/>
       <c r="L117" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M117" s="3" t="s">
         <v>64</v>
@@ -9664,7 +9664,7 @@
         <v>85</v>
       </c>
       <c r="U117" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V117" s="3"/>
       <c r="W117" s="3"/>
@@ -9676,10 +9676,10 @@
       <c r="AC117" s="3"/>
       <c r="AD117" s="3"/>
       <c r="AE117" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF117" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG117" s="3"/>
       <c r="AH117" s="3"/>
@@ -9688,13 +9688,13 @@
       <c r="AK117" s="3"/>
       <c r="AL117" s="3"/>
     </row>
-    <row r="118" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" s="3"/>
       <c r="B118" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>53</v>
@@ -9736,27 +9736,27 @@
         <v>85</v>
       </c>
       <c r="U118" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V118" s="3"/>
       <c r="W118" s="3"/>
       <c r="Y118" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Z118" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="AA118" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="AA118" s="4" t="s">
-        <v>194</v>
       </c>
       <c r="AB118" s="3"/>
       <c r="AC118" s="3"/>
       <c r="AD118" s="3"/>
       <c r="AE118" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="AF118" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="AF118" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="AG118" s="3"/>
       <c r="AH118" s="3"/>
@@ -9765,13 +9765,13 @@
       <c r="AK118" s="3"/>
       <c r="AL118" s="3"/>
     </row>
-    <row r="119" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" s="3"/>
       <c r="B119" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D119" s="3" t="s">
         <v>53</v>
@@ -9813,27 +9813,27 @@
         <v>85</v>
       </c>
       <c r="U119" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V119" s="3"/>
       <c r="W119" s="3"/>
       <c r="Y119" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Z119" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="AA119" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="AA119" s="4" t="s">
-        <v>197</v>
       </c>
       <c r="AB119" s="3"/>
       <c r="AC119" s="3"/>
       <c r="AD119" s="3"/>
       <c r="AE119" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF119" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG119" s="3"/>
       <c r="AH119" s="3"/>
@@ -9842,13 +9842,13 @@
       <c r="AK119" s="3"/>
       <c r="AL119" s="3"/>
     </row>
-    <row r="120" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120" s="3"/>
       <c r="B120" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>54</v>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="K120" s="3"/>
       <c r="L120" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M120" s="3" t="s">
         <v>64</v>
@@ -9892,7 +9892,7 @@
         <v>85</v>
       </c>
       <c r="U120" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V120" s="3"/>
       <c r="W120" s="3"/>
@@ -9904,10 +9904,10 @@
       <c r="AC120" s="3"/>
       <c r="AD120" s="3"/>
       <c r="AE120" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="AF120" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="AF120" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="AG120" s="3"/>
       <c r="AH120" s="3"/>
@@ -9916,13 +9916,13 @@
       <c r="AK120" s="3"/>
       <c r="AL120" s="3"/>
     </row>
-    <row r="121" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" s="3"/>
       <c r="B121" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>54</v>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="K121" s="3"/>
       <c r="L121" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M121" s="3" t="s">
         <v>64</v>
@@ -9966,7 +9966,7 @@
         <v>85</v>
       </c>
       <c r="U121" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V121" s="3"/>
       <c r="W121" s="3"/>
@@ -9978,10 +9978,10 @@
       <c r="AC121" s="3"/>
       <c r="AD121" s="3"/>
       <c r="AE121" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF121" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG121" s="3"/>
       <c r="AH121" s="3"/>
@@ -9990,7 +9990,7 @@
       <c r="AK121" s="3"/>
       <c r="AL121" s="3"/>
     </row>
-    <row r="122" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122" s="3"/>
       <c r="B122" s="3" t="s">
         <v>42</v>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="K122" s="3"/>
       <c r="L122" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M122" s="3" t="s">
         <v>64</v>
@@ -10040,7 +10040,7 @@
         <v>50</v>
       </c>
       <c r="U122" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V122" s="3"/>
       <c r="W122" s="3"/>
@@ -10052,10 +10052,10 @@
       <c r="AC122" s="3"/>
       <c r="AD122" s="3"/>
       <c r="AE122" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AF122" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG122" s="3"/>
       <c r="AH122" s="3"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="AL122" s="3"/>
     </row>
-    <row r="123" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" s="3"/>
       <c r="B123" s="3" t="s">
         <v>42</v>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="K123" s="3"/>
       <c r="L123" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M123" s="3" t="s">
         <v>64</v>
@@ -10120,7 +10120,7 @@
         <v>50</v>
       </c>
       <c r="U123" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V123" s="3"/>
       <c r="W123" s="3"/>
@@ -10132,10 +10132,10 @@
       <c r="AC123" s="3"/>
       <c r="AD123" s="3"/>
       <c r="AE123" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AF123" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG123" s="3"/>
       <c r="AH123" s="3"/>
@@ -10152,19 +10152,19 @@
         <v>87</v>
       </c>
     </row>
-    <row r="124" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" s="3"/>
       <c r="B124" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>76</v>
@@ -10202,7 +10202,7 @@
         <v>85</v>
       </c>
       <c r="U124" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V124" s="3"/>
       <c r="W124" s="3"/>
@@ -10222,19 +10222,19 @@
       <c r="AK124" s="3"/>
       <c r="AL124" s="3"/>
     </row>
-    <row r="125" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" s="3"/>
       <c r="B125" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>76</v>
@@ -10272,7 +10272,7 @@
         <v>85</v>
       </c>
       <c r="U125" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V125" s="3"/>
       <c r="W125" s="3"/>
@@ -10292,19 +10292,19 @@
       <c r="AK125" s="3"/>
       <c r="AL125" s="3"/>
     </row>
-    <row r="126" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126" s="3"/>
       <c r="B126" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>76</v>
@@ -10342,7 +10342,7 @@
         <v>85</v>
       </c>
       <c r="U126" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V126" s="3"/>
       <c r="W126" s="3"/>
@@ -10362,19 +10362,19 @@
       <c r="AK126" s="3"/>
       <c r="AL126" s="3"/>
     </row>
-    <row r="127" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127" s="3"/>
       <c r="B127" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>76</v>
@@ -10412,7 +10412,7 @@
         <v>85</v>
       </c>
       <c r="U127" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V127" s="3"/>
       <c r="W127" s="3"/>
@@ -10432,19 +10432,19 @@
       <c r="AK127" s="3"/>
       <c r="AL127" s="3"/>
     </row>
-    <row r="128" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A128" s="3"/>
       <c r="B128" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>76</v>
@@ -10482,7 +10482,7 @@
         <v>85</v>
       </c>
       <c r="U128" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V128" s="3"/>
       <c r="W128" s="3"/>
@@ -10502,19 +10502,19 @@
       <c r="AK128" s="3"/>
       <c r="AL128" s="3"/>
     </row>
-    <row r="129" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A129" s="3"/>
       <c r="B129" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>76</v>
@@ -10552,7 +10552,7 @@
         <v>50</v>
       </c>
       <c r="U129" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V129" s="3"/>
       <c r="W129" s="3"/>
@@ -10572,19 +10572,19 @@
       <c r="AK129" s="3"/>
       <c r="AL129" s="3"/>
     </row>
-    <row r="130" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" s="3"/>
       <c r="B130" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>76</v>
@@ -10622,7 +10622,7 @@
         <v>50</v>
       </c>
       <c r="U130" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V130" s="3"/>
       <c r="W130" s="3"/>
@@ -10642,19 +10642,19 @@
       <c r="AK130" s="3"/>
       <c r="AL130" s="3"/>
     </row>
-    <row r="131" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131" s="3"/>
       <c r="B131" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>76</v>
@@ -10692,7 +10692,7 @@
         <v>50</v>
       </c>
       <c r="U131" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V131" s="3"/>
       <c r="W131" s="3"/>
@@ -10712,19 +10712,19 @@
       <c r="AK131" s="3"/>
       <c r="AL131" s="3"/>
     </row>
-    <row r="132" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A132" s="3"/>
       <c r="B132" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>76</v>
@@ -10762,7 +10762,7 @@
         <v>50</v>
       </c>
       <c r="U132" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V132" s="3"/>
       <c r="W132" s="3"/>
@@ -10782,19 +10782,19 @@
       <c r="AK132" s="3"/>
       <c r="AL132" s="3"/>
     </row>
-    <row r="133" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" s="3"/>
       <c r="B133" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>76</v>
@@ -10832,7 +10832,7 @@
         <v>50</v>
       </c>
       <c r="U133" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V133" s="3"/>
       <c r="W133" s="3"/>
@@ -10852,19 +10852,19 @@
       <c r="AK133" s="3"/>
       <c r="AL133" s="3"/>
     </row>
-    <row r="134" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A134" s="3"/>
       <c r="B134" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>76</v>
@@ -10902,7 +10902,7 @@
         <v>50</v>
       </c>
       <c r="U134" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V134" s="3"/>
       <c r="W134" s="3"/>
@@ -10922,19 +10922,19 @@
       <c r="AK134" s="3"/>
       <c r="AL134" s="3"/>
     </row>
-    <row r="135" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A135" s="3"/>
       <c r="B135" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>76</v>
@@ -10972,7 +10972,7 @@
         <v>50</v>
       </c>
       <c r="U135" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V135" s="3"/>
       <c r="W135" s="3"/>
@@ -10992,7 +10992,7 @@
       <c r="AK135" s="3"/>
       <c r="AL135" s="3"/>
     </row>
-    <row r="136" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A136" s="3"/>
       <c r="B136" s="3" t="s">
         <v>42</v>
@@ -11040,7 +11040,7 @@
         <v>85</v>
       </c>
       <c r="U136" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V136" s="3"/>
       <c r="W136" s="3"/>
@@ -11055,7 +11055,7 @@
         <v>73</v>
       </c>
       <c r="AF136" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG136" s="3">
         <v>1.101672</v>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="AL136" s="3"/>
     </row>
-    <row r="137" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A137" s="3"/>
       <c r="B137" s="3" t="s">
         <v>42</v>
@@ -11124,7 +11124,7 @@
         <v>50</v>
       </c>
       <c r="U137" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V137" s="3"/>
       <c r="W137" s="3"/>
@@ -11144,7 +11144,7 @@
       <c r="AK137" s="3"/>
       <c r="AL137" s="3"/>
     </row>
-    <row r="138" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A138" s="3"/>
       <c r="B138" s="3" t="s">
         <v>42</v>
@@ -11194,7 +11194,7 @@
         <v>50</v>
       </c>
       <c r="U138" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V138" s="3"/>
       <c r="W138" s="3"/>
@@ -11214,13 +11214,13 @@
       <c r="AK138" s="3"/>
       <c r="AL138" s="3"/>
     </row>
-    <row r="139" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A139" s="3"/>
       <c r="B139" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>43</v>
@@ -11262,7 +11262,7 @@
         <v>85</v>
       </c>
       <c r="U139" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V139" s="3"/>
       <c r="W139" s="3"/>
@@ -11277,7 +11277,7 @@
         <v>73</v>
       </c>
       <c r="AF139" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AG139" s="3"/>
       <c r="AH139" s="3"/>
@@ -11292,13 +11292,13 @@
       </c>
       <c r="AL139" s="3"/>
     </row>
-    <row r="140" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A140" s="3"/>
       <c r="B140" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D140" s="3" t="s">
         <v>57</v>
@@ -11342,7 +11342,7 @@
         <v>50</v>
       </c>
       <c r="U140" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V140" s="3"/>
       <c r="W140" s="3"/>
@@ -11362,13 +11362,13 @@
       <c r="AK140" s="3"/>
       <c r="AL140" s="3"/>
     </row>
-    <row r="141" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A141" s="3"/>
       <c r="B141" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D141" s="3" t="s">
         <v>58</v>
@@ -11412,7 +11412,7 @@
         <v>50</v>
       </c>
       <c r="U141" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V141" s="3"/>
       <c r="W141" s="3"/>
@@ -11432,13 +11432,13 @@
       <c r="AK141" s="3"/>
       <c r="AL141" s="3"/>
     </row>
-    <row r="142" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A142" s="3"/>
       <c r="B142" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>43</v>
@@ -11482,7 +11482,7 @@
         <v>85</v>
       </c>
       <c r="U142" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V142" s="3"/>
       <c r="W142" s="3"/>
@@ -11502,13 +11502,13 @@
       <c r="AK142" s="3"/>
       <c r="AL142" s="3"/>
     </row>
-    <row r="143" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A143" s="3"/>
       <c r="B143" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D143" s="3" t="s">
         <v>57</v>
@@ -11552,7 +11552,7 @@
         <v>50</v>
       </c>
       <c r="U143" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V143" s="3"/>
       <c r="W143" s="3"/>
@@ -11572,13 +11572,13 @@
       <c r="AK143" s="3"/>
       <c r="AL143" s="3"/>
     </row>
-    <row r="144" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A144" s="3"/>
       <c r="B144" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>58</v>
@@ -11622,7 +11622,7 @@
         <v>50</v>
       </c>
       <c r="U144" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V144" s="3"/>
       <c r="W144" s="3"/>
@@ -11642,19 +11642,19 @@
       <c r="AK144" s="3"/>
       <c r="AL144" s="3"/>
     </row>
-    <row r="145" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A145" s="3"/>
       <c r="B145" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>76</v>
@@ -11690,7 +11690,7 @@
         <v>85</v>
       </c>
       <c r="U145" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V145" s="3"/>
       <c r="W145" s="3"/>
@@ -11705,7 +11705,7 @@
         <v>73</v>
       </c>
       <c r="AF145" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG145" s="3"/>
       <c r="AH145" s="3"/>
@@ -11720,19 +11720,19 @@
       </c>
       <c r="AL145" s="3"/>
     </row>
-    <row r="146" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A146" s="3"/>
       <c r="B146" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>76</v>
@@ -11768,7 +11768,7 @@
         <v>85</v>
       </c>
       <c r="U146" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V146" s="3"/>
       <c r="W146" s="3"/>
@@ -11783,7 +11783,7 @@
         <v>73</v>
       </c>
       <c r="AF146" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG146" s="3"/>
       <c r="AH146" s="3"/>
@@ -11798,19 +11798,19 @@
       </c>
       <c r="AL146" s="3"/>
     </row>
-    <row r="147" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A147" s="3"/>
       <c r="B147" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D147" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>76</v>
@@ -11848,7 +11848,7 @@
         <v>50</v>
       </c>
       <c r="U147" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V147" s="3"/>
       <c r="W147" s="3"/>
@@ -11868,19 +11868,19 @@
       <c r="AK147" s="3"/>
       <c r="AL147" s="3"/>
     </row>
-    <row r="148" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A148" s="3"/>
       <c r="B148" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>76</v>
@@ -11918,7 +11918,7 @@
         <v>50</v>
       </c>
       <c r="U148" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V148" s="3"/>
       <c r="W148" s="3"/>
@@ -11938,19 +11938,19 @@
       <c r="AK148" s="3"/>
       <c r="AL148" s="3"/>
     </row>
-    <row r="149" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A149" s="3"/>
       <c r="B149" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D149" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>70</v>
@@ -11988,7 +11988,7 @@
         <v>50</v>
       </c>
       <c r="U149" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V149" s="3"/>
       <c r="W149" s="3"/>
@@ -12008,19 +12008,19 @@
       <c r="AK149" s="3"/>
       <c r="AL149" s="3"/>
     </row>
-    <row r="150" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A150" s="3"/>
       <c r="B150" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D150" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>76</v>
@@ -12058,7 +12058,7 @@
         <v>85</v>
       </c>
       <c r="U150" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V150" s="3"/>
       <c r="W150" s="3"/>
@@ -12078,19 +12078,19 @@
       <c r="AK150" s="3"/>
       <c r="AL150" s="3"/>
     </row>
-    <row r="151" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A151" s="3"/>
       <c r="B151" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D151" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>76</v>
@@ -12126,7 +12126,7 @@
         <v>85</v>
       </c>
       <c r="U151" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V151" s="3"/>
       <c r="W151" s="3"/>
@@ -12141,7 +12141,7 @@
         <v>73</v>
       </c>
       <c r="AF151" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG151" s="3">
         <v>1.4620299999999999</v>
@@ -12160,19 +12160,19 @@
       </c>
       <c r="AL151" s="3"/>
     </row>
-    <row r="152" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A152" s="3"/>
       <c r="B152" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>76</v>
@@ -12208,7 +12208,7 @@
         <v>85</v>
       </c>
       <c r="U152" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V152" s="3"/>
       <c r="W152" s="3"/>
@@ -12223,7 +12223,7 @@
         <v>73</v>
       </c>
       <c r="AF152" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG152" s="3">
         <v>1.4620299999999999</v>
@@ -12242,19 +12242,19 @@
       </c>
       <c r="AL152" s="3"/>
     </row>
-    <row r="153" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A153" s="3"/>
       <c r="B153" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D153" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>76</v>
@@ -12292,7 +12292,7 @@
         <v>50</v>
       </c>
       <c r="U153" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V153" s="3"/>
       <c r="W153" s="3"/>
@@ -12312,19 +12312,19 @@
       <c r="AK153" s="3"/>
       <c r="AL153" s="3"/>
     </row>
-    <row r="154" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A154" s="3"/>
       <c r="B154" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D154" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>76</v>
@@ -12362,7 +12362,7 @@
         <v>50</v>
       </c>
       <c r="U154" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V154" s="3"/>
       <c r="W154" s="3"/>
@@ -12382,19 +12382,19 @@
       <c r="AK154" s="3"/>
       <c r="AL154" s="3"/>
     </row>
-    <row r="155" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A155" s="3"/>
       <c r="B155" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D155" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>76</v>
@@ -12430,7 +12430,7 @@
         <v>85</v>
       </c>
       <c r="U155" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V155" s="3"/>
       <c r="W155" s="3"/>
@@ -12445,7 +12445,7 @@
         <v>73</v>
       </c>
       <c r="AF155" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG155" s="3"/>
       <c r="AH155" s="3"/>
@@ -12460,19 +12460,19 @@
       </c>
       <c r="AL155" s="3"/>
     </row>
-    <row r="156" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A156" s="3"/>
       <c r="B156" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>76</v>
@@ -12508,7 +12508,7 @@
         <v>85</v>
       </c>
       <c r="U156" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V156" s="3"/>
       <c r="W156" s="3"/>
@@ -12523,7 +12523,7 @@
         <v>73</v>
       </c>
       <c r="AF156" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG156" s="3"/>
       <c r="AH156" s="3"/>
@@ -12538,19 +12538,19 @@
       </c>
       <c r="AL156" s="3"/>
     </row>
-    <row r="157" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A157" s="3"/>
       <c r="B157" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>76</v>
@@ -12588,7 +12588,7 @@
         <v>50</v>
       </c>
       <c r="U157" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V157" s="3"/>
       <c r="W157" s="3"/>
@@ -12608,19 +12608,19 @@
       <c r="AK157" s="3"/>
       <c r="AL157" s="3"/>
     </row>
-    <row r="158" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A158" s="3"/>
       <c r="B158" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D158" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>76</v>
@@ -12658,7 +12658,7 @@
         <v>50</v>
       </c>
       <c r="U158" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V158" s="3"/>
       <c r="W158" s="3"/>
@@ -12678,19 +12678,19 @@
       <c r="AK158" s="3"/>
       <c r="AL158" s="3"/>
     </row>
-    <row r="159" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A159" s="3"/>
       <c r="B159" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>70</v>
@@ -12728,7 +12728,7 @@
         <v>50</v>
       </c>
       <c r="U159" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V159" s="3"/>
       <c r="W159" s="3"/>
@@ -12748,19 +12748,19 @@
       <c r="AK159" s="3"/>
       <c r="AL159" s="3"/>
     </row>
-    <row r="160" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A160" s="3"/>
       <c r="B160" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>70</v>
@@ -12798,7 +12798,7 @@
         <v>50</v>
       </c>
       <c r="U160" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V160" s="3"/>
       <c r="W160" s="3"/>
@@ -12818,19 +12818,19 @@
       <c r="AK160" s="3"/>
       <c r="AL160" s="3"/>
     </row>
-    <row r="161" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A161" s="3"/>
       <c r="B161" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>76</v>
@@ -12868,7 +12868,7 @@
         <v>50</v>
       </c>
       <c r="U161" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V161" s="3"/>
       <c r="W161" s="3"/>
@@ -12888,19 +12888,19 @@
       <c r="AK161" s="3"/>
       <c r="AL161" s="3"/>
     </row>
-    <row r="162" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A162" s="3"/>
       <c r="B162" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>76</v>
@@ -12938,7 +12938,7 @@
         <v>50</v>
       </c>
       <c r="U162" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V162" s="3"/>
       <c r="W162" s="3"/>
@@ -12958,19 +12958,19 @@
       <c r="AK162" s="3"/>
       <c r="AL162" s="3"/>
     </row>
-    <row r="163" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A163" s="3"/>
       <c r="B163" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D163" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>76</v>
@@ -13006,7 +13006,7 @@
         <v>85</v>
       </c>
       <c r="U163" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V163" s="3"/>
       <c r="W163" s="3"/>
@@ -13021,7 +13021,7 @@
         <v>73</v>
       </c>
       <c r="AF163" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG163" s="3"/>
       <c r="AH163" s="3"/>
@@ -13036,19 +13036,19 @@
       </c>
       <c r="AL163" s="3"/>
     </row>
-    <row r="164" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A164" s="3"/>
       <c r="B164" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D164" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>76</v>
@@ -13084,7 +13084,7 @@
         <v>85</v>
       </c>
       <c r="U164" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V164" s="3"/>
       <c r="W164" s="3"/>
@@ -13099,7 +13099,7 @@
         <v>73</v>
       </c>
       <c r="AF164" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG164" s="3"/>
       <c r="AH164" s="3"/>
@@ -13114,19 +13114,19 @@
       </c>
       <c r="AL164" s="3"/>
     </row>
-    <row r="165" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A165" s="3"/>
       <c r="B165" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>76</v>
@@ -13164,7 +13164,7 @@
         <v>50</v>
       </c>
       <c r="U165" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V165" s="3"/>
       <c r="W165" s="3"/>
@@ -13184,19 +13184,19 @@
       <c r="AK165" s="3"/>
       <c r="AL165" s="3"/>
     </row>
-    <row r="166" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A166" s="3"/>
       <c r="B166" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D166" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>76</v>
@@ -13234,7 +13234,7 @@
         <v>50</v>
       </c>
       <c r="U166" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V166" s="3"/>
       <c r="W166" s="3"/>
@@ -13254,19 +13254,19 @@
       <c r="AK166" s="3"/>
       <c r="AL166" s="3"/>
     </row>
-    <row r="167" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A167" s="3"/>
       <c r="B167" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>76</v>
@@ -13304,7 +13304,7 @@
         <v>85</v>
       </c>
       <c r="U167" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V167" s="3"/>
       <c r="W167" s="3"/>
@@ -13324,19 +13324,19 @@
       <c r="AK167" s="3"/>
       <c r="AL167" s="3"/>
     </row>
-    <row r="168" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A168" s="3"/>
       <c r="B168" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D168" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>76</v>
@@ -13374,7 +13374,7 @@
         <v>85</v>
       </c>
       <c r="U168" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V168" s="3"/>
       <c r="W168" s="3"/>
@@ -13394,19 +13394,19 @@
       <c r="AK168" s="3"/>
       <c r="AL168" s="3"/>
     </row>
-    <row r="169" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A169" s="3"/>
       <c r="B169" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D169" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>76</v>
@@ -13444,7 +13444,7 @@
         <v>50</v>
       </c>
       <c r="U169" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V169" s="3"/>
       <c r="W169" s="3"/>
@@ -13464,19 +13464,19 @@
       <c r="AK169" s="3"/>
       <c r="AL169" s="3"/>
     </row>
-    <row r="170" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A170" s="3"/>
       <c r="B170" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>76</v>
@@ -13514,7 +13514,7 @@
         <v>50</v>
       </c>
       <c r="U170" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V170" s="3"/>
       <c r="W170" s="3"/>
@@ -13534,19 +13534,19 @@
       <c r="AK170" s="3"/>
       <c r="AL170" s="3"/>
     </row>
-    <row r="171" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A171" s="3"/>
       <c r="B171" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D171" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>76</v>
@@ -13582,7 +13582,7 @@
         <v>85</v>
       </c>
       <c r="U171" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V171" s="3"/>
       <c r="W171" s="3"/>
@@ -13597,7 +13597,7 @@
         <v>73</v>
       </c>
       <c r="AF171" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG171" s="3"/>
       <c r="AH171" s="3"/>
@@ -13612,19 +13612,19 @@
       </c>
       <c r="AL171" s="3"/>
     </row>
-    <row r="172" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A172" s="3"/>
       <c r="B172" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D172" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>76</v>
@@ -13660,7 +13660,7 @@
         <v>85</v>
       </c>
       <c r="U172" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V172" s="3"/>
       <c r="W172" s="3"/>
@@ -13675,7 +13675,7 @@
         <v>73</v>
       </c>
       <c r="AF172" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG172" s="3"/>
       <c r="AH172" s="3"/>
@@ -13690,19 +13690,19 @@
       </c>
       <c r="AL172" s="3"/>
     </row>
-    <row r="173" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A173" s="3"/>
       <c r="B173" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>76</v>
@@ -13740,7 +13740,7 @@
         <v>50</v>
       </c>
       <c r="U173" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V173" s="3"/>
       <c r="W173" s="3"/>
@@ -13760,19 +13760,19 @@
       <c r="AK173" s="3"/>
       <c r="AL173" s="3"/>
     </row>
-    <row r="174" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A174" s="3"/>
       <c r="B174" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>76</v>
@@ -13810,7 +13810,7 @@
         <v>85</v>
       </c>
       <c r="U174" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V174" s="3"/>
       <c r="W174" s="3"/>
@@ -13830,19 +13830,19 @@
       <c r="AK174" s="3"/>
       <c r="AL174" s="3"/>
     </row>
-    <row r="175" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A175" s="3"/>
       <c r="B175" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>76</v>
@@ -13880,7 +13880,7 @@
         <v>50</v>
       </c>
       <c r="U175" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V175" s="3"/>
       <c r="W175" s="3"/>
@@ -13900,19 +13900,19 @@
       <c r="AK175" s="3"/>
       <c r="AL175" s="3"/>
     </row>
-    <row r="176" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A176" s="3"/>
       <c r="B176" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>76</v>
@@ -13948,7 +13948,7 @@
         <v>85</v>
       </c>
       <c r="U176" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V176" s="3"/>
       <c r="W176" s="3"/>
@@ -13963,7 +13963,7 @@
         <v>73</v>
       </c>
       <c r="AF176" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG176" s="3"/>
       <c r="AH176" s="3"/>
@@ -13978,19 +13978,19 @@
       </c>
       <c r="AL176" s="3"/>
     </row>
-    <row r="177" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A177" s="3"/>
       <c r="B177" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>76</v>
@@ -14026,7 +14026,7 @@
         <v>85</v>
       </c>
       <c r="U177" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V177" s="3"/>
       <c r="W177" s="3"/>
@@ -14041,7 +14041,7 @@
         <v>73</v>
       </c>
       <c r="AF177" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG177" s="3"/>
       <c r="AH177" s="3"/>
@@ -14056,19 +14056,19 @@
       </c>
       <c r="AL177" s="3"/>
     </row>
-    <row r="178" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A178" s="3"/>
       <c r="B178" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D178" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>76</v>
@@ -14106,7 +14106,7 @@
         <v>50</v>
       </c>
       <c r="U178" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V178" s="3"/>
       <c r="W178" s="3"/>
@@ -14126,19 +14126,19 @@
       <c r="AK178" s="3"/>
       <c r="AL178" s="3"/>
     </row>
-    <row r="179" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A179" s="3"/>
       <c r="B179" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>76</v>
@@ -14174,7 +14174,7 @@
         <v>85</v>
       </c>
       <c r="U179" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V179" s="3"/>
       <c r="W179" s="3"/>
@@ -14189,7 +14189,7 @@
         <v>73</v>
       </c>
       <c r="AF179" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG179" s="3"/>
       <c r="AH179" s="3"/>
@@ -14204,19 +14204,19 @@
       </c>
       <c r="AL179" s="3"/>
     </row>
-    <row r="180" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A180" s="3"/>
       <c r="B180" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D180" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>76</v>
@@ -14252,7 +14252,7 @@
         <v>85</v>
       </c>
       <c r="U180" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V180" s="3"/>
       <c r="W180" s="3"/>
@@ -14267,7 +14267,7 @@
         <v>73</v>
       </c>
       <c r="AF180" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG180" s="3"/>
       <c r="AH180" s="3"/>
@@ -14282,19 +14282,19 @@
       </c>
       <c r="AL180" s="3"/>
     </row>
-    <row r="181" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A181" s="3"/>
       <c r="B181" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D181" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>76</v>
@@ -14332,7 +14332,7 @@
         <v>50</v>
       </c>
       <c r="U181" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V181" s="3"/>
       <c r="W181" s="3"/>
@@ -14352,19 +14352,19 @@
       <c r="AK181" s="3"/>
       <c r="AL181" s="3"/>
     </row>
-    <row r="182" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A182" s="3"/>
       <c r="B182" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D182" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>76</v>
@@ -14402,7 +14402,7 @@
         <v>50</v>
       </c>
       <c r="U182" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V182" s="3"/>
       <c r="W182" s="3"/>
@@ -14422,13 +14422,13 @@
       <c r="AK182" s="3"/>
       <c r="AL182" s="3"/>
     </row>
-    <row r="183" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A183" s="3"/>
       <c r="B183" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D183" s="3" t="s">
         <v>79</v>
@@ -14492,7 +14492,7 @@
       <c r="AK183" s="3"/>
       <c r="AL183" s="3"/>
     </row>
-    <row r="184" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A184" s="3"/>
       <c r="B184" s="3" t="s">
         <v>42</v>
@@ -14560,13 +14560,13 @@
       <c r="AK184" s="3"/>
       <c r="AL184" s="3"/>
     </row>
-    <row r="185" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A185" s="3"/>
       <c r="B185" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D185" s="3" t="s">
         <v>79</v>
@@ -14644,7 +14644,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="186" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A186" s="3"/>
       <c r="B186" s="3" t="s">
         <v>42</v>
@@ -14700,13 +14700,13 @@
       <c r="W186" s="3"/>
       <c r="X186" s="3"/>
       <c r="Y186" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Z186" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AA186" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AB186" s="3"/>
       <c r="AC186" s="3"/>
@@ -14720,7 +14720,7 @@
       <c r="AK186" s="3"/>
       <c r="AL186" s="3"/>
     </row>
-    <row r="187" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A187" s="3"/>
       <c r="B187" s="3" t="s">
         <v>42</v>
@@ -14779,10 +14779,10 @@
         <v>90</v>
       </c>
       <c r="Z187" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AA187" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AB187" s="3"/>
       <c r="AC187" s="3"/>
@@ -14796,7 +14796,7 @@
       <c r="AK187" s="3"/>
       <c r="AL187" s="3"/>
     </row>
-    <row r="188" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A188" s="3"/>
       <c r="B188" s="3" t="s">
         <v>42</v>
@@ -14855,10 +14855,10 @@
         <v>91</v>
       </c>
       <c r="Z188" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA188" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AB188" s="3"/>
       <c r="AC188" s="3"/>
@@ -14872,7 +14872,7 @@
       <c r="AK188" s="3"/>
       <c r="AL188" s="3"/>
     </row>
-    <row r="189" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A189" s="3"/>
       <c r="B189" s="3" t="s">
         <v>42</v>
@@ -14931,10 +14931,10 @@
         <v>93</v>
       </c>
       <c r="Z189" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AA189" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB189" s="3"/>
       <c r="AC189" s="3"/>
@@ -14948,7 +14948,7 @@
       <c r="AK189" s="3"/>
       <c r="AL189" s="3"/>
     </row>
-    <row r="190" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A190" s="3"/>
       <c r="B190" s="3" t="s">
         <v>42</v>
@@ -15007,10 +15007,10 @@
         <v>94</v>
       </c>
       <c r="Z190" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA190" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB190" s="3"/>
       <c r="AC190" s="3"/>
@@ -15024,7 +15024,7 @@
       <c r="AK190" s="3"/>
       <c r="AL190" s="3"/>
     </row>
-    <row r="191" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A191" s="3"/>
       <c r="B191" s="3" t="s">
         <v>42</v>
@@ -15083,10 +15083,10 @@
         <v>96</v>
       </c>
       <c r="Z191" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AA191" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB191" s="3"/>
       <c r="AC191" s="3"/>
@@ -15100,7 +15100,7 @@
       <c r="AK191" s="3"/>
       <c r="AL191" s="3"/>
     </row>
-    <row r="192" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A192" s="3"/>
       <c r="B192" s="3" t="s">
         <v>42</v>
@@ -15159,10 +15159,10 @@
         <v>94</v>
       </c>
       <c r="Z192" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA192" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB192" s="3"/>
       <c r="AC192" s="3"/>
@@ -15176,7 +15176,7 @@
       <c r="AK192" s="3"/>
       <c r="AL192" s="3"/>
     </row>
-    <row r="193" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A193" s="3"/>
       <c r="B193" s="3" t="s">
         <v>42</v>
@@ -15235,10 +15235,10 @@
         <v>96</v>
       </c>
       <c r="Z193" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AA193" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB193" s="3"/>
       <c r="AC193" s="3"/>
@@ -15252,7 +15252,7 @@
       <c r="AK193" s="3"/>
       <c r="AL193" s="3"/>
     </row>
-    <row r="194" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A194" s="3"/>
       <c r="B194" s="3" t="s">
         <v>42</v>
@@ -15308,13 +15308,13 @@
       <c r="W194" s="3"/>
       <c r="X194" s="3"/>
       <c r="Y194" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Z194" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AA194" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AB194" s="3"/>
       <c r="AC194" s="3"/>
@@ -15328,7 +15328,7 @@
       <c r="AK194" s="3"/>
       <c r="AL194" s="3"/>
     </row>
-    <row r="195" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A195" s="3"/>
       <c r="B195" s="3" t="s">
         <v>42</v>
@@ -15387,10 +15387,10 @@
         <v>90</v>
       </c>
       <c r="Z195" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AA195" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AB195" s="3"/>
       <c r="AC195" s="3"/>
@@ -15404,7 +15404,7 @@
       <c r="AK195" s="3"/>
       <c r="AL195" s="3"/>
     </row>
-    <row r="196" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A196" s="3"/>
       <c r="B196" s="3" t="s">
         <v>42</v>
@@ -15463,10 +15463,10 @@
         <v>91</v>
       </c>
       <c r="Z196" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA196" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AB196" s="3"/>
       <c r="AC196" s="3"/>
@@ -15480,7 +15480,7 @@
       <c r="AK196" s="3"/>
       <c r="AL196" s="3"/>
     </row>
-    <row r="197" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A197" s="3"/>
       <c r="B197" s="3" t="s">
         <v>42</v>
@@ -15539,10 +15539,10 @@
         <v>93</v>
       </c>
       <c r="Z197" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AA197" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB197" s="3"/>
       <c r="AC197" s="3"/>
@@ -15556,7 +15556,7 @@
       <c r="AK197" s="3"/>
       <c r="AL197" s="3"/>
     </row>
-    <row r="198" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A198" s="3"/>
       <c r="B198" s="3" t="s">
         <v>42</v>
@@ -15615,10 +15615,10 @@
         <v>94</v>
       </c>
       <c r="Z198" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA198" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB198" s="3"/>
       <c r="AC198" s="3"/>
@@ -15632,7 +15632,7 @@
       <c r="AK198" s="3"/>
       <c r="AL198" s="3"/>
     </row>
-    <row r="199" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A199" s="3"/>
       <c r="B199" s="3" t="s">
         <v>42</v>
@@ -15691,10 +15691,10 @@
         <v>96</v>
       </c>
       <c r="Z199" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AA199" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB199" s="3"/>
       <c r="AC199" s="3"/>
@@ -15708,7 +15708,7 @@
       <c r="AK199" s="3"/>
       <c r="AL199" s="3"/>
     </row>
-    <row r="200" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A200" s="3"/>
       <c r="B200" s="3" t="s">
         <v>42</v>
@@ -15767,10 +15767,10 @@
         <v>94</v>
       </c>
       <c r="Z200" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA200" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB200" s="3"/>
       <c r="AC200" s="3"/>
@@ -15784,7 +15784,7 @@
       <c r="AK200" s="3"/>
       <c r="AL200" s="3"/>
     </row>
-    <row r="201" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A201" s="3"/>
       <c r="B201" s="3" t="s">
         <v>42</v>
@@ -15843,10 +15843,10 @@
         <v>96</v>
       </c>
       <c r="Z201" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AA201" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB201" s="3"/>
       <c r="AC201" s="3"/>
@@ -15860,19 +15860,19 @@
       <c r="AK201" s="3"/>
       <c r="AL201" s="3"/>
     </row>
-    <row r="202" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A202" s="3"/>
       <c r="B202" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D202" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>76</v>
@@ -15902,13 +15902,13 @@
         <v>50</v>
       </c>
       <c r="S202" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="T202" s="3">
         <v>15</v>
       </c>
       <c r="U202" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V202" s="3"/>
       <c r="W202" s="3"/>
@@ -15928,7 +15928,7 @@
       <c r="AK202" s="3"/>
       <c r="AL202" s="3"/>
     </row>
-    <row r="203" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A203" s="3"/>
       <c r="B203" s="3" t="s">
         <v>42</v>
@@ -15940,7 +15940,7 @@
         <v>79</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="3"/>
@@ -15961,22 +15961,22 @@
         <v>9</v>
       </c>
       <c r="P203" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q203" s="3">
+        <v>1</v>
+      </c>
+      <c r="R203" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S203" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="Q203" s="3">
-        <v>1</v>
-      </c>
-      <c r="R203" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S203" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="T203" s="3">
         <v>15</v>
       </c>
       <c r="U203" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V203" s="3"/>
       <c r="W203" s="3"/>
@@ -15996,13 +15996,13 @@
       <c r="AK203" s="3"/>
       <c r="AL203" s="3"/>
     </row>
-    <row r="204" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A204" s="3"/>
       <c r="B204" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D204" s="3" t="s">
         <v>79</v>
@@ -16046,7 +16046,7 @@
         <v>50</v>
       </c>
       <c r="U204" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V204" s="3"/>
       <c r="W204" s="3"/>
@@ -16066,22 +16066,22 @@
       <c r="AK204" s="3"/>
       <c r="AL204" s="3"/>
     </row>
-    <row r="205" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A205" s="3"/>
       <c r="B205" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D205" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E205" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F205" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="F205" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="G205" s="3"/>
       <c r="H205" s="3" t="s">
@@ -16116,7 +16116,7 @@
         <v>85</v>
       </c>
       <c r="U205" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V205" s="3"/>
       <c r="W205" s="3"/>
@@ -16136,13 +16136,13 @@
       <c r="AK205" s="3"/>
       <c r="AL205" s="3"/>
     </row>
-    <row r="206" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A206" s="3"/>
       <c r="B206" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>79</v>
@@ -16163,7 +16163,7 @@
       </c>
       <c r="K206" s="3"/>
       <c r="L206" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M206" s="3" t="s">
         <v>64</v>
@@ -16186,7 +16186,7 @@
         <v>85</v>
       </c>
       <c r="U206" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V206" s="3"/>
       <c r="W206" s="3"/>
@@ -16198,10 +16198,10 @@
       <c r="AC206" s="3"/>
       <c r="AD206" s="3"/>
       <c r="AE206" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="AF206" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="AF206" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="AG206" s="3"/>
       <c r="AH206" s="3"/>
@@ -16210,13 +16210,13 @@
       <c r="AK206" s="3"/>
       <c r="AL206" s="3"/>
     </row>
-    <row r="207" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A207" s="3"/>
       <c r="B207" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D207" s="3" t="s">
         <v>79</v>
@@ -16237,7 +16237,7 @@
       </c>
       <c r="K207" s="3"/>
       <c r="L207" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M207" s="3" t="s">
         <v>64</v>
@@ -16260,7 +16260,7 @@
         <v>85</v>
       </c>
       <c r="U207" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V207" s="3"/>
       <c r="W207" s="3"/>
@@ -16272,10 +16272,10 @@
       <c r="AC207" s="3"/>
       <c r="AD207" s="3"/>
       <c r="AE207" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF207" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG207" s="3"/>
       <c r="AH207" s="3"/>
@@ -16284,13 +16284,13 @@
       <c r="AK207" s="3"/>
       <c r="AL207" s="3"/>
     </row>
-    <row r="208" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A208" s="3"/>
       <c r="B208" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D208" s="3" t="s">
         <v>79</v>
@@ -16354,19 +16354,19 @@
       <c r="AK208" s="3"/>
       <c r="AL208" s="3"/>
     </row>
-    <row r="209" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A209" s="3"/>
       <c r="B209" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D209" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>76</v>
@@ -16424,19 +16424,19 @@
       <c r="AK209" s="3"/>
       <c r="AL209" s="3"/>
     </row>
-    <row r="210" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A210" s="3"/>
       <c r="B210" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D210" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="3"/>
@@ -16492,19 +16492,19 @@
       <c r="AK210" s="3"/>
       <c r="AL210" s="3"/>
     </row>
-    <row r="211" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A211" s="3"/>
       <c r="B211" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D211" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F211" s="3"/>
       <c r="G211" s="3"/>
@@ -16560,19 +16560,19 @@
       <c r="AK211" s="3"/>
       <c r="AL211" s="3"/>
     </row>
-    <row r="212" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A212" s="3"/>
       <c r="B212" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D212" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F212" s="3"/>
       <c r="G212" s="3"/>
@@ -16628,19 +16628,19 @@
       <c r="AK212" s="3"/>
       <c r="AL212" s="3"/>
     </row>
-    <row r="213" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A213" s="3"/>
       <c r="B213" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D213" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F213" s="3"/>
       <c r="G213" s="3"/>
@@ -16696,19 +16696,19 @@
       <c r="AK213" s="3"/>
       <c r="AL213" s="3"/>
     </row>
-    <row r="214" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A214" s="3"/>
       <c r="B214" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D214" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>76</v>
@@ -16746,7 +16746,7 @@
         <v>85</v>
       </c>
       <c r="U214" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V214" s="3"/>
       <c r="W214" s="3"/>
@@ -16766,19 +16766,19 @@
       <c r="AK214" s="3"/>
       <c r="AL214" s="3"/>
     </row>
-    <row r="215" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A215" s="3"/>
       <c r="B215" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D215" s="3" t="s">
         <v>79</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>76</v>
@@ -16816,7 +16816,7 @@
         <v>50</v>
       </c>
       <c r="U215" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V215" s="3"/>
       <c r="W215" s="3"/>
@@ -16836,13 +16836,13 @@
       <c r="AK215" s="3"/>
       <c r="AL215" s="3"/>
     </row>
-    <row r="216" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A216" s="3"/>
       <c r="B216" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D216" s="3" t="s">
         <v>43</v>
@@ -16906,19 +16906,19 @@
       <c r="AK216" s="3"/>
       <c r="AL216" s="3"/>
     </row>
-    <row r="217" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A217" s="3"/>
       <c r="B217" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>76</v>
@@ -16976,19 +16976,19 @@
       <c r="AK217" s="3"/>
       <c r="AL217" s="3"/>
     </row>
-    <row r="218" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A218" s="3"/>
       <c r="B218" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="3"/>
@@ -17044,19 +17044,19 @@
       <c r="AK218" s="3"/>
       <c r="AL218" s="3"/>
     </row>
-    <row r="219" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A219" s="3"/>
       <c r="B219" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D219" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="3"/>
@@ -17112,19 +17112,19 @@
       <c r="AK219" s="3"/>
       <c r="AL219" s="3"/>
     </row>
-    <row r="220" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A220" s="3"/>
       <c r="B220" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D220" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="3"/>
@@ -17180,19 +17180,19 @@
       <c r="AK220" s="3"/>
       <c r="AL220" s="3"/>
     </row>
-    <row r="221" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A221" s="3"/>
       <c r="B221" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D221" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="3"/>
@@ -17248,19 +17248,19 @@
       <c r="AK221" s="3"/>
       <c r="AL221" s="3"/>
     </row>
-    <row r="222" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A222" s="3"/>
       <c r="B222" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D222" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>76</v>
@@ -17298,7 +17298,7 @@
         <v>85</v>
       </c>
       <c r="U222" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V222" s="3"/>
       <c r="W222" s="3"/>
@@ -17318,19 +17318,19 @@
       <c r="AK222" s="3"/>
       <c r="AL222" s="3"/>
     </row>
-    <row r="223" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A223" s="3"/>
       <c r="B223" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D223" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>76</v>
@@ -17368,7 +17368,7 @@
         <v>50</v>
       </c>
       <c r="U223" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V223" s="3"/>
       <c r="W223" s="3"/>
@@ -17388,13 +17388,13 @@
       <c r="AK223" s="3"/>
       <c r="AL223" s="3"/>
     </row>
-    <row r="224" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A224" s="3"/>
       <c r="B224" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D224" s="3" t="s">
         <v>54</v>
@@ -17458,19 +17458,19 @@
       <c r="AK224" s="3"/>
       <c r="AL224" s="3"/>
     </row>
-    <row r="225" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A225" s="3"/>
       <c r="B225" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D225" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>76</v>
@@ -17528,19 +17528,19 @@
       <c r="AK225" s="3"/>
       <c r="AL225" s="3"/>
     </row>
-    <row r="226" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A226" s="3"/>
       <c r="B226" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D226" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F226" s="3"/>
       <c r="G226" s="3"/>
@@ -17596,19 +17596,19 @@
       <c r="AK226" s="3"/>
       <c r="AL226" s="3"/>
     </row>
-    <row r="227" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A227" s="3"/>
       <c r="B227" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="3"/>
@@ -17664,19 +17664,19 @@
       <c r="AK227" s="3"/>
       <c r="AL227" s="3"/>
     </row>
-    <row r="228" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A228" s="3"/>
       <c r="B228" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D228" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="3"/>
@@ -17732,19 +17732,19 @@
       <c r="AK228" s="3"/>
       <c r="AL228" s="3"/>
     </row>
-    <row r="229" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A229" s="3"/>
       <c r="B229" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F229" s="3"/>
       <c r="G229" s="3"/>
@@ -17800,19 +17800,19 @@
       <c r="AK229" s="3"/>
       <c r="AL229" s="3"/>
     </row>
-    <row r="230" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A230" s="3"/>
       <c r="B230" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D230" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>76</v>
@@ -17850,7 +17850,7 @@
         <v>85</v>
       </c>
       <c r="U230" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V230" s="3"/>
       <c r="W230" s="3"/>
@@ -17870,19 +17870,19 @@
       <c r="AK230" s="3"/>
       <c r="AL230" s="3"/>
     </row>
-    <row r="231" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A231" s="3"/>
       <c r="B231" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>76</v>
@@ -17920,7 +17920,7 @@
         <v>50</v>
       </c>
       <c r="U231" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V231" s="3"/>
       <c r="W231" s="3"/>
@@ -17940,19 +17940,19 @@
       <c r="AK231" s="3"/>
       <c r="AL231" s="3"/>
     </row>
-    <row r="232" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A232" s="3"/>
       <c r="B232" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D232" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="3"/>
@@ -18008,19 +18008,19 @@
       <c r="AK232" s="3"/>
       <c r="AL232" s="3"/>
     </row>
-    <row r="233" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A233" s="3"/>
       <c r="B233" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="3"/>
@@ -18076,19 +18076,19 @@
       <c r="AK233" s="3"/>
       <c r="AL233" s="3"/>
     </row>
-    <row r="234" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A234" s="3"/>
       <c r="B234" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D234" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="3"/>
@@ -18144,19 +18144,19 @@
       <c r="AK234" s="3"/>
       <c r="AL234" s="3"/>
     </row>
-    <row r="235" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A235" s="3"/>
       <c r="B235" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D235" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F235" s="3"/>
       <c r="G235" s="3"/>
@@ -18212,19 +18212,19 @@
       <c r="AK235" s="3"/>
       <c r="AL235" s="3"/>
     </row>
-    <row r="236" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A236" s="3"/>
       <c r="B236" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D236" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>76</v>
@@ -18262,7 +18262,7 @@
         <v>85</v>
       </c>
       <c r="U236" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V236" s="3"/>
       <c r="W236" s="3"/>
@@ -18282,7 +18282,7 @@
       <c r="AK236" s="3"/>
       <c r="AL236" s="3"/>
     </row>
-    <row r="237" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A237" s="3"/>
       <c r="B237" s="3" t="s">
         <v>42</v>
@@ -18360,13 +18360,13 @@
       </c>
       <c r="AL237" s="3"/>
     </row>
-    <row r="238" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A238" s="3"/>
       <c r="B238" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D238" s="3" t="s">
         <v>53</v>
@@ -18438,13 +18438,13 @@
       </c>
       <c r="AL238" s="3"/>
     </row>
-    <row r="239" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A239" s="3"/>
       <c r="B239" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D239" s="3" t="s">
         <v>53</v>
@@ -18508,19 +18508,19 @@
       <c r="AK239" s="3"/>
       <c r="AL239" s="3"/>
     </row>
-    <row r="240" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A240" s="3"/>
       <c r="B240" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D240" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="3"/>
@@ -18533,7 +18533,7 @@
       </c>
       <c r="K240" s="3"/>
       <c r="L240" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M240" s="3" t="s">
         <v>64</v>
@@ -18571,7 +18571,7 @@
         <v>73</v>
       </c>
       <c r="AF240" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG240" s="3"/>
       <c r="AH240" s="3"/>
@@ -18586,19 +18586,19 @@
       </c>
       <c r="AL240" s="3"/>
     </row>
-    <row r="241" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A241" s="3"/>
       <c r="B241" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D241" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F241" s="3"/>
       <c r="G241" s="3"/>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="K241" s="3"/>
       <c r="L241" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M241" s="3" t="s">
         <v>64</v>
@@ -18649,7 +18649,7 @@
         <v>73</v>
       </c>
       <c r="AF241" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG241" s="3"/>
       <c r="AH241" s="3"/>
@@ -18664,7 +18664,7 @@
       </c>
       <c r="AL241" s="3"/>
     </row>
-    <row r="242" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A242" s="3"/>
       <c r="B242" s="3" t="s">
         <v>42</v>
@@ -18691,7 +18691,7 @@
       </c>
       <c r="K242" s="3"/>
       <c r="L242" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M242" s="3" t="s">
         <v>64</v>
@@ -18714,7 +18714,7 @@
         <v>50</v>
       </c>
       <c r="U242" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V242" s="3"/>
       <c r="W242" s="3"/>
@@ -18726,10 +18726,10 @@
       <c r="AC242" s="3"/>
       <c r="AD242" s="3"/>
       <c r="AE242" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AF242" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG242" s="3"/>
       <c r="AH242" s="3"/>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="AL242" s="3"/>
     </row>
-    <row r="243" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A243" s="3"/>
       <c r="B243" s="3" t="s">
         <v>42</v>
@@ -18771,7 +18771,7 @@
       </c>
       <c r="K243" s="3"/>
       <c r="L243" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M243" s="3" t="s">
         <v>64</v>
@@ -18794,7 +18794,7 @@
         <v>50</v>
       </c>
       <c r="U243" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V243" s="3"/>
       <c r="W243" s="3"/>
@@ -18806,10 +18806,10 @@
       <c r="AC243" s="3"/>
       <c r="AD243" s="3"/>
       <c r="AE243" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AF243" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG243" s="3"/>
       <c r="AH243" s="3"/>
@@ -18826,19 +18826,19 @@
         <v>87</v>
       </c>
     </row>
-    <row r="244" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A244" s="3"/>
       <c r="B244" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D244" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>76</v>
@@ -18876,7 +18876,7 @@
         <v>85</v>
       </c>
       <c r="U244" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V244" s="3"/>
       <c r="W244" s="3"/>
@@ -18896,19 +18896,19 @@
       <c r="AK244" s="3"/>
       <c r="AL244" s="3"/>
     </row>
-    <row r="245" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A245" s="3"/>
       <c r="B245" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D245" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>76</v>
@@ -18946,7 +18946,7 @@
         <v>85</v>
       </c>
       <c r="U245" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V245" s="3"/>
       <c r="W245" s="3"/>
@@ -18966,7 +18966,7 @@
       <c r="AK245" s="3"/>
       <c r="AL245" s="3"/>
     </row>
-    <row r="246" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A246" s="3"/>
       <c r="B246" s="3" t="s">
         <v>42</v>
@@ -19014,7 +19014,7 @@
         <v>85</v>
       </c>
       <c r="U246" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V246" s="3"/>
       <c r="W246" s="3"/>
@@ -19029,7 +19029,7 @@
         <v>73</v>
       </c>
       <c r="AF246" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG246" s="3">
         <v>1.101672</v>
@@ -19048,13 +19048,13 @@
       </c>
       <c r="AL246" s="3"/>
     </row>
-    <row r="247" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A247" s="3"/>
       <c r="B247" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D247" s="3" t="s">
         <v>53</v>
@@ -19096,7 +19096,7 @@
         <v>85</v>
       </c>
       <c r="U247" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V247" s="3"/>
       <c r="W247" s="3"/>
@@ -19111,7 +19111,7 @@
         <v>73</v>
       </c>
       <c r="AF247" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AG247" s="3"/>
       <c r="AH247" s="3"/>
@@ -19126,13 +19126,13 @@
       </c>
       <c r="AL247" s="3"/>
     </row>
-    <row r="248" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A248" s="3"/>
       <c r="B248" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>53</v>
@@ -19176,7 +19176,7 @@
         <v>85</v>
       </c>
       <c r="U248" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V248" s="3"/>
       <c r="W248" s="3"/>
@@ -19196,19 +19196,19 @@
       <c r="AK248" s="3"/>
       <c r="AL248" s="3"/>
     </row>
-    <row r="249" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A249" s="3"/>
       <c r="B249" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D249" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>76</v>
@@ -19244,7 +19244,7 @@
         <v>85</v>
       </c>
       <c r="U249" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V249" s="3"/>
       <c r="W249" s="3"/>
@@ -19259,7 +19259,7 @@
         <v>73</v>
       </c>
       <c r="AF249" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG249" s="3"/>
       <c r="AH249" s="3"/>
@@ -19274,19 +19274,19 @@
       </c>
       <c r="AL249" s="3"/>
     </row>
-    <row r="250" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A250" s="3"/>
       <c r="B250" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D250" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>76</v>
@@ -19322,7 +19322,7 @@
         <v>85</v>
       </c>
       <c r="U250" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V250" s="3"/>
       <c r="W250" s="3"/>
@@ -19337,7 +19337,7 @@
         <v>73</v>
       </c>
       <c r="AF250" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG250" s="3"/>
       <c r="AH250" s="3"/>
@@ -19352,19 +19352,19 @@
       </c>
       <c r="AL250" s="3"/>
     </row>
-    <row r="251" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A251" s="3"/>
       <c r="B251" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D251" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>70</v>
@@ -19402,7 +19402,7 @@
         <v>50</v>
       </c>
       <c r="U251" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V251" s="3"/>
       <c r="W251" s="3"/>
@@ -19422,19 +19422,19 @@
       <c r="AK251" s="3"/>
       <c r="AL251" s="3"/>
     </row>
-    <row r="252" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A252" s="3"/>
       <c r="B252" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D252" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>76</v>
@@ -19470,7 +19470,7 @@
         <v>85</v>
       </c>
       <c r="U252" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V252" s="3"/>
       <c r="W252" s="3"/>
@@ -19485,7 +19485,7 @@
         <v>73</v>
       </c>
       <c r="AF252" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG252" s="3">
         <v>1.4620299999999999</v>
@@ -19504,19 +19504,19 @@
       </c>
       <c r="AL252" s="3"/>
     </row>
-    <row r="253" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A253" s="3"/>
       <c r="B253" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D253" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>76</v>
@@ -19552,7 +19552,7 @@
         <v>85</v>
       </c>
       <c r="U253" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V253" s="3"/>
       <c r="W253" s="3"/>
@@ -19567,7 +19567,7 @@
         <v>73</v>
       </c>
       <c r="AF253" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG253" s="3">
         <v>1.4620299999999999</v>
@@ -19586,19 +19586,19 @@
       </c>
       <c r="AL253" s="3"/>
     </row>
-    <row r="254" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A254" s="3"/>
       <c r="B254" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D254" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>76</v>
@@ -19634,7 +19634,7 @@
         <v>85</v>
       </c>
       <c r="U254" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V254" s="3"/>
       <c r="W254" s="3"/>
@@ -19649,7 +19649,7 @@
         <v>73</v>
       </c>
       <c r="AF254" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG254" s="3"/>
       <c r="AH254" s="3"/>
@@ -19664,19 +19664,19 @@
       </c>
       <c r="AL254" s="3"/>
     </row>
-    <row r="255" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A255" s="3"/>
       <c r="B255" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D255" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>76</v>
@@ -19712,7 +19712,7 @@
         <v>85</v>
       </c>
       <c r="U255" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V255" s="3"/>
       <c r="W255" s="3"/>
@@ -19727,7 +19727,7 @@
         <v>73</v>
       </c>
       <c r="AF255" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG255" s="3"/>
       <c r="AH255" s="3"/>
@@ -19742,19 +19742,19 @@
       </c>
       <c r="AL255" s="3"/>
     </row>
-    <row r="256" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A256" s="3"/>
       <c r="B256" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D256" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>70</v>
@@ -19792,7 +19792,7 @@
         <v>50</v>
       </c>
       <c r="U256" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V256" s="3"/>
       <c r="W256" s="3"/>
@@ -19812,19 +19812,19 @@
       <c r="AK256" s="3"/>
       <c r="AL256" s="3"/>
     </row>
-    <row r="257" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A257" s="3"/>
       <c r="B257" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D257" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>76</v>
@@ -19860,7 +19860,7 @@
         <v>85</v>
       </c>
       <c r="U257" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V257" s="3"/>
       <c r="W257" s="3"/>
@@ -19875,7 +19875,7 @@
         <v>73</v>
       </c>
       <c r="AF257" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG257" s="3"/>
       <c r="AH257" s="3"/>
@@ -19890,19 +19890,19 @@
       </c>
       <c r="AL257" s="3"/>
     </row>
-    <row r="258" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A258" s="3"/>
       <c r="B258" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D258" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>76</v>
@@ -19938,7 +19938,7 @@
         <v>85</v>
       </c>
       <c r="U258" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V258" s="3"/>
       <c r="W258" s="3"/>
@@ -19953,7 +19953,7 @@
         <v>73</v>
       </c>
       <c r="AF258" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG258" s="3"/>
       <c r="AH258" s="3"/>
@@ -19968,19 +19968,19 @@
       </c>
       <c r="AL258" s="3"/>
     </row>
-    <row r="259" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A259" s="3"/>
       <c r="B259" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D259" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>76</v>
@@ -20018,7 +20018,7 @@
         <v>85</v>
       </c>
       <c r="U259" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V259" s="3"/>
       <c r="W259" s="3"/>
@@ -20038,19 +20038,19 @@
       <c r="AK259" s="3"/>
       <c r="AL259" s="3"/>
     </row>
-    <row r="260" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A260" s="3"/>
       <c r="B260" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D260" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>76</v>
@@ -20088,7 +20088,7 @@
         <v>85</v>
       </c>
       <c r="U260" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V260" s="3"/>
       <c r="W260" s="3"/>
@@ -20108,19 +20108,19 @@
       <c r="AK260" s="3"/>
       <c r="AL260" s="3"/>
     </row>
-    <row r="261" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A261" s="3"/>
       <c r="B261" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D261" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>76</v>
@@ -20156,7 +20156,7 @@
         <v>85</v>
       </c>
       <c r="U261" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V261" s="3"/>
       <c r="W261" s="3"/>
@@ -20171,7 +20171,7 @@
         <v>73</v>
       </c>
       <c r="AF261" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG261" s="3"/>
       <c r="AH261" s="3"/>
@@ -20186,19 +20186,19 @@
       </c>
       <c r="AL261" s="3"/>
     </row>
-    <row r="262" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A262" s="3"/>
       <c r="B262" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D262" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>76</v>
@@ -20234,7 +20234,7 @@
         <v>85</v>
       </c>
       <c r="U262" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V262" s="3"/>
       <c r="W262" s="3"/>
@@ -20249,7 +20249,7 @@
         <v>73</v>
       </c>
       <c r="AF262" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG262" s="3"/>
       <c r="AH262" s="3"/>
@@ -20264,19 +20264,19 @@
       </c>
       <c r="AL262" s="3"/>
     </row>
-    <row r="263" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A263" s="3"/>
       <c r="B263" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D263" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>76</v>
@@ -20314,7 +20314,7 @@
         <v>85</v>
       </c>
       <c r="U263" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V263" s="3"/>
       <c r="W263" s="3"/>
@@ -20334,19 +20334,19 @@
       <c r="AK263" s="3"/>
       <c r="AL263" s="3"/>
     </row>
-    <row r="264" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A264" s="3"/>
       <c r="B264" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D264" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>76</v>
@@ -20382,7 +20382,7 @@
         <v>85</v>
       </c>
       <c r="U264" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V264" s="3"/>
       <c r="W264" s="3"/>
@@ -20397,7 +20397,7 @@
         <v>73</v>
       </c>
       <c r="AF264" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG264" s="3"/>
       <c r="AH264" s="3"/>
@@ -20412,19 +20412,19 @@
       </c>
       <c r="AL264" s="3"/>
     </row>
-    <row r="265" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A265" s="3"/>
       <c r="B265" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D265" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>76</v>
@@ -20460,7 +20460,7 @@
         <v>85</v>
       </c>
       <c r="U265" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V265" s="3"/>
       <c r="W265" s="3"/>
@@ -20475,7 +20475,7 @@
         <v>73</v>
       </c>
       <c r="AF265" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AG265" s="3"/>
       <c r="AH265" s="3"/>
@@ -20490,19 +20490,19 @@
       </c>
       <c r="AL265" s="3"/>
     </row>
-    <row r="266" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A266" s="3"/>
       <c r="B266" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D266" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>76</v>
@@ -20538,7 +20538,7 @@
         <v>85</v>
       </c>
       <c r="U266" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V266" s="3"/>
       <c r="W266" s="3"/>
@@ -20553,7 +20553,7 @@
         <v>73</v>
       </c>
       <c r="AF266" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG266" s="3"/>
       <c r="AH266" s="3"/>
@@ -20568,19 +20568,19 @@
       </c>
       <c r="AL266" s="3"/>
     </row>
-    <row r="267" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A267" s="3"/>
       <c r="B267" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D267" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>76</v>
@@ -20616,7 +20616,7 @@
         <v>85</v>
       </c>
       <c r="U267" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V267" s="3"/>
       <c r="W267" s="3"/>
@@ -20631,7 +20631,7 @@
         <v>73</v>
       </c>
       <c r="AF267" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG267" s="3"/>
       <c r="AH267" s="3"/>

--- a/inst/extdata/colorado_criteria_crosswalk.xlsx
+++ b/inst/extdata/colorado_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="13_ncr:1_{4D3C5983-93D7-4EE7-99A9-9B9AB47C3C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67702059-A150-46E3-A3CB-A5146CDC35FF}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="13_ncr:1_{4D3C5983-93D7-4EE7-99A9-9B9AB47C3C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F0291EE-A12E-41A9-9370-4263EBE8476D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{380839A1-A469-4C26-93CF-5FD0D1BCA51C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{380839A1-A469-4C26-93CF-5FD0D1BCA51C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3512" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3515" uniqueCount="232">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -686,9 +686,6 @@
     <t>pHDirection</t>
   </si>
   <si>
-    <t>TemperatureExtreme</t>
-  </si>
-  <si>
     <t>pH_param_9</t>
   </si>
   <si>
@@ -719,10 +716,22 @@
     <t>((0.0577/(1+10^(7.688-pH))) + (2.487/(1+10^(pH-7.688)))) * 1.45*10^(0.028*(25-max(Temperature,7)))</t>
   </si>
   <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
+    <t>AmmoniaEqType</t>
+  </si>
+  <si>
+    <t>pH_param_10</t>
+  </si>
+  <si>
+    <t>pH_param_11</t>
+  </si>
+  <si>
+    <t>pH_param_12</t>
+  </si>
+  <si>
+    <t>Min Multiplier</t>
+  </si>
+  <si>
+    <t>Max Exponent</t>
   </si>
 </sst>
 </file>
@@ -1138,25 +1147,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F27C99-86A4-42C9-ADFF-84FEE74EA84D}">
-  <dimension ref="A1:AX267"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BA267"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="5"/>
-    <col min="3" max="3" width="24.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="24" width="9.140625" style="5"/>
-    <col min="25" max="25" width="10.5703125" style="5" customWidth="1"/>
-    <col min="26" max="30" width="9.140625" style="5"/>
-    <col min="31" max="31" width="20.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="102.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="19.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="9.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="2" width="9.109375" style="5"/>
+    <col min="3" max="3" width="24.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="24" width="9.109375" style="5"/>
+    <col min="25" max="25" width="10.5546875" style="5" customWidth="1"/>
+    <col min="26" max="30" width="9.109375" style="5"/>
+    <col min="31" max="31" width="20.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="102.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="19.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="9.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1272,7 +1281,7 @@
         <v>34</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>35</v>
@@ -1287,28 +1296,37 @@
         <v>38</v>
       </c>
       <c r="AR1" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="AS1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="AS1" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="AT1" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="AW1" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="AZ1" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="BA1" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="AX1" s="6" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="2" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>39</v>
@@ -1379,7 +1397,7 @@
       <c r="AL2" s="3"/>
       <c r="AM2" s="3"/>
     </row>
-    <row r="3" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -1450,7 +1468,7 @@
       <c r="AL3" s="3"/>
       <c r="AM3" s="3"/>
     </row>
-    <row r="4" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>39</v>
@@ -1521,7 +1539,7 @@
       <c r="AL4" s="3"/>
       <c r="AM4" s="3"/>
     </row>
-    <row r="5" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>39</v>
@@ -1590,7 +1608,7 @@
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
     </row>
-    <row r="6" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -1659,7 +1677,7 @@
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
     </row>
-    <row r="7" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>39</v>
@@ -1728,7 +1746,7 @@
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
     </row>
-    <row r="8" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>39</v>
@@ -1797,7 +1815,7 @@
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
     </row>
-    <row r="9" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>39</v>
@@ -1866,7 +1884,7 @@
       <c r="AL9" s="3"/>
       <c r="AM9" s="3"/>
     </row>
-    <row r="10" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>39</v>
@@ -1935,7 +1953,7 @@
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
     </row>
-    <row r="11" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>39</v>
@@ -2004,7 +2022,7 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>39</v>
@@ -2073,7 +2091,7 @@
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
     </row>
-    <row r="13" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -2142,7 +2160,7 @@
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
     </row>
-    <row r="14" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>39</v>
@@ -2211,7 +2229,7 @@
       <c r="AL14" s="3"/>
       <c r="AM14" s="3"/>
     </row>
-    <row r="15" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>39</v>
@@ -2296,7 +2314,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>39</v>
@@ -2381,7 +2399,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -2466,7 +2484,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -2542,7 +2560,7 @@
         <v>1.8308</v>
       </c>
     </row>
-    <row r="19" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -2622,7 +2640,7 @@
         <v>-3.8660000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>39</v>
@@ -2702,7 +2720,7 @@
         <v>-3.4430000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -2784,7 +2802,7 @@
         <v>-3.8660000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -2866,7 +2884,7 @@
         <v>-3.4430000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>39</v>
@@ -2942,7 +2960,7 @@
         <v>2.5735999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -3013,7 +3031,7 @@
       <c r="AL24" s="3"/>
       <c r="AM24" s="3"/>
     </row>
-    <row r="25" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -3090,7 +3108,7 @@
       <c r="AL25" s="3"/>
       <c r="AM25" s="3"/>
     </row>
-    <row r="26" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -3167,7 +3185,7 @@
       <c r="AL26" s="3"/>
       <c r="AM26" s="3"/>
     </row>
-    <row r="27" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -3244,7 +3262,7 @@
       <c r="AL27" s="3"/>
       <c r="AM27" s="3"/>
     </row>
-    <row r="28" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>39</v>
@@ -3321,7 +3339,7 @@
       <c r="AL28" s="3"/>
       <c r="AM28" s="3"/>
     </row>
-    <row r="29" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>39</v>
@@ -3398,7 +3416,7 @@
       <c r="AL29" s="3"/>
       <c r="AM29" s="3"/>
     </row>
-    <row r="30" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>39</v>
@@ -3475,7 +3493,7 @@
       <c r="AL30" s="3"/>
       <c r="AM30" s="3"/>
     </row>
-    <row r="31" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>39</v>
@@ -3552,7 +3570,7 @@
       <c r="AL31" s="3"/>
       <c r="AM31" s="3"/>
     </row>
-    <row r="32" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>39</v>
@@ -3629,7 +3647,7 @@
       <c r="AL32" s="3"/>
       <c r="AM32" s="3"/>
     </row>
-    <row r="33" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>39</v>
@@ -3706,7 +3724,7 @@
       <c r="AL33" s="3"/>
       <c r="AM33" s="3"/>
     </row>
-    <row r="34" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>39</v>
@@ -3783,7 +3801,7 @@
       <c r="AL34" s="3"/>
       <c r="AM34" s="3"/>
     </row>
-    <row r="35" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>39</v>
@@ -3860,7 +3878,7 @@
       <c r="AL35" s="3"/>
       <c r="AM35" s="3"/>
     </row>
-    <row r="36" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>39</v>
@@ -3937,7 +3955,7 @@
       <c r="AL36" s="3"/>
       <c r="AM36" s="3"/>
     </row>
-    <row r="37" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>39</v>
@@ -4014,7 +4032,7 @@
       <c r="AL37" s="3"/>
       <c r="AM37" s="3"/>
     </row>
-    <row r="38" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
         <v>39</v>
@@ -4091,7 +4109,7 @@
       <c r="AL38" s="3"/>
       <c r="AM38" s="3"/>
     </row>
-    <row r="39" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>39</v>
@@ -4168,7 +4186,7 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
         <v>39</v>
@@ -4245,7 +4263,7 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>39</v>
@@ -4322,7 +4340,7 @@
       <c r="AL41" s="3"/>
       <c r="AM41" s="3"/>
     </row>
-    <row r="42" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>39</v>
@@ -4399,7 +4417,7 @@
       <c r="AL42" s="3"/>
       <c r="AM42" s="3"/>
     </row>
-    <row r="43" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>39</v>
@@ -4476,7 +4494,7 @@
       <c r="AL43" s="3"/>
       <c r="AM43" s="3"/>
     </row>
-    <row r="44" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
         <v>39</v>
@@ -4553,7 +4571,7 @@
       <c r="AL44" s="3"/>
       <c r="AM44" s="3"/>
     </row>
-    <row r="45" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>39</v>
@@ -4630,7 +4648,7 @@
       <c r="AL45" s="3"/>
       <c r="AM45" s="3"/>
     </row>
-    <row r="46" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
         <v>39</v>
@@ -4707,7 +4725,7 @@
       <c r="AL46" s="3"/>
       <c r="AM46" s="3"/>
     </row>
-    <row r="47" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>39</v>
@@ -4784,7 +4802,7 @@
       <c r="AL47" s="3"/>
       <c r="AM47" s="3"/>
     </row>
-    <row r="48" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
         <v>39</v>
@@ -4861,7 +4879,7 @@
       <c r="AL48" s="3"/>
       <c r="AM48" s="3"/>
     </row>
-    <row r="49" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
         <v>39</v>
@@ -4938,7 +4956,7 @@
       <c r="AL49" s="3"/>
       <c r="AM49" s="3"/>
     </row>
-    <row r="50" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
         <v>39</v>
@@ -5015,7 +5033,7 @@
       <c r="AL50" s="3"/>
       <c r="AM50" s="3"/>
     </row>
-    <row r="51" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
         <v>39</v>
@@ -5092,7 +5110,7 @@
       <c r="AL51" s="3"/>
       <c r="AM51" s="3"/>
     </row>
-    <row r="52" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
         <v>39</v>
@@ -5169,7 +5187,7 @@
       <c r="AL52" s="3"/>
       <c r="AM52" s="3"/>
     </row>
-    <row r="53" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
         <v>39</v>
@@ -5246,7 +5264,7 @@
       <c r="AL53" s="3"/>
       <c r="AM53" s="3"/>
     </row>
-    <row r="54" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
         <v>39</v>
@@ -5323,7 +5341,7 @@
       <c r="AL54" s="3"/>
       <c r="AM54" s="3"/>
     </row>
-    <row r="55" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
         <v>39</v>
@@ -5400,7 +5418,7 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
         <v>39</v>
@@ -5477,7 +5495,7 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
         <v>39</v>
@@ -5554,7 +5572,7 @@
       <c r="AL57" s="3"/>
       <c r="AM57" s="3"/>
     </row>
-    <row r="58" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
         <v>39</v>
@@ -5631,7 +5649,7 @@
       <c r="AL58" s="3"/>
       <c r="AM58" s="3"/>
     </row>
-    <row r="59" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
         <v>39</v>
@@ -5708,7 +5726,7 @@
       <c r="AL59" s="3"/>
       <c r="AM59" s="3"/>
     </row>
-    <row r="60" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
         <v>39</v>
@@ -5785,7 +5803,7 @@
       <c r="AL60" s="3"/>
       <c r="AM60" s="3"/>
     </row>
-    <row r="61" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
         <v>39</v>
@@ -5862,7 +5880,7 @@
       <c r="AL61" s="3"/>
       <c r="AM61" s="3"/>
     </row>
-    <row r="62" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
         <v>39</v>
@@ -5939,7 +5957,7 @@
       <c r="AL62" s="3"/>
       <c r="AM62" s="3"/>
     </row>
-    <row r="63" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
         <v>39</v>
@@ -6016,7 +6034,7 @@
       <c r="AL63" s="3"/>
       <c r="AM63" s="3"/>
     </row>
-    <row r="64" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
         <v>39</v>
@@ -6093,7 +6111,7 @@
       <c r="AL64" s="3"/>
       <c r="AM64" s="3"/>
     </row>
-    <row r="65" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
         <v>39</v>
@@ -6170,7 +6188,7 @@
       <c r="AL65" s="3"/>
       <c r="AM65" s="3"/>
     </row>
-    <row r="66" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
         <v>39</v>
@@ -6247,7 +6265,7 @@
       <c r="AL66" s="3"/>
       <c r="AM66" s="3"/>
     </row>
-    <row r="67" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
         <v>39</v>
@@ -6324,7 +6342,7 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
         <v>39</v>
@@ -6401,7 +6419,7 @@
       <c r="AL68" s="3"/>
       <c r="AM68" s="3"/>
     </row>
-    <row r="69" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
         <v>39</v>
@@ -6478,7 +6496,7 @@
       <c r="AL69" s="3"/>
       <c r="AM69" s="3"/>
     </row>
-    <row r="70" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3" t="s">
         <v>39</v>
@@ -6555,7 +6573,7 @@
       <c r="AL70" s="3"/>
       <c r="AM70" s="3"/>
     </row>
-    <row r="71" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3" t="s">
         <v>39</v>
@@ -6632,7 +6650,7 @@
       <c r="AL71" s="3"/>
       <c r="AM71" s="3"/>
     </row>
-    <row r="72" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3" t="s">
         <v>39</v>
@@ -6709,7 +6727,7 @@
       <c r="AL72" s="3"/>
       <c r="AM72" s="3"/>
     </row>
-    <row r="73" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="3"/>
       <c r="B73" s="3" t="s">
         <v>39</v>
@@ -6776,7 +6794,7 @@
       <c r="AL73" s="3"/>
       <c r="AM73" s="3"/>
     </row>
-    <row r="74" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="3"/>
       <c r="B74" s="3" t="s">
         <v>39</v>
@@ -6843,7 +6861,7 @@
       <c r="AL74" s="3"/>
       <c r="AM74" s="3"/>
     </row>
-    <row r="75" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75" s="3"/>
       <c r="B75" s="3" t="s">
         <v>39</v>
@@ -6910,7 +6928,7 @@
       <c r="AL75" s="3"/>
       <c r="AM75" s="3"/>
     </row>
-    <row r="76" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
       <c r="B76" s="3" t="s">
         <v>39</v>
@@ -6977,7 +6995,7 @@
       <c r="AL76" s="3"/>
       <c r="AM76" s="3"/>
     </row>
-    <row r="77" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="3"/>
       <c r="B77" s="3" t="s">
         <v>39</v>
@@ -7048,7 +7066,7 @@
       <c r="AL77" s="3"/>
       <c r="AM77" s="3"/>
     </row>
-    <row r="78" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="3"/>
       <c r="B78" s="3" t="s">
         <v>39</v>
@@ -7119,7 +7137,7 @@
       <c r="AL78" s="3"/>
       <c r="AM78" s="3"/>
     </row>
-    <row r="79" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79" s="3"/>
       <c r="B79" s="3" t="s">
         <v>39</v>
@@ -7188,7 +7206,7 @@
       <c r="AL79" s="3"/>
       <c r="AM79" s="3"/>
     </row>
-    <row r="80" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
       <c r="B80" s="3" t="s">
         <v>39</v>
@@ -7257,7 +7275,7 @@
       <c r="AL80" s="3"/>
       <c r="AM80" s="3"/>
     </row>
-    <row r="81" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81" s="3"/>
       <c r="B81" s="3" t="s">
         <v>39</v>
@@ -7326,7 +7344,7 @@
       <c r="AL81" s="3"/>
       <c r="AM81" s="3"/>
     </row>
-    <row r="82" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="3"/>
       <c r="B82" s="3" t="s">
         <v>39</v>
@@ -7395,7 +7413,7 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="3" t="s">
         <v>39</v>
@@ -7473,7 +7491,7 @@
         <v>-10.51</v>
       </c>
     </row>
-    <row r="84" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84" s="3"/>
       <c r="B84" s="3" t="s">
         <v>39</v>
@@ -7540,7 +7558,7 @@
       <c r="AK84" s="3"/>
       <c r="AL84" s="3"/>
     </row>
-    <row r="85" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85" s="3"/>
       <c r="B85" s="3" t="s">
         <v>39</v>
@@ -7608,7 +7626,7 @@
       <c r="AK85" s="3"/>
       <c r="AL85" s="3"/>
     </row>
-    <row r="86" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="3"/>
       <c r="B86" s="3" t="s">
         <v>39</v>
@@ -7686,7 +7704,7 @@
         <v>-5.0839999999999996</v>
       </c>
     </row>
-    <row r="87" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
       <c r="B87" s="3" t="s">
         <v>39</v>
@@ -7755,7 +7773,7 @@
       <c r="AL87" s="3"/>
       <c r="AM87" s="3"/>
     </row>
-    <row r="88" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
       <c r="B88" s="3" t="s">
         <v>39</v>
@@ -7824,7 +7842,7 @@
       <c r="AL88" s="3"/>
       <c r="AM88" s="3"/>
     </row>
-    <row r="89" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89" s="3"/>
       <c r="B89" s="3" t="s">
         <v>39</v>
@@ -7893,7 +7911,7 @@
       <c r="AL89" s="3"/>
       <c r="AM89" s="3"/>
     </row>
-    <row r="90" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="3"/>
       <c r="B90" s="3" t="s">
         <v>39</v>
@@ -7962,7 +7980,7 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
       <c r="B91" s="3" t="s">
         <v>39</v>
@@ -8031,7 +8049,7 @@
       <c r="AL91" s="3"/>
       <c r="AM91" s="3"/>
     </row>
-    <row r="92" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
       <c r="B92" s="3" t="s">
         <v>39</v>
@@ -8100,7 +8118,7 @@
       <c r="AL92" s="3"/>
       <c r="AM92" s="3"/>
     </row>
-    <row r="93" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93" s="3"/>
       <c r="B93" s="3" t="s">
         <v>39</v>
@@ -8169,7 +8187,7 @@
       <c r="AL93" s="3"/>
       <c r="AM93" s="3"/>
     </row>
-    <row r="94" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
       <c r="B94" s="3" t="s">
         <v>39</v>
@@ -8238,7 +8256,7 @@
       <c r="AL94" s="3"/>
       <c r="AM94" s="3"/>
     </row>
-    <row r="95" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
       <c r="B95" s="3" t="s">
         <v>39</v>
@@ -8307,7 +8325,7 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="3" t="s">
         <v>39</v>
@@ -8376,7 +8394,7 @@
       <c r="AL96" s="3"/>
       <c r="AM96" s="3"/>
     </row>
-    <row r="97" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="3" t="s">
         <v>39</v>
@@ -8445,7 +8463,7 @@
       <c r="AL97" s="3"/>
       <c r="AM97" s="3"/>
     </row>
-    <row r="98" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="3" t="s">
         <v>39</v>
@@ -8514,7 +8532,7 @@
       <c r="AL98" s="3"/>
       <c r="AM98" s="3"/>
     </row>
-    <row r="99" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="3" t="s">
         <v>39</v>
@@ -8583,7 +8601,7 @@
       <c r="AL99" s="3"/>
       <c r="AM99" s="3"/>
     </row>
-    <row r="100" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="3" t="s">
         <v>39</v>
@@ -8652,7 +8670,7 @@
       <c r="AL100" s="3"/>
       <c r="AM100" s="3"/>
     </row>
-    <row r="101" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="3" t="s">
         <v>39</v>
@@ -8721,7 +8739,7 @@
       <c r="AL101" s="3"/>
       <c r="AM101" s="3"/>
     </row>
-    <row r="102" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
       <c r="B102" s="3" t="s">
         <v>39</v>
@@ -8790,7 +8808,7 @@
       <c r="AL102" s="3"/>
       <c r="AM102" s="3"/>
     </row>
-    <row r="103" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
       <c r="B103" s="3" t="s">
         <v>39</v>
@@ -8859,7 +8877,7 @@
       <c r="AL103" s="3"/>
       <c r="AM103" s="3"/>
     </row>
-    <row r="104" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
       <c r="B104" s="3" t="s">
         <v>39</v>
@@ -8928,7 +8946,7 @@
       <c r="AL104" s="3"/>
       <c r="AM104" s="3"/>
     </row>
-    <row r="105" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
       <c r="B105" s="3" t="s">
         <v>39</v>
@@ -8999,7 +9017,7 @@
       <c r="AL105" s="3"/>
       <c r="AM105" s="3"/>
     </row>
-    <row r="106" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A106" s="3"/>
       <c r="B106" s="3" t="s">
         <v>39</v>
@@ -9070,7 +9088,7 @@
       <c r="AL106" s="3"/>
       <c r="AM106" s="3"/>
     </row>
-    <row r="107" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
       <c r="B107" s="3" t="s">
         <v>39</v>
@@ -9141,7 +9159,7 @@
       <c r="AL107" s="3"/>
       <c r="AM107" s="3"/>
     </row>
-    <row r="108" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
       <c r="B108" s="3" t="s">
         <v>39</v>
@@ -9212,7 +9230,7 @@
       <c r="AL108" s="3"/>
       <c r="AM108" s="3"/>
     </row>
-    <row r="109" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109" s="3"/>
       <c r="B109" s="3" t="s">
         <v>39</v>
@@ -9283,7 +9301,7 @@
       <c r="AL109" s="3"/>
       <c r="AM109" s="3"/>
     </row>
-    <row r="110" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A110" s="3"/>
       <c r="B110" s="3" t="s">
         <v>39</v>
@@ -9354,7 +9372,7 @@
       <c r="AL110" s="3"/>
       <c r="AM110" s="3"/>
     </row>
-    <row r="111" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="3" t="s">
         <v>39</v>
@@ -9425,7 +9443,7 @@
       <c r="AL111" s="3"/>
       <c r="AM111" s="3"/>
     </row>
-    <row r="112" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
       <c r="B112" s="3" t="s">
         <v>39</v>
@@ -9494,7 +9512,7 @@
       <c r="AL112" s="3"/>
       <c r="AM112" s="3"/>
     </row>
-    <row r="113" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113" s="3"/>
       <c r="B113" s="3" t="s">
         <v>39</v>
@@ -9563,7 +9581,7 @@
       <c r="AL113" s="3"/>
       <c r="AM113" s="3"/>
     </row>
-    <row r="114" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="3"/>
       <c r="B114" s="3" t="s">
         <v>39</v>
@@ -9634,7 +9652,7 @@
       <c r="AL114" s="3"/>
       <c r="AM114" s="3"/>
     </row>
-    <row r="115" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A115" s="3"/>
       <c r="B115" s="3" t="s">
         <v>39</v>
@@ -9703,7 +9721,7 @@
       <c r="AL115" s="3"/>
       <c r="AM115" s="3"/>
     </row>
-    <row r="116" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A116" s="3"/>
       <c r="B116" s="3" t="s">
         <v>39</v>
@@ -9777,7 +9795,7 @@
       <c r="AK116" s="3"/>
       <c r="AL116" s="3"/>
       <c r="AM116" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN116" s="5">
         <v>5.7700000000000001E-2</v>
@@ -9807,7 +9825,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A117" s="3"/>
       <c r="B117" s="3" t="s">
         <v>39</v>
@@ -9872,7 +9890,7 @@
         <v>133</v>
       </c>
       <c r="AF117" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG117" s="3"/>
       <c r="AH117" s="3"/>
@@ -9881,7 +9899,7 @@
       <c r="AK117" s="3"/>
       <c r="AL117" s="3"/>
       <c r="AM117" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AN117" s="5">
         <v>5.7700000000000001E-2</v>
@@ -9911,7 +9929,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118" s="3"/>
       <c r="B118" s="3" t="s">
         <v>39</v>
@@ -9988,7 +10006,7 @@
       <c r="AK118" s="3"/>
       <c r="AL118" s="3"/>
       <c r="AM118" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN118" s="5">
         <v>5.7700000000000001E-2</v>
@@ -10018,7 +10036,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A119" s="3"/>
       <c r="B119" s="3" t="s">
         <v>39</v>
@@ -10086,7 +10104,7 @@
         <v>133</v>
       </c>
       <c r="AF119" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG119" s="3"/>
       <c r="AH119" s="3"/>
@@ -10095,7 +10113,7 @@
       <c r="AK119" s="3"/>
       <c r="AL119" s="3"/>
       <c r="AM119" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AN119" s="5">
         <v>5.7700000000000001E-2</v>
@@ -10125,7 +10143,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
       <c r="B120" s="3" t="s">
         <v>39</v>
@@ -10199,7 +10217,7 @@
       <c r="AK120" s="3"/>
       <c r="AL120" s="3"/>
       <c r="AM120" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN120" s="5">
         <v>5.7700000000000001E-2</v>
@@ -10229,7 +10247,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A121" s="3"/>
       <c r="B121" s="3" t="s">
         <v>39</v>
@@ -10294,7 +10312,7 @@
         <v>133</v>
       </c>
       <c r="AF121" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG121" s="3"/>
       <c r="AH121" s="3"/>
@@ -10303,7 +10321,7 @@
       <c r="AK121" s="3"/>
       <c r="AL121" s="3"/>
       <c r="AM121" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AN121" s="5">
         <v>5.7700000000000001E-2</v>
@@ -10333,7 +10351,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>
       <c r="B122" s="3" t="s">
         <v>39</v>
@@ -10404,7 +10422,7 @@
         <v>7</v>
       </c>
       <c r="AH122" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AI122" s="3"/>
       <c r="AJ122" s="3">
@@ -10417,7 +10435,7 @@
         <v>-0.11849999999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
       <c r="B123" s="3" t="s">
         <v>39</v>
@@ -10488,7 +10506,7 @@
         <v>7</v>
       </c>
       <c r="AH123" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AI123" s="3"/>
       <c r="AJ123" s="3">
@@ -10500,11 +10518,11 @@
       <c r="AL123" s="3">
         <v>-0.11849999999999999</v>
       </c>
-      <c r="AW123" s="5">
+      <c r="AZ123" s="5">
         <v>87</v>
       </c>
     </row>
-    <row r="124" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
       <c r="B124" s="3" t="s">
         <v>39</v>
@@ -10575,7 +10593,7 @@
       <c r="AL124" s="3"/>
       <c r="AM124" s="3"/>
     </row>
-    <row r="125" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A125" s="3"/>
       <c r="B125" s="3" t="s">
         <v>39</v>
@@ -10646,7 +10664,7 @@
       <c r="AL125" s="3"/>
       <c r="AM125" s="3"/>
     </row>
-    <row r="126" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A126" s="3"/>
       <c r="B126" s="3" t="s">
         <v>39</v>
@@ -10717,7 +10735,7 @@
       <c r="AL126" s="3"/>
       <c r="AM126" s="3"/>
     </row>
-    <row r="127" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
       <c r="B127" s="3" t="s">
         <v>39</v>
@@ -10788,7 +10806,7 @@
       <c r="AL127" s="3"/>
       <c r="AM127" s="3"/>
     </row>
-    <row r="128" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
       <c r="B128" s="3" t="s">
         <v>39</v>
@@ -10859,7 +10877,7 @@
       <c r="AL128" s="3"/>
       <c r="AM128" s="3"/>
     </row>
-    <row r="129" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A129" s="3"/>
       <c r="B129" s="3" t="s">
         <v>39</v>
@@ -10930,7 +10948,7 @@
       <c r="AL129" s="3"/>
       <c r="AM129" s="3"/>
     </row>
-    <row r="130" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A130" s="3"/>
       <c r="B130" s="3" t="s">
         <v>39</v>
@@ -11001,7 +11019,7 @@
       <c r="AL130" s="3"/>
       <c r="AM130" s="3"/>
     </row>
-    <row r="131" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
       <c r="B131" s="3" t="s">
         <v>39</v>
@@ -11072,7 +11090,7 @@
       <c r="AL131" s="3"/>
       <c r="AM131" s="3"/>
     </row>
-    <row r="132" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
       <c r="B132" s="3" t="s">
         <v>39</v>
@@ -11143,7 +11161,7 @@
       <c r="AL132" s="3"/>
       <c r="AM132" s="3"/>
     </row>
-    <row r="133" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133" s="3"/>
       <c r="B133" s="3" t="s">
         <v>39</v>
@@ -11214,7 +11232,7 @@
       <c r="AL133" s="3"/>
       <c r="AM133" s="3"/>
     </row>
-    <row r="134" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A134" s="3"/>
       <c r="B134" s="3" t="s">
         <v>39</v>
@@ -11285,7 +11303,7 @@
       <c r="AL134" s="3"/>
       <c r="AM134" s="3"/>
     </row>
-    <row r="135" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
       <c r="B135" s="3" t="s">
         <v>39</v>
@@ -11356,7 +11374,7 @@
       <c r="AL135" s="3"/>
       <c r="AM135" s="3"/>
     </row>
-    <row r="136" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136" s="3"/>
       <c r="B136" s="3" t="s">
         <v>39</v>
@@ -11436,7 +11454,7 @@
         <v>-3.9089999999999998</v>
       </c>
     </row>
-    <row r="137" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="3"/>
       <c r="B137" s="3" t="s">
         <v>39</v>
@@ -11507,7 +11525,7 @@
       <c r="AL137" s="3"/>
       <c r="AM137" s="3"/>
     </row>
-    <row r="138" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A138" s="3"/>
       <c r="B138" s="3" t="s">
         <v>39</v>
@@ -11578,7 +11596,7 @@
       <c r="AL138" s="3"/>
       <c r="AM138" s="3"/>
     </row>
-    <row r="139" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
       <c r="B139" s="3" t="s">
         <v>39</v>
@@ -11656,7 +11674,7 @@
         <v>0.53400000000000003</v>
       </c>
     </row>
-    <row r="140" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140" s="3"/>
       <c r="B140" s="3" t="s">
         <v>39</v>
@@ -11727,7 +11745,7 @@
       <c r="AL140" s="3"/>
       <c r="AM140" s="3"/>
     </row>
-    <row r="141" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141" s="3"/>
       <c r="B141" s="3" t="s">
         <v>39</v>
@@ -11798,7 +11816,7 @@
       <c r="AL141" s="3"/>
       <c r="AM141" s="3"/>
     </row>
-    <row r="142" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A142" s="3"/>
       <c r="B142" s="3" t="s">
         <v>39</v>
@@ -11869,7 +11887,7 @@
       <c r="AL142" s="3"/>
       <c r="AM142" s="3"/>
     </row>
-    <row r="143" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
       <c r="B143" s="3" t="s">
         <v>39</v>
@@ -11940,7 +11958,7 @@
       <c r="AL143" s="3"/>
       <c r="AM143" s="3"/>
     </row>
-    <row r="144" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
       <c r="B144" s="3" t="s">
         <v>39</v>
@@ -12011,7 +12029,7 @@
       <c r="AL144" s="3"/>
       <c r="AM144" s="3"/>
     </row>
-    <row r="145" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A145" s="3"/>
       <c r="B145" s="3" t="s">
         <v>39</v>
@@ -12089,7 +12107,7 @@
         <v>-1.7407999999999999</v>
       </c>
     </row>
-    <row r="146" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A146" s="3"/>
       <c r="B146" s="3" t="s">
         <v>39</v>
@@ -12167,7 +12185,7 @@
         <v>-1.7427999999999999</v>
       </c>
     </row>
-    <row r="147" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
       <c r="B147" s="3" t="s">
         <v>39</v>
@@ -12238,7 +12256,7 @@
       <c r="AL147" s="3"/>
       <c r="AM147" s="3"/>
     </row>
-    <row r="148" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
       <c r="B148" s="3" t="s">
         <v>39</v>
@@ -12309,7 +12327,7 @@
       <c r="AL148" s="3"/>
       <c r="AM148" s="3"/>
     </row>
-    <row r="149" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149" s="3"/>
       <c r="B149" s="3" t="s">
         <v>39</v>
@@ -12380,7 +12398,7 @@
       <c r="AL149" s="3"/>
       <c r="AM149" s="3"/>
     </row>
-    <row r="150" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A150" s="3"/>
       <c r="B150" s="3" t="s">
         <v>39</v>
@@ -12451,7 +12469,7 @@
       <c r="AL150" s="3"/>
       <c r="AM150" s="3"/>
     </row>
-    <row r="151" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A151" s="3"/>
       <c r="B151" s="3" t="s">
         <v>39</v>
@@ -12531,7 +12549,7 @@
         <v>-1.46</v>
       </c>
     </row>
-    <row r="152" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A152" s="3"/>
       <c r="B152" s="3" t="s">
         <v>39</v>
@@ -12611,7 +12629,7 @@
         <v>-4.7050000000000001</v>
       </c>
     </row>
-    <row r="153" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A153" s="3"/>
       <c r="B153" s="3" t="s">
         <v>39</v>
@@ -12682,7 +12700,7 @@
       <c r="AL153" s="3"/>
       <c r="AM153" s="3"/>
     </row>
-    <row r="154" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154" s="3"/>
       <c r="B154" s="3" t="s">
         <v>39</v>
@@ -12753,7 +12771,7 @@
       <c r="AL154" s="3"/>
       <c r="AM154" s="3"/>
     </row>
-    <row r="155" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A155" s="3"/>
       <c r="B155" s="3" t="s">
         <v>39</v>
@@ -12831,7 +12849,7 @@
         <v>6.4676</v>
       </c>
     </row>
-    <row r="156" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A156" s="3"/>
       <c r="B156" s="3" t="s">
         <v>39</v>
@@ -12909,7 +12927,7 @@
         <v>5.8742999999999999</v>
       </c>
     </row>
-    <row r="157" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A157" s="3"/>
       <c r="B157" s="3" t="s">
         <v>39</v>
@@ -12980,7 +12998,7 @@
       <c r="AL157" s="3"/>
       <c r="AM157" s="3"/>
     </row>
-    <row r="158" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A158" s="3"/>
       <c r="B158" s="3" t="s">
         <v>39</v>
@@ -13051,7 +13069,7 @@
       <c r="AL158" s="3"/>
       <c r="AM158" s="3"/>
     </row>
-    <row r="159" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A159" s="3"/>
       <c r="B159" s="3" t="s">
         <v>39</v>
@@ -13122,7 +13140,7 @@
       <c r="AL159" s="3"/>
       <c r="AM159" s="3"/>
     </row>
-    <row r="160" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A160" s="3"/>
       <c r="B160" s="3" t="s">
         <v>39</v>
@@ -13193,7 +13211,7 @@
       <c r="AL160" s="3"/>
       <c r="AM160" s="3"/>
     </row>
-    <row r="161" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A161" s="3"/>
       <c r="B161" s="3" t="s">
         <v>39</v>
@@ -13264,7 +13282,7 @@
       <c r="AL161" s="3"/>
       <c r="AM161" s="3"/>
     </row>
-    <row r="162" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A162" s="3"/>
       <c r="B162" s="3" t="s">
         <v>39</v>
@@ -13335,7 +13353,7 @@
       <c r="AL162" s="3"/>
       <c r="AM162" s="3"/>
     </row>
-    <row r="163" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A163" s="3"/>
       <c r="B163" s="3" t="s">
         <v>39</v>
@@ -13413,7 +13431,7 @@
         <v>2.2530000000000001</v>
       </c>
     </row>
-    <row r="164" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A164" s="3"/>
       <c r="B164" s="3" t="s">
         <v>39</v>
@@ -13491,7 +13509,7 @@
         <v>5.5399999999999998E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A165" s="3"/>
       <c r="B165" s="3" t="s">
         <v>39</v>
@@ -13562,7 +13580,7 @@
       <c r="AL165" s="3"/>
       <c r="AM165" s="3"/>
     </row>
-    <row r="166" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A166" s="3"/>
       <c r="B166" s="3" t="s">
         <v>39</v>
@@ -13633,7 +13651,7 @@
       <c r="AL166" s="3"/>
       <c r="AM166" s="3"/>
     </row>
-    <row r="167" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A167" s="3"/>
       <c r="B167" s="3" t="s">
         <v>39</v>
@@ -13704,7 +13722,7 @@
       <c r="AL167" s="3"/>
       <c r="AM167" s="3"/>
     </row>
-    <row r="168" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A168" s="3"/>
       <c r="B168" s="3" t="s">
         <v>39</v>
@@ -13775,7 +13793,7 @@
       <c r="AL168" s="3"/>
       <c r="AM168" s="3"/>
     </row>
-    <row r="169" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A169" s="3"/>
       <c r="B169" s="3" t="s">
         <v>39</v>
@@ -13846,7 +13864,7 @@
       <c r="AL169" s="3"/>
       <c r="AM169" s="3"/>
     </row>
-    <row r="170" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A170" s="3"/>
       <c r="B170" s="3" t="s">
         <v>39</v>
@@ -13917,7 +13935,7 @@
       <c r="AL170" s="3"/>
       <c r="AM170" s="3"/>
     </row>
-    <row r="171" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A171" s="3"/>
       <c r="B171" s="3" t="s">
         <v>39</v>
@@ -13995,7 +14013,7 @@
         <v>-6.52</v>
       </c>
     </row>
-    <row r="172" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A172" s="3"/>
       <c r="B172" s="3" t="s">
         <v>39</v>
@@ -14073,7 +14091,7 @@
         <v>-9.06</v>
       </c>
     </row>
-    <row r="173" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A173" s="3"/>
       <c r="B173" s="3" t="s">
         <v>39</v>
@@ -14144,7 +14162,7 @@
       <c r="AL173" s="3"/>
       <c r="AM173" s="3"/>
     </row>
-    <row r="174" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A174" s="3"/>
       <c r="B174" s="3" t="s">
         <v>39</v>
@@ -14215,7 +14233,7 @@
       <c r="AL174" s="3"/>
       <c r="AM174" s="3"/>
     </row>
-    <row r="175" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A175" s="3"/>
       <c r="B175" s="3" t="s">
         <v>39</v>
@@ -14286,7 +14304,7 @@
       <c r="AL175" s="3"/>
       <c r="AM175" s="3"/>
     </row>
-    <row r="176" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A176" s="3"/>
       <c r="B176" s="3" t="s">
         <v>39</v>
@@ -14364,7 +14382,7 @@
         <v>2.7088000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A177" s="3"/>
       <c r="B177" s="3" t="s">
         <v>39</v>
@@ -14442,7 +14460,7 @@
         <v>2.2382</v>
       </c>
     </row>
-    <row r="178" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A178" s="3"/>
       <c r="B178" s="3" t="s">
         <v>39</v>
@@ -14513,7 +14531,7 @@
       <c r="AL178" s="3"/>
       <c r="AM178" s="3"/>
     </row>
-    <row r="179" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A179" s="3"/>
       <c r="B179" s="3" t="s">
         <v>39</v>
@@ -14591,7 +14609,7 @@
         <v>0.90949999999999998</v>
       </c>
     </row>
-    <row r="180" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A180" s="3"/>
       <c r="B180" s="3" t="s">
         <v>39</v>
@@ -14669,7 +14687,7 @@
         <v>0.62350000000000005</v>
       </c>
     </row>
-    <row r="181" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A181" s="3"/>
       <c r="B181" s="3" t="s">
         <v>39</v>
@@ -14740,7 +14758,7 @@
       <c r="AL181" s="3"/>
       <c r="AM181" s="3"/>
     </row>
-    <row r="182" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A182" s="3"/>
       <c r="B182" s="3" t="s">
         <v>39</v>
@@ -14811,7 +14829,7 @@
       <c r="AL182" s="3"/>
       <c r="AM182" s="3"/>
     </row>
-    <row r="183" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A183" s="3"/>
       <c r="B183" s="3" t="s">
         <v>39</v>
@@ -14882,7 +14900,7 @@
       <c r="AL183" s="3"/>
       <c r="AM183" s="3"/>
     </row>
-    <row r="184" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A184" s="3"/>
       <c r="B184" s="3" t="s">
         <v>39</v>
@@ -14951,7 +14969,7 @@
       <c r="AL184" s="3"/>
       <c r="AM184" s="3"/>
     </row>
-    <row r="185" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A185" s="3"/>
       <c r="B185" s="3" t="s">
         <v>39</v>
@@ -15036,7 +15054,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="186" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A186" s="3"/>
       <c r="B186" s="3" t="s">
         <v>39</v>
@@ -15113,7 +15131,7 @@
       <c r="AL186" s="3"/>
       <c r="AM186" s="3"/>
     </row>
-    <row r="187" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A187" s="3"/>
       <c r="B187" s="3" t="s">
         <v>39</v>
@@ -15190,7 +15208,7 @@
       <c r="AL187" s="3"/>
       <c r="AM187" s="3"/>
     </row>
-    <row r="188" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A188" s="3"/>
       <c r="B188" s="3" t="s">
         <v>39</v>
@@ -15267,7 +15285,7 @@
       <c r="AL188" s="3"/>
       <c r="AM188" s="3"/>
     </row>
-    <row r="189" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A189" s="3"/>
       <c r="B189" s="3" t="s">
         <v>39</v>
@@ -15344,7 +15362,7 @@
       <c r="AL189" s="3"/>
       <c r="AM189" s="3"/>
     </row>
-    <row r="190" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A190" s="3"/>
       <c r="B190" s="3" t="s">
         <v>39</v>
@@ -15421,7 +15439,7 @@
       <c r="AL190" s="3"/>
       <c r="AM190" s="3"/>
     </row>
-    <row r="191" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A191" s="3"/>
       <c r="B191" s="3" t="s">
         <v>39</v>
@@ -15498,7 +15516,7 @@
       <c r="AL191" s="3"/>
       <c r="AM191" s="3"/>
     </row>
-    <row r="192" spans="1:43" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:43" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A192" s="3"/>
       <c r="B192" s="3" t="s">
         <v>39</v>
@@ -15575,7 +15593,7 @@
       <c r="AL192" s="3"/>
       <c r="AM192" s="3"/>
     </row>
-    <row r="193" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A193" s="3"/>
       <c r="B193" s="3" t="s">
         <v>39</v>
@@ -15652,7 +15670,7 @@
       <c r="AL193" s="3"/>
       <c r="AM193" s="3"/>
     </row>
-    <row r="194" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A194" s="3"/>
       <c r="B194" s="3" t="s">
         <v>39</v>
@@ -15729,7 +15747,7 @@
       <c r="AL194" s="3"/>
       <c r="AM194" s="3"/>
     </row>
-    <row r="195" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A195" s="3"/>
       <c r="B195" s="3" t="s">
         <v>39</v>
@@ -15806,7 +15824,7 @@
       <c r="AL195" s="3"/>
       <c r="AM195" s="3"/>
     </row>
-    <row r="196" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A196" s="3"/>
       <c r="B196" s="3" t="s">
         <v>39</v>
@@ -15883,7 +15901,7 @@
       <c r="AL196" s="3"/>
       <c r="AM196" s="3"/>
     </row>
-    <row r="197" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A197" s="3"/>
       <c r="B197" s="3" t="s">
         <v>39</v>
@@ -15960,7 +15978,7 @@
       <c r="AL197" s="3"/>
       <c r="AM197" s="3"/>
     </row>
-    <row r="198" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A198" s="3"/>
       <c r="B198" s="3" t="s">
         <v>39</v>
@@ -16037,7 +16055,7 @@
       <c r="AL198" s="3"/>
       <c r="AM198" s="3"/>
     </row>
-    <row r="199" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A199" s="3"/>
       <c r="B199" s="3" t="s">
         <v>39</v>
@@ -16114,7 +16132,7 @@
       <c r="AL199" s="3"/>
       <c r="AM199" s="3"/>
     </row>
-    <row r="200" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A200" s="3"/>
       <c r="B200" s="3" t="s">
         <v>39</v>
@@ -16191,7 +16209,7 @@
       <c r="AL200" s="3"/>
       <c r="AM200" s="3"/>
     </row>
-    <row r="201" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A201" s="3"/>
       <c r="B201" s="3" t="s">
         <v>39</v>
@@ -16268,7 +16286,7 @@
       <c r="AL201" s="3"/>
       <c r="AM201" s="3"/>
     </row>
-    <row r="202" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A202" s="3"/>
       <c r="B202" s="3" t="s">
         <v>39</v>
@@ -16337,7 +16355,7 @@
       <c r="AL202" s="3"/>
       <c r="AM202" s="3"/>
     </row>
-    <row r="203" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A203" s="3"/>
       <c r="B203" s="3" t="s">
         <v>39</v>
@@ -16406,7 +16424,7 @@
       <c r="AL203" s="3"/>
       <c r="AM203" s="3"/>
     </row>
-    <row r="204" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A204" s="3"/>
       <c r="B204" s="3" t="s">
         <v>39</v>
@@ -16477,7 +16495,7 @@
       <c r="AL204" s="3"/>
       <c r="AM204" s="3"/>
     </row>
-    <row r="205" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A205" s="3"/>
       <c r="B205" s="3" t="s">
         <v>39</v>
@@ -16548,7 +16566,7 @@
       <c r="AL205" s="3"/>
       <c r="AM205" s="3"/>
     </row>
-    <row r="206" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A206" s="3"/>
       <c r="B206" s="3" t="s">
         <v>39</v>
@@ -16622,7 +16640,7 @@
       <c r="AK206" s="3"/>
       <c r="AL206" s="3"/>
       <c r="AM206" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN206" s="5">
         <v>5.7700000000000001E-2</v>
@@ -16652,7 +16670,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="207" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A207" s="3"/>
       <c r="B207" s="3" t="s">
         <v>39</v>
@@ -16717,7 +16735,7 @@
         <v>133</v>
       </c>
       <c r="AF207" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG207" s="3"/>
       <c r="AH207" s="3"/>
@@ -16726,7 +16744,7 @@
       <c r="AK207" s="3"/>
       <c r="AL207" s="3"/>
       <c r="AM207" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AN207" s="5">
         <v>5.7700000000000001E-2</v>
@@ -16756,7 +16774,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="208" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A208" s="3"/>
       <c r="B208" s="3" t="s">
         <v>39</v>
@@ -16827,7 +16845,7 @@
       <c r="AL208" s="3"/>
       <c r="AM208" s="3"/>
     </row>
-    <row r="209" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A209" s="3"/>
       <c r="B209" s="3" t="s">
         <v>39</v>
@@ -16898,7 +16916,7 @@
       <c r="AL209" s="3"/>
       <c r="AM209" s="3"/>
     </row>
-    <row r="210" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A210" s="3"/>
       <c r="B210" s="3" t="s">
         <v>39</v>
@@ -16967,7 +16985,7 @@
       <c r="AL210" s="3"/>
       <c r="AM210" s="3"/>
     </row>
-    <row r="211" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A211" s="3"/>
       <c r="B211" s="3" t="s">
         <v>39</v>
@@ -17036,7 +17054,7 @@
       <c r="AL211" s="3"/>
       <c r="AM211" s="3"/>
     </row>
-    <row r="212" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A212" s="3"/>
       <c r="B212" s="3" t="s">
         <v>39</v>
@@ -17105,7 +17123,7 @@
       <c r="AL212" s="3"/>
       <c r="AM212" s="3"/>
     </row>
-    <row r="213" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A213" s="3"/>
       <c r="B213" s="3" t="s">
         <v>39</v>
@@ -17174,7 +17192,7 @@
       <c r="AL213" s="3"/>
       <c r="AM213" s="3"/>
     </row>
-    <row r="214" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A214" s="3"/>
       <c r="B214" s="3" t="s">
         <v>39</v>
@@ -17245,7 +17263,7 @@
       <c r="AL214" s="3"/>
       <c r="AM214" s="3"/>
     </row>
-    <row r="215" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A215" s="3"/>
       <c r="B215" s="3" t="s">
         <v>39</v>
@@ -17316,7 +17334,7 @@
       <c r="AL215" s="3"/>
       <c r="AM215" s="3"/>
     </row>
-    <row r="216" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A216" s="3"/>
       <c r="B216" s="3" t="s">
         <v>39</v>
@@ -17387,7 +17405,7 @@
       <c r="AL216" s="3"/>
       <c r="AM216" s="3"/>
     </row>
-    <row r="217" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A217" s="3"/>
       <c r="B217" s="3" t="s">
         <v>39</v>
@@ -17458,7 +17476,7 @@
       <c r="AL217" s="3"/>
       <c r="AM217" s="3"/>
     </row>
-    <row r="218" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A218" s="3"/>
       <c r="B218" s="3" t="s">
         <v>39</v>
@@ -17527,7 +17545,7 @@
       <c r="AL218" s="3"/>
       <c r="AM218" s="3"/>
     </row>
-    <row r="219" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A219" s="3"/>
       <c r="B219" s="3" t="s">
         <v>39</v>
@@ -17596,7 +17614,7 @@
       <c r="AL219" s="3"/>
       <c r="AM219" s="3"/>
     </row>
-    <row r="220" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A220" s="3"/>
       <c r="B220" s="3" t="s">
         <v>39</v>
@@ -17665,7 +17683,7 @@
       <c r="AL220" s="3"/>
       <c r="AM220" s="3"/>
     </row>
-    <row r="221" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A221" s="3"/>
       <c r="B221" s="3" t="s">
         <v>39</v>
@@ -17734,7 +17752,7 @@
       <c r="AL221" s="3"/>
       <c r="AM221" s="3"/>
     </row>
-    <row r="222" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A222" s="3"/>
       <c r="B222" s="3" t="s">
         <v>39</v>
@@ -17805,7 +17823,7 @@
       <c r="AL222" s="3"/>
       <c r="AM222" s="3"/>
     </row>
-    <row r="223" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A223" s="3"/>
       <c r="B223" s="3" t="s">
         <v>39</v>
@@ -17876,7 +17894,7 @@
       <c r="AL223" s="3"/>
       <c r="AM223" s="3"/>
     </row>
-    <row r="224" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A224" s="3"/>
       <c r="B224" s="3" t="s">
         <v>39</v>
@@ -17947,7 +17965,7 @@
       <c r="AL224" s="3"/>
       <c r="AM224" s="3"/>
     </row>
-    <row r="225" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A225" s="3"/>
       <c r="B225" s="3" t="s">
         <v>39</v>
@@ -18018,7 +18036,7 @@
       <c r="AL225" s="3"/>
       <c r="AM225" s="3"/>
     </row>
-    <row r="226" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A226" s="3"/>
       <c r="B226" s="3" t="s">
         <v>39</v>
@@ -18087,7 +18105,7 @@
       <c r="AL226" s="3"/>
       <c r="AM226" s="3"/>
     </row>
-    <row r="227" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A227" s="3"/>
       <c r="B227" s="3" t="s">
         <v>39</v>
@@ -18156,7 +18174,7 @@
       <c r="AL227" s="3"/>
       <c r="AM227" s="3"/>
     </row>
-    <row r="228" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A228" s="3"/>
       <c r="B228" s="3" t="s">
         <v>39</v>
@@ -18225,7 +18243,7 @@
       <c r="AL228" s="3"/>
       <c r="AM228" s="3"/>
     </row>
-    <row r="229" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A229" s="3"/>
       <c r="B229" s="3" t="s">
         <v>39</v>
@@ -18294,7 +18312,7 @@
       <c r="AL229" s="3"/>
       <c r="AM229" s="3"/>
     </row>
-    <row r="230" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A230" s="3"/>
       <c r="B230" s="3" t="s">
         <v>39</v>
@@ -18365,7 +18383,7 @@
       <c r="AL230" s="3"/>
       <c r="AM230" s="3"/>
     </row>
-    <row r="231" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A231" s="3"/>
       <c r="B231" s="3" t="s">
         <v>39</v>
@@ -18436,7 +18454,7 @@
       <c r="AL231" s="3"/>
       <c r="AM231" s="3"/>
     </row>
-    <row r="232" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A232" s="3"/>
       <c r="B232" s="3" t="s">
         <v>39</v>
@@ -18505,7 +18523,7 @@
       <c r="AL232" s="3"/>
       <c r="AM232" s="3"/>
     </row>
-    <row r="233" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A233" s="3"/>
       <c r="B233" s="3" t="s">
         <v>39</v>
@@ -18574,7 +18592,7 @@
       <c r="AL233" s="3"/>
       <c r="AM233" s="3"/>
     </row>
-    <row r="234" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A234" s="3"/>
       <c r="B234" s="3" t="s">
         <v>39</v>
@@ -18643,7 +18661,7 @@
       <c r="AL234" s="3"/>
       <c r="AM234" s="3"/>
     </row>
-    <row r="235" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A235" s="3"/>
       <c r="B235" s="3" t="s">
         <v>39</v>
@@ -18712,7 +18730,7 @@
       <c r="AL235" s="3"/>
       <c r="AM235" s="3"/>
     </row>
-    <row r="236" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A236" s="3"/>
       <c r="B236" s="3" t="s">
         <v>39</v>
@@ -18783,7 +18801,7 @@
       <c r="AL236" s="3"/>
       <c r="AM236" s="3"/>
     </row>
-    <row r="237" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A237" s="3"/>
       <c r="B237" s="3" t="s">
         <v>39</v>
@@ -18861,7 +18879,7 @@
         <v>1.8308</v>
       </c>
     </row>
-    <row r="238" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A238" s="3"/>
       <c r="B238" s="3" t="s">
         <v>39</v>
@@ -18939,7 +18957,7 @@
         <v>2.5735999999999999</v>
       </c>
     </row>
-    <row r="239" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A239" s="3"/>
       <c r="B239" s="3" t="s">
         <v>39</v>
@@ -19010,7 +19028,7 @@
       <c r="AL239" s="3"/>
       <c r="AM239" s="3"/>
     </row>
-    <row r="240" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A240" s="3"/>
       <c r="B240" s="3" t="s">
         <v>39</v>
@@ -19088,7 +19106,7 @@
         <v>-9.06</v>
       </c>
     </row>
-    <row r="241" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A241" s="3"/>
       <c r="B241" s="3" t="s">
         <v>39</v>
@@ -19166,7 +19184,7 @@
         <v>0.62350000000000005</v>
       </c>
     </row>
-    <row r="242" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A242" s="3"/>
       <c r="B242" s="3" t="s">
         <v>39</v>
@@ -19237,7 +19255,7 @@
         <v>7</v>
       </c>
       <c r="AH242" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AI242" s="3"/>
       <c r="AJ242" s="3">
@@ -19250,7 +19268,7 @@
         <v>-0.11849999999999999</v>
       </c>
     </row>
-    <row r="243" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A243" s="3"/>
       <c r="B243" s="3" t="s">
         <v>39</v>
@@ -19321,7 +19339,7 @@
         <v>7</v>
       </c>
       <c r="AH243" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AI243" s="3"/>
       <c r="AJ243" s="3">
@@ -19333,11 +19351,11 @@
       <c r="AL243" s="3">
         <v>-0.11849999999999999</v>
       </c>
-      <c r="AW243" s="5">
+      <c r="AZ243" s="5">
         <v>87</v>
       </c>
     </row>
-    <row r="244" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A244" s="3"/>
       <c r="B244" s="3" t="s">
         <v>39</v>
@@ -19408,7 +19426,7 @@
       <c r="AL244" s="3"/>
       <c r="AM244" s="3"/>
     </row>
-    <row r="245" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A245" s="3"/>
       <c r="B245" s="3" t="s">
         <v>39</v>
@@ -19479,7 +19497,7 @@
       <c r="AL245" s="3"/>
       <c r="AM245" s="3"/>
     </row>
-    <row r="246" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A246" s="3"/>
       <c r="B246" s="3" t="s">
         <v>39</v>
@@ -19559,7 +19577,7 @@
         <v>-3.9089999999999998</v>
       </c>
     </row>
-    <row r="247" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A247" s="3"/>
       <c r="B247" s="3" t="s">
         <v>39</v>
@@ -19635,7 +19653,7 @@
         <v>0.53400000000000003</v>
       </c>
     </row>
-    <row r="248" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A248" s="3"/>
       <c r="B248" s="3" t="s">
         <v>39</v>
@@ -19706,7 +19724,7 @@
       <c r="AL248" s="3"/>
       <c r="AM248" s="3"/>
     </row>
-    <row r="249" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A249" s="3"/>
       <c r="B249" s="3" t="s">
         <v>39</v>
@@ -19784,7 +19802,7 @@
         <v>-1.7407999999999999</v>
       </c>
     </row>
-    <row r="250" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A250" s="3"/>
       <c r="B250" s="3" t="s">
         <v>39</v>
@@ -19862,7 +19880,7 @@
         <v>-1.7427999999999999</v>
       </c>
     </row>
-    <row r="251" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A251" s="3"/>
       <c r="B251" s="3" t="s">
         <v>39</v>
@@ -19933,7 +19951,7 @@
       <c r="AL251" s="3"/>
       <c r="AM251" s="3"/>
     </row>
-    <row r="252" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A252" s="3"/>
       <c r="B252" s="3" t="s">
         <v>39</v>
@@ -20013,7 +20031,7 @@
         <v>-1.46</v>
       </c>
     </row>
-    <row r="253" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A253" s="3"/>
       <c r="B253" s="3" t="s">
         <v>39</v>
@@ -20093,7 +20111,7 @@
         <v>-4.7050000000000001</v>
       </c>
     </row>
-    <row r="254" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A254" s="3"/>
       <c r="B254" s="3" t="s">
         <v>39</v>
@@ -20171,7 +20189,7 @@
         <v>6.4676</v>
       </c>
     </row>
-    <row r="255" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A255" s="3"/>
       <c r="B255" s="3" t="s">
         <v>39</v>
@@ -20249,7 +20267,7 @@
         <v>5.8742999999999999</v>
       </c>
     </row>
-    <row r="256" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A256" s="3"/>
       <c r="B256" s="3" t="s">
         <v>39</v>
@@ -20320,7 +20338,7 @@
       <c r="AL256" s="3"/>
       <c r="AM256" s="3"/>
     </row>
-    <row r="257" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A257" s="3"/>
       <c r="B257" s="3" t="s">
         <v>39</v>
@@ -20398,7 +20416,7 @@
         <v>2.2530000000000001</v>
       </c>
     </row>
-    <row r="258" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A258" s="3"/>
       <c r="B258" s="3" t="s">
         <v>39</v>
@@ -20476,7 +20494,7 @@
         <v>5.5399999999999998E-2</v>
       </c>
     </row>
-    <row r="259" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A259" s="3"/>
       <c r="B259" s="3" t="s">
         <v>39</v>
@@ -20547,7 +20565,7 @@
       <c r="AL259" s="3"/>
       <c r="AM259" s="3"/>
     </row>
-    <row r="260" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A260" s="3"/>
       <c r="B260" s="3" t="s">
         <v>39</v>
@@ -20618,7 +20636,7 @@
       <c r="AL260" s="3"/>
       <c r="AM260" s="3"/>
     </row>
-    <row r="261" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A261" s="3"/>
       <c r="B261" s="3" t="s">
         <v>39</v>
@@ -20696,7 +20714,7 @@
         <v>-6.52</v>
       </c>
     </row>
-    <row r="262" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A262" s="3"/>
       <c r="B262" s="3" t="s">
         <v>39</v>
@@ -20774,7 +20792,7 @@
         <v>-10.51</v>
       </c>
     </row>
-    <row r="263" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A263" s="3"/>
       <c r="B263" s="3" t="s">
         <v>39</v>
@@ -20845,7 +20863,7 @@
       <c r="AL263" s="3"/>
       <c r="AM263" s="3"/>
     </row>
-    <row r="264" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A264" s="3"/>
       <c r="B264" s="3" t="s">
         <v>39</v>
@@ -20923,7 +20941,7 @@
         <v>2.7088000000000001</v>
       </c>
     </row>
-    <row r="265" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A265" s="3"/>
       <c r="B265" s="3" t="s">
         <v>39</v>
@@ -21001,7 +21019,7 @@
         <v>2.2382</v>
       </c>
     </row>
-    <row r="266" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A266" s="3"/>
       <c r="B266" s="3" t="s">
         <v>39</v>
@@ -21079,7 +21097,7 @@
         <v>0.90949999999999998</v>
       </c>
     </row>
-    <row r="267" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A267" s="3"/>
       <c r="B267" s="3" t="s">
         <v>39</v>
